--- a/data/berita_2026-08-04.xlsx
+++ b/data/berita_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -477,912 +477,912 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cerita Saleh Nekat Lompat ke Laut Bermodal Jeriken Saat KM Mutiara Terbakar</t>
+          <t>Klasemen Grup A Piala AFF 2026: Indonesia tempati posisi ketiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:35:42 +0700</t>
+          <t>Tue, 04 Aug 2026 23:48:18 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saleh bahkan tidak kebagian pelampung, namun dorongan untuk bertahan hidup membuatnya melompat ke laut dengan berpegangan jeriken</t>
+          <t>Timnas Indonesia menempati posisi ketiga klasemen sementara Grup A Piala AFF 2026 setelah memainkan total tiga ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604619/cerita-saleh-nekat-lompat-ke-laut-bermodal-jeriken-saat-km-mutiara-terbakar</t>
+          <t>https://www.antaranews.com/berita/5680113/klasemen-grup-a-piala-aff-2026-indonesia-tempati-posisi-ketiga</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785834800940_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/timnas-indonesia-dikalahkan-vietnam-di-piala-aff-2833635.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kagetnya Warga Depok Saat Bakar Sampah Ternyata Isi Jasad Tanpa Kaki</t>
+          <t>Menhub tegaskan insiden KMP Mutiara Sentosa jadi evaluasi total</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:30:38 +0700</t>
+          <t>Tue, 04 Aug 2026 23:48:02 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jasad tanpa kaki ditemukan di lahan kosong Pancoran Mas, Depok. Warga awalnya mengira karung berisi sampah, hingga terungkap setelah dibakar.</t>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi menegaskan insiden kebakaran KMP Mutiara Sentosa II di perairan utara ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604618/kagetnya-warga-depok-saat-bakar-sampah-ternyata-isi-jasad-tanpa-kaki</t>
+          <t>https://www.antaranews.com/berita/5680109/menhub-tegaskan-insiden-kmp-mutiara-sentosa-jadi-evaluasi-total</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/23/penemuan-mayat-wanita-duduk-di-melaya_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/07DA5D4C-ACC9-4FDA-A3C3-B8FAE116FE12.jpeg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Drone Houthi Serang Bandara di Saudi, Layanan Penerbangan Disetop Sementara</t>
+          <t>Mendikdasmen: Pembatasan gawai ciptakan lingkungan sekolah yang aman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:28:12 +0700</t>
+          <t>Tue, 04 Aug 2026 22:05:12 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelompok Houthi menyerang Bandara Najran di Arab Saudi. Layanan penerbangan pun dihentikan sementara.</t>
+          <t>Menteri Pendidikan Dasar dan Menengah (Mendikdasmen) Abdul Mu'ti mengatakan Surat Edaran (SE) Nomor 18 Tahun 2026 ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604615/drone-houthi-serang-bandara-di-saudi-layanan-penerbangan-disetop-sementara</t>
+          <t>https://www.antaranews.com/berita/5680024/mendikdasmen-pembatasan-gawai-ciptakan-lingkungan-sekolah-yang-aman</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/10/27/ilustrasi-bendera-arab-saudi-3_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Gernas-Rana-diperkuat-untuk-perlindungan-anak-040826-MRH-7_1.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KPK Temukan Bupati Kuansing Nonaktif Sunat TPP ASN Hingga 50%</t>
+          <t>Kebakaran hutan lindung Gunung Soputan meluas capai 300 hektare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:51:07 +0700</t>
+          <t>Tue, 04 Aug 2026 21:44:20 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KPK mengungkap dugaan korupsi Bupati Kuansing, Suhardiman Amby, termasuk pemotongan TPP ASN dan penerimaan gratifikasi. Tiga tersangka ditetapkan.</t>
+          <t>Kepala Bidang Kedaruratan dan Logistik Badan Penanggulangan Bencana Daerah (BPBD) Kabupaten Minahasa Tenggara, Sulawesi ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604604/kpk-temukan-bupati-kuansing-nonaktif-sunat-tpp-asn-hingga-50</t>
+          <t>https://www.antaranews.com/berita/5679992/kebakaran-hutan-lindung-gunung-soputan-meluas-capai-300-hektare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/01/kpk-tahan-bupati-kuansing-suhardiman-amby-taufiqdetikcom-1782896316779_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001982099_1.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KPK Juga Geledah Kantor Imigrasi Jakpus Terkait Kasus Silmy Karim</t>
+          <t>Indonesia tambah tiga medali pada hari keempat Indonesia Open</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:46:58 +0700</t>
+          <t>Tue, 04 Aug 2026 21:43:26 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penggeledahan itu sendiri telah selesai. KPK belum menjelaskan barang bukti yng disita dan ruang mana saja yang digeledah.</t>
+          <t>Indonesia menambah tiga medali yang terdiri dari satu perak dan dua perunggu pada hari keempat 8th Asian Taekwondo ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604602/kpk-juga-geledah-kantor-imigrasi-jakpus-terkait-kasus-silmy-karim</t>
+          <t>https://www.antaranews.com/berita/5679989/indonesia-tambah-tiga-medali-pada-hari-keempat-indonesia-open</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/silmy-karim-ditahan-kpk-usai-menyerahkan-diri-1780539987753_43.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/adrian-kaiser-raih-perak-asian-taekwondo-indonesia-open-championships-2834348.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anggaran Miliaran untuk Trotoar di Sawangan tapi Setahun Sudah Amblas</t>
+          <t>KPK tahan tiga tersangka kasus dugaan korupsi dalam digitalisasi SPBU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:36:22 +0700</t>
+          <t>Tue, 04 Aug 2026 19:57:47 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trotoar di Jalan Raya Sawangan, Depok, amblas setelah setahun dibangun dengan anggaran Rp 9,7 miliar. Pemkot Depok alokasikan Rp 1 miliar untuk perbaikan.</t>
+          <t>Komisi Pemberantasan Korupsi (KPK) menahan tiga tersangka kasus dugaan korupsi dalam pengadaan digitalisasi stasiun ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604599/anggaran-miliaran-untuk-trotoar-di-sawangan-tapi-setahun-sudah-amblas</t>
+          <t>https://www.antaranews.com/berita/5679803/kpk-tahan-tiga-tersangka-kasus-dugaan-korupsi-dalam-digitalisasi-spbu</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/trotoar-di-jalan-raya-sawangan-depok-jawa-barat-jabar-amblas-1785857768913_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/konpres-penahanan-tersangka-kasus-korupsi-digitalisasi-spbu-pertamina-2834421_1.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nama Tak Biasa Warga +62: Dari Shinchan hingga Nobita</t>
+          <t>KMP Mutiara Sentosa; Keselamatan dan pentingnya memanusiakan penumpang</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:21:18 +0700</t>
+          <t>Tue, 04 Aug 2026 19:55:59 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nama-nama unik di Indonesia, seperti Nobita dan Shinchan, tercatat resmi. Data Dukcapil menunjukkan banyak anak dinamai tokoh anime dan negara.</t>
+          <t>Peristiwa terbakarnya Kapal Motor Penyeberangan (KMP) Mutiara Sentosa 2 rute Surabaya-Makassar, pada Minggu (2/8) ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604590/nama-tak-biasa-warga-62-dari-shinchan-hingga-nobita</t>
+          <t>https://www.antaranews.com/berita/5679800/kmp-mutiara-sentosa-keselamatan-dan-pentingnya-memanusiakan-penumpang</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tokoh-anime-terkenal-dijadikan-nama-anak-di-indonesia-dok-youtube-dukcapil-kemendagri-1785814905415_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/KMPMutiara_copy_1280x853.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mensos Minta Seluruh Unit Kerja Pastikan Sekolah Rakyat Berjalan Optimal</t>
+          <t>Kejagung respons gugatan praperadilan Febrie Adriansyah</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:21:00 +0700</t>
+          <t>Tue, 04 Aug 2026 19:03:18 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Menteri Sosial Gus Ipul menegaskan pentingnya kolaborasi unit kerja untuk program Sekolah Rakyat, mendukung pengentasan kemiskinan dan pendidikan anak.</t>
+          <t>Kejaksaan Agung (Kejagung) merespons soal gugatan praperadilan yang akan diajukan tersangka kasus dugaan tindak pidana ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604589/mensos-minta-seluruh-unit-kerja-pastikan-sekolah-rakyat-berjalan-optimal</t>
+          <t>https://www.antaranews.com/berita/5679675/kejagung-respons-gugatan-praperadilan-febrie-adriansyah</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kemensos-1785856710946_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087161_1.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2 Karyawan Toko Emas di Bogor Gelapkan Perhiasan, Kerugian Rp 635 Juta</t>
+          <t>OJK bentuk Satgas guna siapkan pengaturan dan pengawasan bursa mineral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:17:53 +0700</t>
+          <t>Tue, 04 Aug 2026 18:27:14 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polisi kemudian melakukan penyelidikan terhadap laporan tersebut. Hasilnya, diketahui bahwa pelaku telah melakukan aksinya sejak bulan Mei-Juli 2026.</t>
+          <t>Otoritas Jasa Keuangan (OJK) telah membentuk Satuan Tugas Persiapan Pengaturan dan Pengawasan Bursa Mineral dan ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604585/2-karyawan-toko-emas-di-bogor-gelapkan-perhiasan-kerugian-rp-635-juta</t>
+          <t>https://www.antaranews.com/berita/5679619/ojk-bentuk-satgas-guna-siapkan-pengaturan-dan-pengawasan-bursa-mineral</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2-karyawan-toko-emas-di-bogor-terbukti-melakukan-penggelapan-data-penjualan-rizkydetikcom-1785856635377_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-18.20.41.jpeg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ada yang Gondrong tapi Bukan Rambut, Nama Kelurahan di Tangerang</t>
+          <t>Latihan musik Pagelaran Sabang Merauke</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:14:34 +0700</t>
+          <t>Tue, 04 Aug 2026 18:18:17 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kelurahan Gondrong di Cipondoh, Tangerang, memiliki beragam kisah asal-usul nama. Dari sosok berambut gondrong hingga pohon jambu, semua menyimpan cerita unik.</t>
+          <t>Penampilan Yura Yunita (kiri) bersama vokalis Padi Reborn Andi Fadly Arifuddin (kanan) pada latihan musik Pagelaran ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604582/ada-yang-gondrong-tapi-bukan-rambut-nama-kelurahan-di-tangerang</t>
+          <t>https://www.antaranews.com/foto/5679585/latihan-musik-pagelaran-sabang-merauke</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kelurahan-gondrong-adhfardetikcom-1785825763342_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/latihan-musik-pagelaran-sabang-merauke-040826-dr-04.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ada Proyek Galian, Jalan Layang Antasari Arah Cipete Macet Malam Ini</t>
+          <t>Kemenkes: Anak harus dilindungi dari promosi vape di medsos</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:11:41 +0700</t>
+          <t>Tue, 04 Aug 2026 18:14:32 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kemacetan terjadi di Jalan Layang Antasari, Jakarta Selatan, akibat pengerjaan galian. Polisi lakukan rekayasa lalu lintas untuk mengurangi kepadatan.</t>
+          <t>Kementerian Kesehatan menegaskan bahwa anak harus dilindungi dari paparan dan promosi produk tembakau, baik ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604578/ada-proyek-galian-jalan-layang-antasari-arah-cipete-macet-malam-ini</t>
+          <t>https://www.antaranews.com/berita/5679575/kemenkes-anak-harus-dilindungi-dari-promosi-vape-di-medsos</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kemacetan-di-turunan-jlnt-antasari-arah-cipete-karena-ada-galian-xtmc-polda-metro-jaya-1785856259312_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/10/usulan-pelarangan-rokok-elektronik-di-ruu-narkotika-2768977.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Petani Tembakau di Nganjuk Berbagi Air Sumur Hadapi Kemarau Panjang</t>
+          <t>OJK: Arus dana asing berbalik positif "net buy" Rp1,62 triliun di Juli</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:00:40 +0700</t>
+          <t>Tue, 04 Aug 2026 17:36:42 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petani tembakau di Nganjuk berbagi pasokan air sumur untuk menjaga tanaman tetap tumbuh saat kemarau. Upaya ini dilakukan agar produktivitas tetap terjaga.</t>
+          <t>Otoritas Jasa Keuangan (OJK) mencatat aliran dana investor asing berbalik positif dengan membukukan net buy senilai ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.detik.com/foto-news/d-8603806/petani-tembakau-di-nganjuk-berbagi-air-sumur-hadapi-kemarau-panjang</t>
+          <t>https://www.antaranews.com/berita/5679520/ojk-arus-dana-asing-berbalik-positif-net-buy-rp162-triliun-di-juli</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/petani-tembakau-di-nganjuk-berbagi-air-sumur-hadapi-kemarau-panjang-1785829212848_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/hasan.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KPK Terbitkan 3 Sprindik Baru Kasus Suap Eks Kepala Kantor Pajak Banjarmasin</t>
+          <t>Jaksa Agung berhentikan sementara status jaksa Febrie Adriansyah</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:00:32 +0700</t>
+          <t>Tue, 04 Aug 2026 17:28:52 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KPK mengatakan ada tiga surat perintah penyidikan (sprindik) baru yang dikeluarkan di kasus tersebut.</t>
+          <t>Jaksa Agung RI ST Burhanuddin memberhentikan sementara status jaksa dari mantan Jaksa Agung Muda Bidang Tindak Pidana ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604569/kpk-terbitkan-3-sprindik-baru-kasus-suap-eks-kepala-kantor-pajak-banjarmasin</t>
+          <t>https://www.antaranews.com/berita/5679508/jaksa-agung-berhentikan-sementara-status-jaksa-febrie-adriansyah</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/13/plt-direktur-penyidikan-kpk-achmad-taufik-husein-1776092670324_43.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087161_1.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ngeri! 3 Sanca Besar 'Bersarang' di Plafon Rumah Warga Jaksel</t>
+          <t>Tiga korban TPPO di Libya alami eksploitasi ekonomi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:36:09 +0700</t>
+          <t>Tue, 04 Aug 2026 16:17:19 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tiga ular sanca besar dievakuasi dari plafon rumah warga di Jagakarsa, Jakarta Selatan. Proses evakuasi melibatkan petugas damkar.</t>
+          <t>Ketiga korban Tindak Pidana Perdagangan Orang (TPPO) berinisial NAR (21), SS (45), dan NKR (39) mengalami ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604549/ngeri-3-sanca-besar-bersarang-di-plafon-rumah-warga-jaksel</t>
+          <t>https://www.antaranews.com/berita/5679340/tiga-korban-tppo-di-libya-alami-eksploitasi-ekonomi</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tiga-ekor-ular-sanca-besar-dievakuasi-dari-plafon-rumah-warga-di-jagakarsa-jakarta-selatan-1785854115714_169.png?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/tiga-korban-tppo-libya-dipulangkan-ke-indonesia-2834140_1.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KPK Geledah Kantor Imigrasi Jaksel Terkait Kasus Eks Wamen Silmy Karim</t>
+          <t>PM Thailand: ASEAN kini di persimpangan jalan hadapi tantangan global</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:34:10 +0700</t>
+          <t>Tue, 04 Aug 2026 16:11:35 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Penggeledahan dilakukan terkait kasus dugaan pemerasan izin tinggal Warga Negara Asing (WNA) yang menjerat mantan Wamen Imipas Silmy Karim.</t>
+          <t>Perdana Menteri (PM) Thailand Anutin Charnvirakul mengatakan ASEAN kini berada di persimpangan jalan, dimana pilihan ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604547/kpk-geledah-kantor-imigrasi-jaksel-terkait-kasus-eks-wamen-silmy-karim</t>
+          <t>https://www.antaranews.com/berita/5679317/pm-thailand-asean-kini-di-persimpangan-jalan-hadapi-tantangan-global</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/28/69bae68b-1d8e-430c-b130-0bc9367b2f65_169.jpg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/kunjungan-pm-thailand-ke-sekretariat-asean-2833977_1.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ulah Oknum Ubah Proyek Waduk di Jaktim Malah Jadi Lokasi Sampah Numpuk</t>
+          <t>Penjualan mobil naik, Menkeu yakin daya beli domestik tetap terjaga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:09:30 +0700</t>
+          <t>Tue, 04 Aug 2026 13:45:23 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lahan itu tidak boleh dipakai sebagai TPS lagi. Lahan akan dikembalikan sesuai dengan peruntukannya sebagai waduk.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pertumbuhan penjualan mobil menjadi salah satu indikator yang ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604530/ulah-oknum-ubah-proyek-waduk-di-jaktim-malah-jadi-lokasi-sampah-numpuk</t>
+          <t>https://www.antaranews.com/berita/5679033/penjualan-mobil-naik-menkeu-yakin-daya-beli-domestik-tetap-terjaga</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/damkar-masih-menyemprotkan-air-ke-tempat-pembuangan-sampah-tps-liar-di-kramat-jati-jakarta-timur-api-terus-disemprotkan-agar-a-1785749215344_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.50.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Satgas PRR Kawal Usulan Normalisasi Sungai Tamiang Cegah Banjir Berulang</t>
+          <t>Ada 2 bibit siklon tropis, BMKG: Waspada ombak setinggi 4 meter di RI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:08:05 +0700</t>
+          <t>Tue, 04 Aug 2026 12:09:44 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Satgas PRR Pascabencana Sumatera akan percepat normalisasi Sungai Tamiang untuk mencegah banjir. Langkah ini penting untuk lindungi infrastruktur dan masyarakat</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi kemunculan dua bibit siklon tropis sekaligus di wilayah ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604525/satgas-prr-kawal-usulan-normalisasi-sungai-tamiang-cegah-banjir-berulang</t>
+          <t>https://www.antaranews.com/berita/5678879/ada-2-bibit-siklon-tropis-bmkg-waspada-ombak-setinggi-4-meter-di-ri</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/satgas-prr-1785852342942_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20250609_135328.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mayat Mutilasi di Depok Diautopsi ke RS Polri, Identitas Belum Diketahui</t>
+          <t>Korban tewas gempa Venezuela terus bertambah jadi 6.100 orang</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:05:44 +0700</t>
+          <t>Tue, 04 Aug 2026 12:00:56 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Made menjelaskan potongan tubuh korban tidak berada di lokasi. Saat ini polisi masih melakukan penyelidikan dengan pemeriksaan dokter forensik RS Polri.</t>
+          <t>Jumlah korban tewas akibat gempa kembar dahsyat yang mengguncang Venezuela pada 24 Juni 2026, terus bertambah ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604519/mayat-mutilasi-di-depok-diautopsi-ke-rs-polri-identitas-belum-diketahui</t>
+          <t>https://www.antaranews.com/berita/5678865/korban-tewas-gempa-venezuela-terus-bertambah-jadi-6100-orang</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/23/penemuan-mayat-perempuan-duduk-di-melaya_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_d4a34a165f13a0667255577d3cfac46f.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Top News</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Saat Netanyahu Sebut Gaza Sama dengan Korut</t>
+          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:01:48 +0700</t>
+          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Perdana Menteri (PM) Israel Benjamin Netanyahu kembali bikin pernyataan kontroversial. Dia menyamakan Jalur Gaza di Palestina dengan Korea Utara (Korut).</t>
+          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604514/saat-netanyahu-sebut-gaza-sama-dengan-korut</t>
+          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/29/2288038725-1785305349518_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506_1.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Ekonomi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DPD RI Raih Penghargaan Opini WTP ke-20 Berturut-turut dari BPK</t>
+          <t>Tiket GIIAS 2026: Daftar Harga dan cara belinya</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:59:59 +0700</t>
+          <t>Tue, 04 Aug 2026 16:29:46 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DPD RI meraih Opini WTP ke-20 dari BPK RI, mencerminkan tata kelola keuangan yang transparan dan akuntabel. Komitmen untuk perbaikan berkelanjutan ditekankan.</t>
+          <t>Pameran GAIKINDO Indonesia International Auto Show (GIIAS) 2026 resmi digelar sejak 30 Juli hingga 9 Agustus 2026. ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604511/dpd-ri-raih-penghargaan-opini-wtp-ke-20-berturut-turut-dari-bpk</t>
+          <t>https://otomotif.antaranews.com/berita/5679373/tiket-giias-2026-daftar-harga-dan-cara-belinya</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/dpd-raih-opini-wtp-dari-bpk-1785851361404_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/WhatsApp-Image-2026-07-30-at-21.31.47.jpeg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Terobosan BPA Kejagung, Kini Punya Sistem AI Awasi Proses Pemulihan Aset</t>
+          <t>Kenapa nyamuk lebih banyak saat musim kemarau? Ini penyebabnya</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:59:40 +0700</t>
+          <t>Tue, 04 Aug 2026 16:51:54 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BPA Kejagung adakan FGD untuk terapkan AI dalam pemulihan aset. Fokus pada manajemen risiko dan transformasi penegakan hukum menuju Visi 2035.</t>
+          <t>Jumlah nyamuk yang meningkat saat musim kemarau kerap dirasakan masyarakat, terutama ketika cuaca panas dan kering ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604513/terobosan-bpa-kejagung-kini-punya-sistem-ai-awasi-proses-pemulihan-aset</t>
+          <t>https://www.antaranews.com/berita/5679429/kenapa-nyamuk-lebih-banyak-saat-musim-kemarau-ini-penyebabnya</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kepala-bpa-kejaksaan-ri-patris-yusrian-jaya-1785852815388_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/10/DBD.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mayat Mutilasi dalam Karung di Depok Dikira Sampah, Sempat Dibakar Warga</t>
+          <t>10 Cara move on setelah putus cinta yang sehat dan efektif</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:36:14 +0700</t>
+          <t>Tue, 04 Aug 2026 16:33:16 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jasad termutilasi di Depok, terbungkus karung. Mayat korban sempat dikira sampah oleh warga.</t>
+          <t>Putus cinta sering kali menjadi pengalaman emosional yang tidak mudah dilalui. Rasa sedih, kecewa, marah, hingga ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604492/mayat-mutilasi-dalam-karung-di-depok-dikira-sampah-sempat-dibakar-warga</t>
+          <t>https://www.antaranews.com/berita/5679381/10-cara-move-on-setelah-putus-cinta-yang-sehat-dan-efektif</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/9def71f1-1c47-4d30-8a60-a8c3521d9475_169.jpg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2014/06/20140624patah_hati.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hujan Deras Guyur Bogor, 1 Pohon Tumbang Timpa Atap Rumah Warga</t>
+          <t>10 Kesalahan yang sebaiknya Anda hindari setelah putus cinta</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:35:19 +0700</t>
+          <t>Tue, 04 Aug 2026 16:04:43 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hujan deras melanda kawasan Desa Cijayanti, Kecamatan Babakan Madang, Bogor, Jawa Barat. Akibatnya, sebuah pohon tumbang kemudian menimpa rumah warga.</t>
+          <t>Putus cinta merupakan pengalaman emosional yang bisa dirasakan siapa saja. Berakhirnya sebuah hubungan sering kali ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604491/hujan-deras-guyur-bogor-1-pohon-tumbang-timpa-atap-rumah-warga</t>
+          <t>https://www.antaranews.com/berita/5679292/10-kesalahan-yang-sebaiknya-anda-hindari-setelah-putus-cinta</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pohon-tumbang-timpa-rumah-warga-di-bogor-dokistimewa-1785850485303_43.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/02/03/patah.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bapenda Jabar Populerkan Inovasi KiosK Samsat di Rakornas Dukcapil</t>
+          <t>Tanda-tanda Anda belum benar-benar move on dari mantan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:29:33 +0700</t>
+          <t>Tue, 04 Aug 2026 15:54:35 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bapenda Jabar luncurkan KiosK Samsat untuk pembayaran pajak kendaraan secara digital. Inovasi ini memanfaatkan data kependudukan untuk efisiensi layanan.</t>
+          <t>Putus cinta bukan hanya mengakhiri sebuah hubungan, tetapi juga memulai proses penyesuaian emosional yang tidak selalu ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604482/bapenda-jabar-populerkan-inovasi-kiosk-samsat-di-rakornas-dukcapil</t>
+          <t>https://www.antaranews.com/berita/5679256/tanda-tanda-anda-belum-benar-benar-move-on-dari-mantan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ditjen-dukcapil-1785850075424_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/09/shutterstock_362866388.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
@@ -1394,28 +1394,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lantik 67 Pejabat Kemensos, Gus Ipul Ingatkan Jaga Integritas dan Amanah</t>
+          <t>Cerita Saleh Nekat Lompat ke Laut Bermodal Jeriken Saat KM Mutiara Terbakar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:27:59 +0700</t>
+          <t>Tue, 04 Aug 2026 23:35:42 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Menteri Sosial Gus Ipul melantik 67 pejabat fungsional, menekankan pentingnya data akurat dan integritas untuk penyaluran bantuan sosial yang tepat sasaran.</t>
+          <t>Saleh bahkan tidak kebagian pelampung, namun dorongan untuk bertahan hidup membuatnya melompat ke laut dengan berpegangan jeriken</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604449/lantik-67-pejabat-kemensos-gus-ipul-ingatkan-jaga-integritas-dan-amanah</t>
+          <t>https://news.detik.com/berita/d-8604619/cerita-saleh-nekat-lompat-ke-laut-bermodal-jeriken-saat-km-mutiara-terbakar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kemensos-1785846538698_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/km-mutiara-sentosa-2-terbakar-1785834800940_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1427,33 +1427,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tambak Modern Udang Vaname Hadirkan Solusi Budi Daya Efisien</t>
+          <t>Kagetnya Warga Depok Saat Bakar Sampah Ternyata Isi Jasad Tanpa Kaki</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:00:40 +0700</t>
+          <t>Tue, 04 Aug 2026 23:30:38 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Budi daya udang vaname dengan sistem tertutup dikembangkan di kawasan industri Semarang. Teknologi ini menghemat air juga meningkatkan produktivitas tambak.</t>
+          <t>Jasad tanpa kaki ditemukan di lahan kosong Pancoran Mas, Depok. Warga awalnya mengira karung berisi sampah, hingga terungkap setelah dibakar.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603831/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien</t>
+          <t>https://news.detik.com/berita/d-8604618/kagetnya-warga-depok-saat-bakar-sampah-ternyata-isi-jasad-tanpa-kaki</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien-1785830418949_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/23/penemuan-mayat-wanita-duduk-di-melaya_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1465,33 +1465,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Harga Minyak Langsung Turun Usai AS-Iran Setop Serangan</t>
+          <t>Drone Houthi Serang Bandara di Saudi, Layanan Penerbangan Disetop Sementara</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:35:07 +0700</t>
+          <t>Tue, 04 Aug 2026 23:28:12 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Harga minyak dunia turun nyaris 4% pada Selasa (4/8/2026) dan menyentuh level terendah dalam tiga pekan.</t>
+          <t>Kelompok Houthi menyerang Bandara Najran di Arab Saudi. Layanan penerbangan pun dihentikan sementara.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604597/harga-minyak-langsung-turun-usai-as-iran-setop-serangan</t>
+          <t>https://news.detik.com/internasional/d-8604615/drone-houthi-serang-bandara-di-saudi-layanan-penerbangan-disetop-sementara</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/24/harga-minyak-dunia-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/10/27/ilustrasi-bendera-arab-saudi-3_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1503,33 +1503,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>604.923 Rekening Terkait Scam Diblokir!</t>
+          <t>KPK Temukan Bupati Kuansing Nonaktif Sunat TPP ASN Hingga 50%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:11:04 +0700</t>
+          <t>Tue, 04 Aug 2026 22:51:07 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OJK bersama Indonesia Anti-Scam Center (IASC) terus memperkuat upaya pemberantasan kasus keuangan ilegal dan penipuan di sektor jasa keuangan.</t>
+          <t>KPK mengungkap dugaan korupsi Bupati Kuansing, Suhardiman Amby, termasuk pemotongan TPP ASN dan penerimaan gratifikasi. Tiga tersangka ditetapkan.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604576/604-923-rekening-terkait-scam-diblokir</t>
+          <t>https://news.detik.com/berita/d-8604604/kpk-temukan-bupati-kuansing-nonaktif-sunat-tpp-asn-hingga-50</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/24/ilustrasi-telepon-scam-atau-penipuan-1766569797414_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/01/kpk-tahan-bupati-kuansing-suhardiman-amby-taufiqdetikcom-1782896316779_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1541,33 +1541,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Warga RI Doyan Pakai Paylater, Ini Buktinya</t>
+          <t>KPK Juga Geledah Kantor Imigrasi Jakpus Terkait Kasus Silmy Karim</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:14:02 +0700</t>
+          <t>Tue, 04 Aug 2026 22:46:58 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Penggunaan layanan Buy Now Pay Later (BNPL) atau paylater masih meningkat.</t>
+          <t>Penggeledahan itu sendiri telah selesai. KPK belum menjelaskan barang bukti yng disita dan ruang mana saja yang digeledah.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604532/warga-ri-doyan-pakai-paylater-ini-buktinya</t>
+          <t>https://news.detik.com/berita/d-8604602/kpk-juga-geledah-kantor-imigrasi-jakpus-terkait-kasus-silmy-karim</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/10/27/ilustrasi-paylater_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/silmy-karim-ditahan-kpk-usai-menyerahkan-diri-1780539987753_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1579,33 +1579,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Izin Tambang Berakhir 2041, Freeport Ajukan Perpanjangan ke Pemerintah</t>
+          <t>Anggaran Miliaran untuk Trotoar di Sawangan tapi Setahun Sudah Amblas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:42:26 +0700</t>
+          <t>Tue, 04 Aug 2026 22:36:22 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Freeport Indonesia telah mengajukan permohonan perpanjangan IUPK untuk melanjutkan operasi tambang Grasberg setelah izin yang berlaku saat ini berakhir 2041.</t>
+          <t>Trotoar di Jalan Raya Sawangan, Depok, amblas setelah setahun dibangun dengan anggaran Rp 9,7 miliar. Pemkot Depok alokasikan Rp 1 miliar untuk perbaikan.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604497/izin-tambang-berakhir-2041-freeport-ajukan-perpanjangan-ke-pemerintah</t>
+          <t>https://news.detik.com/berita/d-8604599/anggaran-miliaran-untuk-trotoar-di-sawangan-tapi-setahun-sudah-amblas</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/11/mengintip-tambang-sedalam-17-km-di-perut-bumi-papua-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/trotoar-di-jalan-raya-sawangan-depok-jawa-barat-jabar-amblas-1785857768913_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1617,33 +1617,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mendes: Kopdes Merah Putih Penggerak Ekonomi Desa</t>
+          <t>Nama Tak Biasa Warga +62: Dari Shinchan hingga Nobita</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:19:08 +0700</t>
+          <t>Tue, 04 Aug 2026 22:21:18 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pemerintah menargetkan pembangunan 30.000 Koperasi Desa/Kelurahan Merah Putih (KDKMP) pada tahun ini.</t>
+          <t>Nama-nama unik di Indonesia, seperti Nobita dan Shinchan, tercatat resmi. Data Dukcapil menunjukkan banyak anak dinamai tokoh anime dan negara.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604472/mendes-kopdes-merah-putih-penggerak-ekonomi-desa</t>
+          <t>https://news.detik.com/berita/d-8604590/nama-tak-biasa-warga-62-dari-shinchan-hingga-nobita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menteri-desa-dan-pembangunan-daerah-tertinggal-pdt-1785853253837_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tokoh-anime-terkenal-dijadikan-nama-anak-di-indonesia-dok-youtube-dukcapil-kemendagri-1785814905415_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1655,33 +1655,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bursa Mineral Meluncur 1 Januari 2027, Ini Bocoran dari OJK</t>
+          <t>Mensos Minta Seluruh Unit Kerja Pastikan Sekolah Rakyat Berjalan Optimal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:00:15 +0700</t>
+          <t>Tue, 04 Aug 2026 22:21:00 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OJK buka-bukaan soal Bursa Mineral bakal meluncur 1 Januari 2027.</t>
+          <t>Menteri Sosial Gus Ipul menegaskan pentingnya kolaborasi unit kerja untuk program Sekolah Rakyat, mendukung pengentasan kemiskinan dan pendidikan anak.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604418/bursa-mineral-meluncur-1-januari-2027-ini-bocoran-dari-ojk</t>
+          <t>https://news.detik.com/berita/d-8604589/mensos-minta-seluruh-unit-kerja-pastikan-sekolah-rakyat-berjalan-optimal</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/18/friderica-widyasari-dewi-1781765532562_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kemensos-1785856710946_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1693,33 +1693,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bea Cukai Amankan 3 Warga Negara Malaysia Bawa Narkotika</t>
+          <t>2 Karyawan Toko Emas di Bogor Gelapkan Perhiasan, Kerugian Rp 635 Juta</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:51:37 +0700</t>
+          <t>Tue, 04 Aug 2026 22:17:53 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Petugas Bea Cukai Bandara Soekarno-Hatta mengamankan ketamin dari 3 wanita penumpang pesawat diduga Warga Negara Malaysia.</t>
+          <t>Polisi kemudian melakukan penyelidikan terhadap laporan tersebut. Hasilnya, diketahui bahwa pelaku telah melakukan aksinya sejak bulan Mei-Juli 2026.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/ekonomi-bisnis/d-8604433/bea-cukai-amankan-3-warga-negara-malaysia-bawa-narkotika</t>
+          <t>https://news.detik.com/berita/d-8604585/2-karyawan-toko-emas-di-bogor-gelapkan-perhiasan-kerugian-rp-635-juta</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/ed32a201-0b77-4c2b-a370-0636977c2075_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2-karyawan-toko-emas-di-bogor-terbukti-melakukan-penggelapan-data-penjualan-rizkydetikcom-1785856635377_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1731,33 +1731,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Industri Kripto RI Terus Melonjak, Transaksinya Rp 28 T per Juni 2026</t>
+          <t>Ada yang Gondrong tapi Bukan Rambut, Nama Kelurahan di Tangerang</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:30:08 +0700</t>
+          <t>Tue, 04 Aug 2026 22:14:34 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aset kripto terus diminati di Indonesia, dengan 22,69 juta akun dan transaksi mencapai Rp 28,58 triliun pada Juni 2026. OJK tetap awasi perlindungan konsumen.</t>
+          <t>Kelurahan Gondrong di Cipondoh, Tangerang, memiliki beragam kisah asal-usul nama. Dari sosok berambut gondrong hingga pohon jambu, semua menyimpan cerita unik.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/fintech/d-8604314/industri-kripto-ri-terus-melonjak-transaksinya-rp-28-t-per-juni-2026</t>
+          <t>https://news.detik.com/berita/d-8604582/ada-yang-gondrong-tapi-bukan-rambut-nama-kelurahan-di-tangerang</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/05/27/ilustrasi-bitcoin_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kelurahan-gondrong-adhfardetikcom-1785825763342_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1769,33 +1769,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sektor Jasa Keuangan Tetap Stabil, Kredit Perbankan Tumbuh 12,67%</t>
+          <t>Ada Proyek Galian, Jalan Layang Antasari Arah Cipete Macet Malam Ini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:19:21 +0700</t>
+          <t>Tue, 04 Aug 2026 22:11:41 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OJK menyatakan sektor jasa keuangan tetap stabil di tengah ketidakpastian global. Pertumbuhan kredit dan permodalan perbankan menunjukkan kinerja positif.</t>
+          <t>Kemacetan terjadi di Jalan Layang Antasari, Jakarta Selatan, akibat pengerjaan galian. Polisi lakukan rekayasa lalu lintas untuk mengurangi kepadatan.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604398/sektor-jasa-keuangan-tetap-stabil-kredit-perbankan-tumbuh-12-67</t>
+          <t>https://news.detik.com/berita/d-8604578/ada-proyek-galian-jalan-layang-antasari-arah-cipete-macet-malam-ini</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ojk-1785845945964_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kemacetan-di-turunan-jlnt-antasari-arah-cipete-karena-ada-galian-xtmc-polda-metro-jaya-1785856259312_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1807,33 +1807,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OJK Catat Total Aset Industri Asuransi RI Capai Rp Rp 1.184 triliun</t>
+          <t>Petani Tembakau di Nganjuk Berbagi Air Sumur Hadapi Kemarau Panjang</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:07:39 +0700</t>
+          <t>Tue, 04 Aug 2026 22:00:40 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OJK melaporkan total aset industri asuransi RI mencapai Rp 1.184 triliun per Juni 2026, dengan pertumbuhan stabil meski beberapa sektor mengalami kontraksi.</t>
+          <t>Petani tembakau di Nganjuk berbagi pasokan air sumur untuk menjaga tanaman tetap tumbuh saat kemarau. Upaya ini dilakukan agar produktivitas tetap terjaga.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604257/ojk-catat-total-aset-industri-asuransi-ri-capai-rp-rp-1-184-triliun</t>
+          <t>https://news.detik.com/foto-news/d-8603806/petani-tembakau-di-nganjuk-berbagi-air-sumur-hadapi-kemarau-panjang</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/14/ilustrasi-asuransi-kesehatan-1778737684617_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/petani-tembakau-di-nganjuk-berbagi-air-sumur-hadapi-kemarau-panjang-1785829212848_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1845,33 +1845,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kredit Perbankan Tembus Rp 9.081 Triliun, Tumbuh 12,67%</t>
+          <t>KPK Terbitkan 3 Sprindik Baru Kasus Suap Eks Kepala Kantor Pajak Banjarmasin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:30:05 +0700</t>
+          <t>Tue, 04 Aug 2026 22:00:32 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kredit perbankan pada bulan Juni 2026 tumbuh 12,67% menjadi Rp 9.081 triliun.</t>
+          <t>KPK mengatakan ada tiga surat perintah penyidikan (sprindik) baru yang dikeluarkan di kasus tersebut.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604271/kredit-perbankan-tembus-rp-9-081-triliun-tumbuh-12-67</t>
+          <t>https://news.detik.com/berita/d-8604569/kpk-terbitkan-3-sprindik-baru-kasus-suap-eks-kepala-kantor-pajak-banjarmasin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/02/10/uang-tunai-rupiah-4_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/13/plt-direktur-penyidikan-kpk-achmad-taufik-husein-1776092670324_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1883,33 +1883,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Utang Pinjol Warga RI Tembus Rp 105 Triliun!</t>
+          <t>Ngeri! 3 Sanca Besar 'Bersarang' di Plafon Rumah Warga Jaksel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:25:04 +0700</t>
+          <t>Tue, 04 Aug 2026 21:36:09 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OJK mencatat nilai pembiayaan pinjol mencapai Rp 105,14 triliun, atau tumbuh 25,88% secara tahunan pada bulan Juni 2026.</t>
+          <t>Tiga ular sanca besar dievakuasi dari plafon rumah warga di Jagakarsa, Jakarta Selatan. Proses evakuasi melibatkan petugas damkar.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604291/utang-pinjol-warga-ri-tembus-rp-105-triliun</t>
+          <t>https://news.detik.com/berita/d-8604549/ngeri-3-sanca-besar-bersarang-di-plafon-rumah-warga-jaksel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/02/04/b3a5ed4c-3141-4fed-a3ff-2bfc948f1b01_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tiga-ekor-ular-sanca-besar-dievakuasi-dari-plafon-rumah-warga-di-jagakarsa-jakarta-selatan-1785854115714_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1921,33 +1921,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BRILink Agen Permudah Perajin &amp;amp; Petani Alor Akses Layanan Perbankan</t>
+          <t>KPK Geledah Kantor Imigrasi Jaksel Terkait Kasus Eks Wamen Silmy Karim</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:13:26 +0700</t>
+          <t>Tue, 04 Aug 2026 21:34:10 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kepulauan Alor, NTT, menawarkan keindahan dan tantangan. Kehadiran BRILink Agen mempermudah akses keuangan, mendukung kemandirian ekonomi masyarakat setempat.</t>
+          <t>Penggeledahan dilakukan terkait kasus dugaan pemerasan izin tinggal Warga Negara Asing (WNA) yang menjerat mantan Wamen Imipas Silmy Karim.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604269/brilink-agen-permudah-perajin-petani-alor-akses-layanan-perbankan</t>
+          <t>https://news.detik.com/berita/d-8604547/kpk-geledah-kantor-imigrasi-jaksel-terkait-kasus-eks-wamen-silmy-karim</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/12/05/4acc195a-ed44-44c8-88b3-7f629b73d63b_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/12/28/69bae68b-1d8e-430c-b130-0bc9367b2f65_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1959,33 +1959,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>36 Ribu Rekening Judi Online Diblokir!</t>
+          <t>Ulah Oknum Ubah Proyek Waduk di Jaktim Malah Jadi Lokasi Sampah Numpuk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:00:20 +0700</t>
+          <t>Tue, 04 Aug 2026 21:09:30 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) sebut 36.735 rekening terkait judi online diblokir.</t>
+          <t>Lahan itu tidak boleh dipakai sebagai TPS lagi. Lahan akan dikembalikan sesuai dengan peruntukannya sebagai waduk.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604245/36-ribu-rekening-judi-online-diblokir</t>
+          <t>https://news.detik.com/berita/d-8604530/ulah-oknum-ubah-proyek-waduk-di-jaktim-malah-jadi-lokasi-sampah-numpuk</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/27/ilustrasi-judi-online-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/damkar-masih-menyemprotkan-air-ke-tempat-pembuangan-sampah-tps-liar-di-kramat-jati-jakarta-timur-api-terus-disemprotkan-agar-a-1785749215344_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1997,33 +1997,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WIKA Sukses Catatkan Kontrak Baru Rp 6,91 Triliun hingga Juni 2026</t>
+          <t>Satgas PRR Kawal Usulan Normalisasi Sungai Tamiang Cegah Banjir Berulang</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:45:19 +0700</t>
+          <t>Tue, 04 Aug 2026 21:08:05 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WIKA raih kontrak baru Rp 6,91 triliun hingga Juni 2026, didorong proyek strategis di konstruksi dan infrastruktur. Optimis dukung pembangunan nasional.</t>
+          <t>Satgas PRR Pascabencana Sumatera akan percepat normalisasi Sungai Tamiang untuk mencegah banjir. Langkah ini penting untuk lindungi infrastruktur dan masyarakat</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/infrastruktur/d-8604234/wika-sukses-catatkan-kontrak-baru-rp-6-91-triliun-hingga-juni-2026</t>
+          <t>https://news.detik.com/berita/d-8604525/satgas-prr-kawal-usulan-normalisasi-sungai-tamiang-cegah-banjir-berulang</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/wika-sukses-catatkan-kontrak-baru-rp-691-triliun-hingga-juni-2026-1785840143413_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/satgas-prr-1785852342942_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2035,33 +2035,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gagal Dapat Diskon Moge Harley Davidson, Purbaya: Yah, Lemes Gue!</t>
+          <t>Mayat Mutilasi di Depok Diautopsi ke RS Polri, Identitas Belum Diketahui</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:38:14 +0700</t>
+          <t>Tue, 04 Aug 2026 21:05:44 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa bercerita dirinya gagal membeli motor Harley Davidson dengan harga diskon karena dianggap gratifikasi.</t>
+          <t>Made menjelaskan potongan tubuh korban tidak berada di lokasi. Saat ini polisi masih melakukan penyelidikan dengan pemeriksaan dokter forensik RS Polri.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604225/gagal-dapat-diskon-moge-harley-davidson-purbaya-yah-lemes-gue</t>
+          <t>https://news.detik.com/berita/d-8604519/mayat-mutilasi-di-depok-diautopsi-ke-rs-polri-identitas-belum-diketahui</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menkeu-purbaya-jajal-moge-harley-davidson-1785839816386_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/23/penemuan-mayat-perempuan-duduk-di-melaya_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2073,33 +2073,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bos OJK Blak-blakan Kondisi Sektor Keuangan RI di Tengah Gejolak Global</t>
+          <t>Saat Netanyahu Sebut Gaza Sama dengan Korut</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:16:02 +0700</t>
+          <t>Tue, 04 Aug 2026 21:01:48 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi buka-bukaan kondisi sektor keuangan di tengah gonjang-ganjing global.</t>
+          <t>Perdana Menteri (PM) Israel Benjamin Netanyahu kembali bikin pernyataan kontroversial. Dia menyamakan Jalur Gaza di Palestina dengan Korea Utara (Korut).</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604173/bos-ojk-blak-blakan-kondisi-sektor-keuangan-ri-di-tengah-gejolak-global</t>
+          <t>https://news.detik.com/internasional/d-8604514/saat-netanyahu-sebut-gaza-sama-dengan-korut</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/frederica-widyasari-dewi-1785765447950_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/29/2288038725-1785305349518_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2111,33 +2111,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Prabowo Minta Harga BBM Subsidi Tak Naik</t>
+          <t>DPD RI Raih Penghargaan Opini WTP ke-20 Berturut-turut dari BPK</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:11:28 +0700</t>
+          <t>Tue, 04 Aug 2026 20:59:59 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Menteri ESDM Bahlil mengungkapkan kebijakan harga BBM bersubsidi tetap dipertahankan meski harga minyak dunia naik.</t>
+          <t>DPD RI meraih Opini WTP ke-20 dari BPK RI, mencerminkan tata kelola keuangan yang transparan dan akuntabel. Komitmen untuk perbaikan berkelanjutan ditekankan.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604168/prabowo-minta-harga-bbm-subsidi-tak-naik</t>
+          <t>https://news.detik.com/berita/d-8604511/dpd-ri-raih-penghargaan-opini-wtp-ke-20-berturut-turut-dari-bpk</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/01/presiden-prabowo-subianto-dok-youtube-setpres-1782871893408_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/dpd-raih-opini-wtp-dari-bpk-1785851361404_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2149,33 +2149,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OJK Kasih Denda Rp 91 Miliar ke 104 Pelaku Pasar Modal</t>
+          <t>Terobosan BPA Kejagung, Kini Punya Sistem AI Awasi Proses Pemulihan Aset</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:03:56 +0700</t>
+          <t>Tue, 04 Aug 2026 20:59:40 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OJK menjatuhkan denda Rp 91 miliar kepada 104 pelaku pasar modal untuk penegakan ketentuan dan perlindungan konsumen. Sanksi administratif juga diterapkan.</t>
+          <t>BPA Kejagung adakan FGD untuk terapkan AI dalam pemulihan aset. Fokus pada manajemen risiko dan transformasi penegakan hukum menuju Visi 2035.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604151/ojk-kasih-denda-rp-91-miliar-ke-104-pelaku-pasar-modal</t>
+          <t>https://news.detik.com/berita/d-8604513/terobosan-bpa-kejagung-kini-punya-sistem-ai-awasi-proses-pemulihan-aset</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/12/30/59e6cb2c-4043-4878-a12b-89f4ab9e5a8e_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kepala-bpa-kejaksaan-ri-patris-yusrian-jaya-1785852815388_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2187,33 +2187,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pelatihan Tata Rias Bekali Siswa Berkebutuhan Khusus Menuju Dunia Kerja</t>
+          <t>Mayat Mutilasi dalam Karung di Depok Dikira Sampah, Sempat Dibakar Warga</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:00:33 +0700</t>
+          <t>Tue, 04 Aug 2026 20:36:14 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pelatihan tata rias menjadi salah satu upaya memperluas kesempatan kerja bagi siswa berkebutuhan khusus. Peserta belajar keterampilan yang bernilai ekonomi.</t>
+          <t>Jasad termutilasi di Depok, terbungkus karung. Mayat korban sempat dikira sampah oleh warga.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603579/pelatihan-tata-rias-bekali-siswa-berkebutuhan-khusus-menuju-dunia-kerja</t>
+          <t>https://news.detik.com/berita/d-8604492/mayat-mutilasi-dalam-karung-di-depok-dikira-sampah-sempat-dibakar-warga</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pelatihan-tata-rias-bekali-siswa-disabilitas-menuju-dunia-kerja-1785821111786_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/9def71f1-1c47-4d30-8a60-a8c3521d9475_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2225,33 +2225,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Penjualan Mobil RI Kalah dari Malaysia, Purbaya Ungkap Biang Keroknya</t>
+          <t>Hujan Deras Guyur Bogor, 1 Pohon Tumbang Timpa Atap Rumah Warga</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:40:03 +0700</t>
+          <t>Tue, 04 Aug 2026 20:35:19 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa buka-bukaan soal biang kerok penjualan kendaraan alami pelemahan.</t>
+          <t>Hujan deras melanda kawasan Desa Cijayanti, Kecamatan Babakan Madang, Bogor, Jawa Barat. Akibatnya, sebuah pohon tumbang kemudian menimpa rumah warga.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/industri/d-8604080/penjualan-mobil-ri-kalah-dari-malaysia-purbaya-ungkap-biang-keroknya</t>
+          <t>https://news.detik.com/berita/d-8604491/hujan-deras-guyur-bogor-1-pohon-tumbang-timpa-atap-rumah-warga</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/giias-2026-dipadati-pengunjung-deretan-mobil-baru-dan-ev-jadi-magnet-utama-1785427971780_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pohon-tumbang-timpa-rumah-warga-di-bogor-dokistimewa-1785850485303_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2268,28 +2268,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Insiden KM Mutiara Sentosa II, Sistem Keselamatan Kapal Diminta Dievaluasi</t>
+          <t>Tambak Modern Udang Vaname Hadirkan Solusi Budi Daya Efisien</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:38:27 +0700</t>
+          <t>Tue, 04 Aug 2026 23:00:40 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Anggota DPR Sudjatmiko menyampaikan duka cita atas kebakaran KM Mutiara Sentosa II. Ia mendesak evaluasi keselamatan pelayaran untuk mencegah tragedi serupa.</t>
+          <t>Budi daya udang vaname dengan sistem tertutup dikembangkan di kawasan industri Semarang. Teknologi ini menghemat air juga meningkatkan produktivitas tambak.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604495/insiden-km-mutiara-sentosa-ii-sistem-keselamatan-kapal-diminta-dievaluasi</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603831/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien-1785830418949_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Prabowo Perintahkan Bahlil Bereskan Listrik Padam di Kalimantan</t>
+          <t>Harga Minyak Langsung Turun Usai AS-Iran Setop Serangan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:36:06 +0700</t>
+          <t>Tue, 04 Aug 2026 22:35:07 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Presiden Prabowo minta pemadaman listrik di Kalimantan segera teratasi. Menteri ESDM Bahlil akan koordinasi dengan PLN untuk pemulihan cepat.</t>
+          <t>Harga minyak dunia turun nyaris 4% pada Selasa (4/8/2026) dan menyentuh level terendah dalam tiga pekan.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604071/prabowo-perintahkan-bahlil-bereskan-listrik-padam-di-kalimantan</t>
+          <t>https://finance.detik.com/moneter/d-8604597/harga-minyak-langsung-turun-usai-as-iran-setop-serangan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/20/prabowo-bahlil-1760968180889_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/24/harga-minyak-dunia-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2344,28 +2344,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Insiden Kapal Berulang Jadi Momentum Evaluasi Keselamatan Pelayaran</t>
+          <t>604.923 Rekening Terkait Scam Diblokir!</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:26:53 +0700</t>
+          <t>Tue, 04 Aug 2026 22:11:04 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deretan insiden kapal di Tanah Air menjadi pendorong untuk evaluasi sistem pengawasan keselamatan pelayaran.</t>
+          <t>OJK bersama Indonesia Anti-Scam Center (IASC) terus memperkuat upaya pemberantasan kasus keuangan ilegal dan penipuan di sektor jasa keuangan.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604051/insiden-kapal-berulang-jadi-momentum-evaluasi-keselamatan-pelayaran</t>
+          <t>https://finance.detik.com/moneter/d-8604576/604-923-rekening-terkait-scam-diblokir</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/24/ilustrasi-telepon-scam-atau-penipuan-1766569797414_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2382,28 +2382,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trump Digugat Massal Gegara Tarif Impor, Indonesia Ikut Terseret</t>
+          <t>Warga RI Doyan Pakai Paylater, Ini Buktinya</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:19:10 +0700</t>
+          <t>Tue, 04 Aug 2026 21:14:02 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sebanyak 25 negara bagian AS menggugat Trump atas tarif impor baru. Mereka menilai tarif tersebut ilegal dan meminta pengembalian bea masuk yang dibayarkan.</t>
+          <t>Penggunaan layanan Buy Now Pay Later (BNPL) atau paylater masih meningkat.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604002/trump-digugat-massal-gegara-tarif-impor-indonesia-ikut-terseret</t>
+          <t>https://finance.detik.com/moneter/d-8604532/warga-ri-doyan-pakai-paylater-ini-buktinya</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/10/27/ilustrasi-paylater_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2420,28 +2420,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WFH ASN Sehari dalam Sepekan Diperpanjang</t>
+          <t>Izin Tambang Berakhir 2041, Freeport Ajukan Perpanjangan ke Pemerintah</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:15:06 +0700</t>
+          <t>Tue, 04 Aug 2026 20:42:26 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pemerintah memperpanjang kebijakan Work from Home (WFH) bagi Aparatur Sipil Negara (ASN) sehari dalam sepekan.</t>
+          <t>Freeport Indonesia telah mengajukan permohonan perpanjangan IUPK untuk melanjutkan operasi tambang Grasberg setelah izin yang berlaku saat ini berakhir 2041.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603998/wfh-asn-sehari-dalam-sepekan-diperpanjang</t>
+          <t>https://finance.detik.com/energi/d-8604497/izin-tambang-berakhir-2041-freeport-ajukan-perpanjangan-ke-pemerintah</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/07/11/27d3660c-abb0-424e-8871-e739c2b6cc4d_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/11/mengintip-tambang-sedalam-17-km-di-perut-bumi-papua-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2458,28 +2458,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IHSG Ditutup Menguat ke Level 6.391</t>
+          <t>Mendes: Kopdes Merah Putih Penggerak Ekonomi Desa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:13:12 +0700</t>
+          <t>Tue, 04 Aug 2026 20:19:08 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IHSG ditutup menguat di level 6.319,6, naik 1,37%. Volume transaksi mencapai 33.150 miliar saham. Kinerja mingguan dan bulanan juga positif.</t>
+          <t>Pemerintah menargetkan pembangunan 30.000 Koperasi Desa/Kelurahan Merah Putih (KDKMP) pada tahun ini.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604014/ihsg-ditutup-menguat-ke-level-6-391</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604472/mendes-kopdes-merah-putih-penggerak-ekonomi-desa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/ihsg-terpuruk-kekhawatiran-pasar-meningkat-1780558039793_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menteri-desa-dan-pembangunan-daerah-tertinggal-pdt-1785853253837_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2496,28 +2496,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kuba Gelap Gulita Lagi, Krisis Listrik Makin Parah</t>
+          <t>Bursa Mineral Meluncur 1 Januari 2027, Ini Bocoran dari OJK</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:09:09 +0700</t>
+          <t>Tue, 04 Aug 2026 20:00:15 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Krisis listrik Kuba semakin parah dengan pemadaman berulang. Sanksi AS dan infrastruktur tua jadi penyebab utama, mempengaruhi jutaan warga.</t>
+          <t>OJK buka-bukaan soal Bursa Mineral bakal meluncur 1 Januari 2027.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603992/kuba-gelap-gulita-lagi-krisis-listrik-makin-parah</t>
+          <t>https://finance.detik.com/energi/d-8604418/bursa-mineral-meluncur-1-januari-2027-ini-bocoran-dari-ojk</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/situasi-di-havana-ibu-kota-kuba-saat-diselimuti-kegelapan-buntut-lumpuhnya-jaringan-listrik-negara-tersebut-1785751638653_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/18/friderica-widyasari-dewi-1781765532562_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2534,28 +2534,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Suntik Dana Rp 400 T ke Perbankan, Purbaya: Kalau Kurang, Saya Tambah!</t>
+          <t>Bea Cukai Amankan 3 Warga Negara Malaysia Bawa Narkotika</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:01:28 +0700</t>
+          <t>Tue, 04 Aug 2026 19:51:37 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa bicara soal suntikan dana SAL ke perbankan Rp 400 triliun.</t>
+          <t>Petugas Bea Cukai Bandara Soekarno-Hatta mengamankan ketamin dari 3 wanita penumpang pesawat diduga Warga Negara Malaysia.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8603978/suntik-dana-rp-400-t-ke-perbankan-purbaya-kalau-kurang-saya-tambah</t>
+          <t>https://finance.detik.com/ekonomi-bisnis/d-8604433/bea-cukai-amankan-3-warga-negara-malaysia-bawa-narkotika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/05/tawa-purbaya-pastikan-ekonomi-hingga-mei-2026-masih-solid-1780655487362_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/ed32a201-0b77-4c2b-a370-0636977c2075_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2572,28 +2572,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BPS Catat Deflasi Bulanan, Harga Komoditas Pangan Jadi Penentu</t>
+          <t>Industri Kripto RI Terus Melonjak, Transaksinya Rp 28 T per Juni 2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:00:57 +0700</t>
+          <t>Tue, 04 Aug 2026 19:30:08 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BPS mencatat deflasi bulanan sebesar 0,14 persen pada Juli 2026. Penurunan harga sejumlah bahan pangan menjadi faktor utama yang menekan Indeks Harga Konsumen.</t>
+          <t>Aset kripto terus diminati di Indonesia, dengan 22,69 juta akun dan transaksi mencapai Rp 28,58 triliun pada Juni 2026. OJK tetap awasi perlindungan konsumen.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603527/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu</t>
+          <t>https://finance.detik.com/fintech/d-8604314/industri-kripto-ri-terus-melonjak-transaksinya-rp-28-t-per-juni-2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu-1785819465759_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/05/27/ilustrasi-bitcoin_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2610,28 +2610,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>66 Ribu UMKM Jalani Pembinaan, Fokus Bangun Nilai Jual Lewat Storytelling</t>
+          <t>Sektor Jasa Keuangan Tetap Stabil, Kredit Perbankan Tumbuh 12,67%</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:58:17 +0700</t>
+          <t>Tue, 04 Aug 2026 19:19:21 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pertamina Patra Niaga membina 66 ribu UMKM dengan fokus pada storytelling untuk meningkatkan nilai jual produk. Strategi ini dorong daya saing di pasar.</t>
+          <t>OJK menyatakan sektor jasa keuangan tetap stabil di tengah ketidakpastian global. Pertumbuhan kredit dan permodalan perbankan menunjukkan kinerja positif.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/solusiukm/d-8604055/66-ribu-umkm-jalani-pembinaan-fokus-bangun-nilai-jual-lewat-storytelling</t>
+          <t>https://finance.detik.com/moneter/d-8604398/sektor-jasa-keuangan-tetap-stabil-kredit-perbankan-tumbuh-12-67</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/30/ilustrasi-umkm-makanan-1748571534080_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ojk-1785845945964_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2648,28 +2648,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pegadaian Raih Penghargaan Khusus di Ajang IDX Channel Anugerah ESG 2026</t>
+          <t>OJK Catat Total Aset Industri Asuransi RI Capai Rp Rp 1.184 triliun</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:55:52 +0700</t>
+          <t>Tue, 04 Aug 2026 19:07:39 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pegadaian raih penghargaan IDX Channel Anugerah ESG 2026 untuk inovasi keuangan inklusif.</t>
+          <t>OJK melaporkan total aset industri asuransi RI mencapai Rp 1.184 triliun per Juni 2026, dengan pertumbuhan stabil meski beberapa sektor mengalami kontraksi.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603968/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026</t>
+          <t>https://finance.detik.com/moneter/d-8604257/ojk-catat-total-aset-industri-asuransi-ri-capai-rp-rp-1-184-triliun</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026-1785833724891_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/14/ilustrasi-asuransi-kesehatan-1778737684617_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2686,28 +2686,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pendapatan Chandra Asri Naik 83%, tapi Laba Malah Anjlok 77% Jadi Rp 6,6 T</t>
+          <t>Kredit Perbankan Tembus Rp 9.081 Triliun, Tumbuh 12,67%</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:48:29 +0700</t>
+          <t>Tue, 04 Aug 2026 18:30:05 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PT Chandra Asri Pacific Tbk (TPIA) membukukan penurunan laba bersih seiring tumbuhnya pendapatan sepanjang semester I-2026.</t>
+          <t>Kredit perbankan pada bulan Juni 2026 tumbuh 12,67% menjadi Rp 9.081 triliun.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603945/pendapatan-chandra-asri-naik-83-tapi-laba-malah-anjlok-77-jadi-rp-6-6-t</t>
+          <t>https://finance.detik.com/moneter/d-8604271/kredit-perbankan-tembus-rp-9-081-triliun-tumbuh-12-67</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/31/chandra-asri_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/02/10/uang-tunai-rupiah-4_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2724,28 +2724,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rayuan Maut Purbaya ke Raksasa Otomotif Jepang</t>
+          <t>Utang Pinjol Warga RI Tembus Rp 105 Triliun!</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:21:30 +0700</t>
+          <t>Tue, 04 Aug 2026 18:25:04 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan rayuan maut agar raksasa otomotif Jepang, Toyota, pindahkan pabriknya ke Indonesia.</t>
+          <t>OJK mencatat nilai pembiayaan pinjol mencapai Rp 105,14 triliun, atau tumbuh 25,88% secara tahunan pada bulan Juni 2026.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/industri/d-8603875/rayuan-maut-purbaya-ke-raksasa-otomotif-jepang</t>
+          <t>https://finance.detik.com/moneter/d-8604291/utang-pinjol-warga-ri-tembus-rp-105-triliun</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/menteri-keuangan-purbaya-yudhi-sadewa-1758533359856_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/02/04/b3a5ed4c-3141-4fed-a3ff-2bfc948f1b01_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2762,28 +2762,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Moody's-Fitch Kasih Nilai Negatif ke Ekonomi RI, Purbaya: Mereka Offside!</t>
+          <t>BRILink Agen Permudah Perajin &amp;amp; Petani Alor Akses Layanan Perbankan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:43:15 +0700</t>
+          <t>Tue, 04 Aug 2026 18:13:26 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa menyebut lembaga rating Moody's dan Fitch salah ukur ekonomi Indonesia.</t>
+          <t>Kepulauan Alor, NTT, menawarkan keindahan dan tantangan. Kehadiran BRILink Agen mempermudah akses keuangan, mendukung kemandirian ekonomi masyarakat setempat.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603805/moodys-fitch-kasih-nilai-negatif-ke-ekonomi-ri-purbaya-mereka-offside</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604269/brilink-agen-permudah-perajin-petani-alor-akses-layanan-perbankan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/purbaya-garuk-kepala-apbn-april-2026-defisit-rp1644-triliun-1779201435955_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/12/05/4acc195a-ed44-44c8-88b3-7f629b73d63b_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2800,28 +2800,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Industri Alas Kaki Indonesia Bertahan di Tengah Tarif Impor AS</t>
+          <t>36 Ribu Rekening Judi Online Diblokir!</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 18:00:20 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Industri alas kaki Indonesia tetap menjaga optimisme di tengah kebijakan tarif impor Amerika Serikat. Pelaku usaha menilai daya saing produk masih terjaga.</t>
+          <t>Otoritas Jasa Keuangan (OJK) sebut 36.735 rekening terkait judi online diblokir.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603497/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604245/36-ribu-rekening-judi-online-diblokir</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as-1785818219683_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/27/ilustrasi-judi-online-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2838,28 +2838,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apa Kabar Proyek Trans Papua 50 Km? Begini Progresnya</t>
+          <t>WIKA Sukses Catatkan Kontrak Baru Rp 6,91 Triliun hingga Juni 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:58:11 +0700</t>
+          <t>Tue, 04 Aug 2026 17:45:19 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kementerian Pekerjaan Umum (PU) mengungkapkan progres pembangunan Jalan Trans Papua.</t>
+          <t>WIKA raih kontrak baru Rp 6,91 triliun hingga Juni 2026, didorong proyek strategis di konstruksi dan infrastruktur. Optimis dukung pembangunan nasional.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/infrastruktur/d-8603725/apa-kabar-proyek-trans-papua-50-km-begini-progresnya</t>
+          <t>https://finance.detik.com/infrastruktur/d-8604234/wika-sukses-catatkan-kontrak-baru-rp-6-91-triliun-hingga-juni-2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pembangunan-trans-papua-1785826507044_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/wika-sukses-catatkan-kontrak-baru-rp-691-triliun-hingga-juni-2026-1785840143413_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2876,28 +2876,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kapan Prabowo Luncurkan Insentif Kendaraan Listrik?</t>
+          <t>Gagal Dapat Diskon Moge Harley Davidson, Purbaya: Yah, Lemes Gue!</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:35:04 +0700</t>
+          <t>Tue, 04 Aug 2026 17:38:14 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa bilang dalam beberapa pekan ke depan insentif kendaraan listrik akan diluncurkan Presiden Prabowo Subianto.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa bercerita dirinya gagal membeli motor Harley Davidson dengan harga diskon karena dianggap gratifikasi.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/industri/d-8603674/kapan-prabowo-luncurkan-insentif-kendaraan-listrik</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604225/gagal-dapat-diskon-moge-harley-davidson-purbaya-yah-lemes-gue</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/06/tekan-biaya-transportasi-motor-listrik-jadi-andalan-baru-masyarakat-1775465692322_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menkeu-purbaya-jajal-moge-harley-davidson-1785839816386_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2914,28 +2914,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Proyek PLTS 100 GW Segera Dimulai, Bali Jadi Lokasi Pertama</t>
+          <t>Bos OJK Blak-blakan Kondisi Sektor Keuangan RI di Tengah Gejolak Global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:26:52 +0700</t>
+          <t>Tue, 04 Aug 2026 17:16:02 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Menteri ESDM Bahlil Lahadalia umumkan pembangunan PLTS 100 GW bertahap, dimulai di Bali. Proyek ini ditargetkan rampung dengan perencanaan matang.</t>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi buka-bukaan kondisi sektor keuangan di tengah gonjang-ganjing global.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603661/proyek-plts-100-gw-segera-dimulai-bali-jadi-lokasi-pertama</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604173/bos-ojk-blak-blakan-kondisi-sektor-keuangan-ri-di-tengah-gejolak-global</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/22/menteri-esdm-bahlil-lahadalia-eva-sdetikcom-1782133701407_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/frederica-widyasari-dewi-1785765447950_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2952,28 +2952,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ketemu World Bank-IMF, Purbaya: I'm the Most Unlucky Minister in the World</t>
+          <t>Prabowo Minta Harga BBM Subsidi Tak Naik</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:10:09 +0700</t>
+          <t>Tue, 04 Aug 2026 17:11:28 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa curhat dirinya menjadi menteri paling kurang beruntung di dunia.</t>
+          <t>Menteri ESDM Bahlil mengungkapkan kebijakan harga BBM bersubsidi tetap dipertahankan meski harga minyak dunia naik.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603641/ketemu-world-bank-imf-purbaya-im-the-most-unlucky-minister-in-the-world</t>
+          <t>https://finance.detik.com/energi/d-8604168/prabowo-minta-harga-bbm-subsidi-tak-naik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786140_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/01/presiden-prabowo-subianto-dok-youtube-setpres-1782871893408_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2990,28 +2990,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Peternakan dan Pertanian Terpadu di Sleman Perkuat Sistem Pangan Berkelanjutan</t>
+          <t>OJK Kasih Denda Rp 91 Miliar ke 104 Pelaku Pasar Modal</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 17:03:56 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Konsep integrated farming di Sleman menghubungkan peternakan, pertanian, dan pengolahan limbah. Sistem ini mendukung produksi lebih efisien dan berkelanjutan.</t>
+          <t>OJK menjatuhkan denda Rp 91 miliar kepada 104 pelaku pasar modal untuk penegakan ketentuan dan perlindungan konsumen. Sanksi administratif juga diterapkan.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603467/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604151/ojk-kasih-denda-rp-91-miliar-ke-104-pelaku-pasar-modal</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan-1785816225367_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/12/30/59e6cb2c-4043-4878-a12b-89f4ab9e5a8e_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3028,28 +3028,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cara Scan QRIS Cross Border di Luar Negeri</t>
+          <t>Pelatihan Tata Rias Bekali Siswa Berkebutuhan Khusus Menuju Dunia Kerja</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:57:38 +0700</t>
+          <t>Tue, 04 Aug 2026 17:00:33 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DANA mendukung transaksi QRIS Cross Border di luar negeri, memudahkan pengguna berbelanja di Thailand, Malaysia, Jepang, dan negara lainnya tanpa uang tunai.</t>
+          <t>Pelatihan tata rias menjadi salah satu upaya memperluas kesempatan kerja bagi siswa berkebutuhan khusus. Peserta belajar keterampilan yang bernilai ekonomi.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603628/cara-scan-qris-cross-border-di-luar-negeri</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603579/pelatihan-tata-rias-bekali-siswa-berkebutuhan-khusus-menuju-dunia-kerja</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ilustrasi-qris-1785823037090_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pelatihan-tata-rias-bekali-siswa-disabilitas-menuju-dunia-kerja-1785821111786_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3066,28 +3066,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IHSG Tertahan di Level 6.200</t>
+          <t>Penjualan Mobil RI Kalah dari Malaysia, Purbaya Ungkap Biang Keroknya</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:41:11 +0700</t>
+          <t>Tue, 04 Aug 2026 16:40:03 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HSG menguat 0,57% ke level 6.270,15 hingga penutupan perdagangan siang ini.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa buka-bukaan soal biang kerok penjualan kendaraan alami pelemahan.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603595/ihsg-tertahan-di-level-6-200</t>
+          <t>https://finance.detik.com/industri/d-8604080/penjualan-mobil-ri-kalah-dari-malaysia-purbaya-ungkap-biang-keroknya</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/18/ihsg-anjlok-ke-zona-merah-bursa-saham-melemah-tajam-1779098741182_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/giias-2026-dipadati-pengunjung-deretan-mobil-baru-dan-ev-jadi-magnet-utama-1785427971780_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3104,28 +3104,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Magang Nasional Banjir Peminat, Pendaftar Tembus 732 Ribu!</t>
+          <t>Insiden KM Mutiara Sentosa II, Sistem Keselamatan Kapal Diminta Dievaluasi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:36:26 +0700</t>
+          <t>Tue, 04 Aug 2026 16:38:27 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Peminat Magang Nasional mencapai 732 ribu, namun hanya 50 ribu yang diterima.</t>
+          <t>Anggota DPR Sudjatmiko menyampaikan duka cita atas kebakaran KM Mutiara Sentosa II. Ia mendesak evaluasi keselamatan pelayaran untuk mencegah tragedi serupa.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603589/magang-nasional-banjir-peminat-pendaftar-tembus-732-ribu</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604495/insiden-km-mutiara-sentosa-ii-sistem-keselamatan-kapal-diminta-dievaluasi</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/program-magang-kerja-phr-batch-9-hadir-untuk-memberikan-pengalaman-profesional-pendampingan-dari-para-ahli-dan-kesempatan-berk-1781240776723_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3142,28 +3142,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gelombang PHK Makin Besar di Singapura, 4.500 Orang Jadi Korban</t>
+          <t>Prabowo Perintahkan Bahlil Bereskan Listrik Padam di Kalimantan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:14:37 +0700</t>
+          <t>Tue, 04 Aug 2026 16:36:06 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gelombang PHK di Singapura meningkat pada kuartal II-2026, mencapai 4.500 pekerja. Meski demikian, total lapangan kerja justru bertambah 10.700.</t>
+          <t>Presiden Prabowo minta pemadaman listrik di Kalimantan segera teratasi. Menteri ESDM Bahlil akan koordinasi dengan PLN untuk pemulihan cepat.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603555/gelombang-phk-makin-besar-di-singapura-4-500-orang-jadi-korban</t>
+          <t>https://finance.detik.com/energi/d-8604071/prabowo-perintahkan-bahlil-bereskan-listrik-padam-di-kalimantan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/10/27/ilustrasi-kena-phk_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/20/prabowo-bahlil-1760968180889_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LPEI Kucurkan US$ 8,5 Juta Danai Ekspor Gerbong Barang ke Selandia Baru</t>
+          <t>Insiden Kapal Berulang Jadi Momentum Evaluasi Keselamatan Pelayaran</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:11:18 +0700</t>
+          <t>Tue, 04 Aug 2026 16:26:53 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LPEI dukung PT INKA ekspor 340 unit Wagon ke Selandia Baru dengan fasilitas USD 8,5 juta. Sinergi ini perkuat industri strategis dan perekonomian nasional.</t>
+          <t>Deretan insiden kapal di Tanah Air menjadi pendorong untuk evaluasi sistem pengawasan keselamatan pelayaran.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8603549/lpei-kucurkan-us-8-5-juta-danai-ekspor-gerbong-barang-ke-selandia-baru</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604051/insiden-kapal-berulang-jadi-momentum-evaluasi-keselamatan-pelayaran</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eximbank-danai-ekspor-pt-inka-ke-selandia-baru-1785820259573_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3218,28 +3218,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alarm Berbunyi di Rusia, Bank-bank Mulai Krisis Uang Tunai!</t>
+          <t>Trump Digugat Massal Gegara Tarif Impor, Indonesia Ikut Terseret</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:03:30 +0700</t>
+          <t>Tue, 04 Aug 2026 16:19:10 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bank-bank Rusia menghadapi tekanan likuiditas rubel, membatasi pembelian obligasi pemerintah. Defisit anggaran meningkat.</t>
+          <t>Sebanyak 25 negara bagian AS menggugat Trump atas tarif impor baru. Mereka menilai tarif tersebut ilegal dan meminta pengembalian bea masuk yang dibayarkan.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8603535/alarm-berbunyi-di-rusia-bank-bank-mulai-krisis-uang-tunai</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604002/trump-digugat-massal-gegara-tarif-impor-indonesia-ikut-terseret</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/01/ini-yang-bikin-warga-rusia-panik-serbu-atm-bank-buat-tarik-uang_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3256,28 +3256,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BSI dan Danantara Perkuat Ekosistem UMKM agar Pelaku Usaha Naik Kelas</t>
+          <t>WFH ASN Sehari dalam Sepekan Diperpanjang</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:51:53 +0700</t>
+          <t>Tue, 04 Aug 2026 16:15:06 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PT Bank Syariah Indonesia (BSI) dan Danantara memperkuat UMKM melalui 35 Sentra dan 4 UMKM Center, mendukung pembiayaan, digitalisasi, dan sertifikasi halal.</t>
+          <t>Pemerintah memperpanjang kebijakan Work from Home (WFH) bagi Aparatur Sipil Negara (ASN) sehari dalam sepekan.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603515/bsi-dan-danantara-perkuat-ekosistem-umkm-agar-pelaku-usaha-naik-kelas</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603998/wfh-asn-sehari-dalam-sepekan-diperpanjang</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/direktur-utama-bsi-anggoro-eko-cahyo-1785820807840_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/07/11/27d3660c-abb0-424e-8871-e739c2b6cc4d_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3294,28 +3294,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tak Mau Kehilangan Guru Berkualitas, Singapura Naikkan Gaji hingga 9%</t>
+          <t>IHSG Ditutup Menguat ke Level 6.391</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:48:03 +0700</t>
+          <t>Tue, 04 Aug 2026 16:13:12 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pemerintah Singapura akan menaikkan gaji guru dan tenaga pendidik 2-9% mulai 1 Oktober 2026, untuk menarik dan mempertahankan tenaga pendidik berkualitas.</t>
+          <t>IHSG ditutup menguat di level 6.319,6, naik 1,37%. Volume transaksi mencapai 33.150 miliar saham. Kinerja mingguan dan bulanan juga positif.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603511/tak-mau-kehilangan-guru-berkualitas-singapura-naikkan-gaji-hingga-9</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604014/ihsg-ditutup-menguat-ke-level-6-391</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/21/pendidikan-nilai-1750494841214_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/ihsg-terpuruk-kekhawatiran-pasar-meningkat-1780558039793_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Trump Bantu Jepang Selamatkan Yen, Apa Untungnya buat AS?</t>
+          <t>Kuba Gelap Gulita Lagi, Krisis Listrik Makin Parah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:43:30 +0700</t>
+          <t>Tue, 04 Aug 2026 16:09:09 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Presiden AS Donald Trump mengatakan, intervensi ini dilakukan atas permintaan pemerintah Jepang.</t>
+          <t>Krisis listrik Kuba semakin parah dengan pemadaman berulang. Sanksi AS dan infrastruktur tua jadi penyebab utama, mempengaruhi jutaan warga.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603507/trump-bantu-jepang-selamatkan-yen-apa-untungnya-buat-as</t>
+          <t>https://finance.detik.com/energi/d-8603992/kuba-gelap-gulita-lagi-krisis-listrik-makin-parah</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/situasi-di-havana-ibu-kota-kuba-saat-diselimuti-kegelapan-buntut-lumpuhnya-jaringan-listrik-negara-tersebut-1785751638653_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3370,28 +3370,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Peresmian Pabrik Baterai EV di Karawang Tinggal Tunggu Jadwal Prabowo</t>
+          <t>Suntik Dana Rp 400 T ke Perbankan, Purbaya: Kalau Kurang, Saya Tambah!</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:11:33 +0700</t>
+          <t>Tue, 04 Aug 2026 16:01:28 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Menteri ESDM Bahlil mengumumkan pabrik baterai listrik di Karawang siap diresmikan, tinggal menunggu jadwal Presiden. Investasi mencapai US$5,9 miliar.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa bicara soal suntikan dana SAL ke perbankan Rp 400 triliun.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603463/peresmian-pabrik-baterai-ev-di-karawang-tinggal-tunggu-jadwal-prabowo</t>
+          <t>https://finance.detik.com/moneter/d-8603978/suntik-dana-rp-400-t-ke-perbankan-purbaya-kalau-kurang-saya-tambah</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/menteri-esdm-bahlil-lahadalia-1784186781817_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/05/tawa-purbaya-pastikan-ekonomi-hingga-mei-2026-masih-solid-1780655487362_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3408,28 +3408,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RI-Thailand Sepakat Genjot Perdagangan Tembus Rp 360 Triliun</t>
+          <t>BPS Catat Deflasi Bulanan, Harga Komoditas Pangan Jadi Penentu</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:02:03 +0700</t>
+          <t>Tue, 04 Aug 2026 16:00:57 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Indonesia dan Thailand sepakat menggenjot perdagangan dengan target Rp 360 triliun pada 2030.</t>
+          <t>BPS mencatat deflasi bulanan sebesar 0,14 persen pada Juli 2026. Penurunan harga sejumlah bahan pangan menjadi faktor utama yang menekan Indeks Harga Konsumen.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603447/ri-thailand-sepakat-genjot-perdagangan-tembus-rp-360-triliun</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603527/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/presiden-prabowo-subianto-menggelar-jamuan-santap-malam-resmi-untuk-pm-kerajaan-thailand-anutin-charnvirakul-foto-rusman-biro--1785806274579_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu-1785819465759_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3446,28 +3446,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mengenang Burhanuddin 'Bur' Maras, Tokoh Migas dan Pendiri Lekom Maras</t>
+          <t>66 Ribu UMKM Jalani Pembinaan, Fokus Bangun Nilai Jual Lewat Storytelling</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:00:37 +0700</t>
+          <t>Tue, 04 Aug 2026 15:58:17 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Burhanuddin 'Bur' Maras, pendiri PT Lekom Maras, wafat di usia 90 tahun. Ia dikenal sebagai tokoh penting di industri perminyakan dan politik Indonesia.</t>
+          <t>Pertamina Patra Niaga membina 66 ribu UMKM dengan fokus pada storytelling untuk meningkatkan nilai jual produk. Strategi ini dorong daya saing di pasar.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603445/mengenang-burhanuddin-bur-maras-tokoh-migas-dan-pendiri-lekom-maras</t>
+          <t>https://finance.detik.com/solusiukm/d-8604055/66-ribu-umkm-jalani-pembinaan-fokus-bangun-nilai-jual-lewat-storytelling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/burhanuddin-bur-maras-1785815972293.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/30/ilustrasi-umkm-makanan-1748571534080_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3484,28 +3484,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Krisis Iran Memanas, Warga Teheran Tetap Jalani Aktivitas di Tengah Ketegangan</t>
+          <t>Pegadaian Raih Penghargaan Khusus di Ajang IDX Channel Anugerah ESG 2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:00:34 +0700</t>
+          <t>Tue, 04 Aug 2026 15:55:52 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Krisis Iran menjadi sorotan dunia. Di tengah ketegangan politik dan hubungan internasional, warga Teheran tetap menjalani aktivitas sehari-hari.</t>
+          <t>Pegadaian raih penghargaan IDX Channel Anugerah ESG 2026 untuk inovasi keuangan inklusif.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602911/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603968/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan-1785761340975_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026-1785833724891_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3522,28 +3522,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Buruh Batalkan Rencana Demo di DPR Senin Depan, Takut Ada Penyusup</t>
+          <t>Pendapatan Chandra Asri Naik 83%, tapi Laba Malah Anjlok 77% Jadi Rp 6,6 T</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:48:57 +0700</t>
+          <t>Tue, 04 Aug 2026 15:48:29 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KBPBI menunda aksi unjuk rasa di depan DPR untuk mendesak RUU Ketenagakerjaan. Keputusan diambil untuk menghindari potensi penyusup dan menjaga ketertiban.</t>
+          <t>PT Chandra Asri Pacific Tbk (TPIA) membukukan penurunan laba bersih seiring tumbuhnya pendapatan sepanjang semester I-2026.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603423/buruh-batalkan-rencana-demo-di-dpr-senin-depan-takut-ada-penyusup</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603945/pendapatan-chandra-asri-naik-83-tapi-laba-malah-anjlok-77-jadi-rp-6-6-t</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/presiden-konfederasi-serikat-pekerja-seluruh-indonesia-kspsi-andi-gani-1758528973493_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/31/chandra-asri_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3560,28 +3560,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Setelah Naik Beruntun, Harga Emas Antam Akhirnya Turun</t>
+          <t>Rayuan Maut Purbaya ke Raksasa Otomotif Jepang</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:51:02 +0700</t>
+          <t>Tue, 04 Aug 2026 15:21:30 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Harga emas Antam hari ini turun Rp 7.000 per gram menjadi Rp 2.603.000. Rincian harga emas dari 0,5 gram hingga 1.000 gram juga disajikan.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan rayuan maut agar raksasa otomotif Jepang, Toyota, pindahkan pabriknya ke Indonesia.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603360/setelah-naik-beruntun-harga-emas-antam-akhirnya-turun</t>
+          <t>https://finance.detik.com/industri/d-8603875/rayuan-maut-purbaya-ke-raksasa-otomotif-jepang</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/13/emas-batangan-1763011692898_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/menteri-keuangan-purbaya-yudhi-sadewa-1758533359856_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3598,28 +3598,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mitratel Cetak Laba Rp 1,11 T</t>
+          <t>Moody's-Fitch Kasih Nilai Negatif ke Ekonomi RI, Purbaya: Mereka Offside!</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:48:19 +0700</t>
+          <t>Tue, 04 Aug 2026 14:43:15 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PT Dayamitra Telekomunikasi Tbk (MTEL) alias Mitratel membukukan kinerja positif hingga akhir Juni 2026.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa menyebut lembaga rating Moody's dan Fitch salah ukur ekonomi Indonesia.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603358/mitratel-cetak-laba-rp-1-11-t</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603805/moodys-fitch-kasih-nilai-negatif-ke-ekonomi-ri-purbaya-mereka-offside</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/17/potret-tower-mitratel-yang-manfaatkan-panel-surya-5_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/purbaya-garuk-kepala-apbn-april-2026-defisit-rp1644-triliun-1779201435955_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3636,28 +3636,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dolar AS Tembus Rp 18.000 Pagi Ini</t>
+          <t>Industri Alas Kaki Indonesia Bertahan di Tengah Tarif Impor AS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:33:38 +0700</t>
+          <t>Tue, 04 Aug 2026 14:00:10 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dolar AS bergerak menguat 0,06% ke level Rp 18.000 di awal pembukaan perdagangan.</t>
+          <t>Industri alas kaki Indonesia tetap menjaga optimisme di tengah kebijakan tarif impor Amerika Serikat. Pelaku usaha menilai daya saing produk masih terjaga.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603345/dolar-as-tembus-rp-18-000-pagi-ini</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603497/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338333_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as-1785818219683_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3674,28 +3674,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IHSG Dibuka Menguat ke 6.255</t>
+          <t>Apa Kabar Proyek Trans Papua 50 Km? Begini Progresnya</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:29:37 +0700</t>
+          <t>Tue, 04 Aug 2026 13:58:11 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
+          <t>Kementerian Pekerjaan Umum (PU) mengungkapkan progres pembangunan Jalan Trans Papua.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603339/ihsg-dibuka-menguat-ke-6-255</t>
+          <t>https://finance.detik.com/infrastruktur/d-8603725/apa-kabar-proyek-trans-papua-50-km-begini-progresnya</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/30/ihsg-rebound-usai-dua-hari-anjlok-seiring-pengunduran-diri-dirut-bei-1769748663323_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pembangunan-trans-papua-1785826507044_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3712,28 +3712,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Empat Sistem Karantina Diperkuat, Ekspor Ikan Hias Indonesia Makin Mendunia</t>
+          <t>Kapan Prabowo Luncurkan Insentif Kendaraan Listrik?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:00:23 +0700</t>
+          <t>Tue, 04 Aug 2026 13:35:04 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Barantin memperkuat empat sistem karantina untuk meningkatkan daya saing dan kepercayaan pasar global terhadap ikan hias Indonesia.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa bilang dalam beberapa pekan ke depan insentif kendaraan listrik akan diluncurkan Presiden Prabowo Subianto.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602609/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia</t>
+          <t>https://finance.detik.com/industri/d-8603674/kapan-prabowo-luncurkan-insentif-kendaraan-listrik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia-1785750239859_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/06/tekan-biaya-transportasi-motor-listrik-jadi-andalan-baru-masyarakat-1775465692322_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3750,28 +3750,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bos BGN Buka Suara soal Putusan MK Anggaran MBG dan Pendidikan Dipisah</t>
+          <t>Proyek PLTS 100 GW Segera Dimulai, Bali Jadi Lokasi Pertama</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:38 +0700</t>
+          <t>Tue, 04 Aug 2026 13:26:52 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kami ini adalah lembaga operasional. Tentu saja kami akan melaksanakan apapun kebijakan dari pemerintah, kata Sudaryono.</t>
+          <t>Menteri ESDM Bahlil Lahadalia umumkan pembangunan PLTS 100 GW bertahap, dimulai di Bali. Proyek ini ditargetkan rampung dengan perencanaan matang.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603305/bos-bgn-buka-suara-soal-putusan-mk-anggaran-mbg-dan-pendidikan-dipisah</t>
+          <t>https://finance.detik.com/energi/d-8603661/proyek-plts-100-gw-segera-dimulai-bali-jadi-lokasi-pertama</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053334_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/22/menteri-esdm-bahlil-lahadalia-eva-sdetikcom-1782133701407_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3788,28 +3788,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TLKM Catat Kinerja Semester I-2026, BUVA dan TAPG Umumkan Aksi Korporasi</t>
+          <t>Ketemu World Bank-IMF, Purbaya: I'm the Most Unlucky Minister in the World</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:45:59 +0700</t>
+          <t>Tue, 04 Aug 2026 13:10:09 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TLKM membukukan pendapatan Rp75,9 triliun dan laba Rp10,6 triliun pada semester I-2026. BUVA siapkan rights issue, sementara TAPG tetapkan dividen interim.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa curhat dirinya menjadi menteri paling kurang beruntung di dunia.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603300/tlkm-catat-kinerja-semester-i-2026-buva-dan-tapg-umumkan-aksi-korporasi</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603641/ketemu-world-bank-imf-purbaya-im-the-most-unlucky-minister-in-the-world</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bursa-dan-valas-1785806578-1785806579142.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786140_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3826,28 +3826,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Trump Tak Suka Exxon &amp;amp; Chevron Untung Gede Gara-gara Harga Minyak Tinggi</t>
+          <t>Peternakan dan Pertanian Terpadu di Sleman Perkuat Sistem Pangan Berkelanjutan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:17:17 +0700</t>
+          <t>Tue, 04 Aug 2026 13:00:10 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mereka meraup terlalu banyak uang dari kelangkaan ini. Saya tidak menyukainya, ujar Trump.</t>
+          <t>Konsep integrated farming di Sleman menghubungkan peternakan, pertanian, dan pengolahan limbah. Sistem ini mendukung produksi lebih efisien dan berkelanjutan.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603261/trump-tak-suka-exxon-chevron-untung-gede-gara-gara-harga-minyak-tinggi</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603467/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan-1785816225367_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3864,28 +3864,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tips Aman Pakai QRIS agar Terhindar dari Penipuan</t>
+          <t>Cara Scan QRIS Cross Border di Luar Negeri</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:05:09 +0700</t>
+          <t>Tue, 04 Aug 2026 12:57:38 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>QRIS adalah metode pembayaran digital praktis. Pelajari tips aman bertransaksi, cara menggunakan QRIS, dan cara mengenali penipuan untuk keamanan Anda.</t>
+          <t>DANA mendukung transaksi QRIS Cross Border di luar negeri, memudahkan pengguna berbelanja di Thailand, Malaysia, Jepang, dan negara lainnya tanpa uang tunai.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8602406/tips-aman-pakai-qris-agar-terhindar-dari-penipuan</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603628/cara-scan-qris-cross-border-di-luar-negeri</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/tips-aman-pakai-qris-agar-terhindar-dari-penipuan-1785745583872.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ilustrasi-qris-1785823037090_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3902,28 +3902,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pernak-pernik HUT Ke-81 RI Mulai Diburu di Pasar Asemka</t>
+          <t>IHSG Tertahan di Level 6.200</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:00:44 +0700</t>
+          <t>Tue, 04 Aug 2026 12:41:11 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Permintaan pernak-pernik kemerdekaan mulai meningkat menjelang HUT Ke-81 RI. Pedagang Pasar Asemka mencatat penjualan naik sekitar 20 persen sejak akhir Juli.</t>
+          <t>HSG menguat 0,57% ke level 6.270,15 hingga penutupan perdagangan siang ini.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8601820/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603595/ihsg-tertahan-di-level-6-200</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka-1785728519984_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/18/ihsg-anjlok-ke-zona-merah-bursa-saham-melemah-tajam-1779098741182_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KSP &amp;amp; Bahlil  Buka Suara soal Ekspor 'Harta Karun' RI</t>
+          <t>Magang Nasional Banjir Peminat, Pendaftar Tembus 732 Ribu!</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:25:00 +0700</t>
+          <t>Tue, 04 Aug 2026 12:36:26 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kantor Staf Presiden (KSP) buka suara terkait soal harta karun Indonesia yakni logam tanah jarang.</t>
+          <t>Peminat Magang Nasional mencapai 732 ribu, namun hanya 50 ribu yang diterima.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603108/ksp-bahlil-buka-suara-soal-ekspor-harta-karun-ri</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603589/magang-nasional-banjir-peminat-pendaftar-tembus-732-ribu</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/09/logam-tanah-jarang-jadi-harta-karun-yang-diincar-dunia-3_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/program-magang-kerja-phr-batch-9-hadir-untuk-memberikan-pengalaman-profesional-pendampingan-dari-para-ahli-dan-kesempatan-berk-1781240776723_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3978,28 +3978,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Musim Cuan 17 Agustus Dimulai, Pedagang Bendera Mulai Gelar Lapak</t>
+          <t>Gelombang PHK Makin Besar di Singapura, 4.500 Orang Jadi Korban</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:56:08 +0700</t>
+          <t>Tue, 04 Aug 2026 12:14:37 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pedagang bendera di Jakarta mulai ramai menjelang HUT ke-81 RI, namun penjualan menurun.</t>
+          <t>Gelombang PHK di Singapura meningkat pada kuartal II-2026, mencapai 4.500 pekerja. Meski demikian, total lapangan kerja justru bertambah 10.700.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603046/musim-cuan-17-agustus-dimulai-pedagang-bendera-mulai-gelar-lapak</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603555/gelombang-phk-makin-besar-di-singapura-4-500-orang-jadi-korban</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pedagang-bendera-1785742448675_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/10/27/ilustrasi-kena-phk_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4016,28 +4016,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pameran Wastra Sultra Dorong Ekonomi Kreatif Perajin Lokal</t>
+          <t>LPEI Kucurkan US$ 8,5 Juta Danai Ekspor Gerbong Barang ke Selandia Baru</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:30:56 +0700</t>
+          <t>Tue, 04 Aug 2026 12:11:18 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pameran kain tenun dan baju adat Sultra di Museum Sultra menjadi upaya melestarikan wastra sekaligus mengenalkan kekayaan budaya daerah.</t>
+          <t>LPEI dukung PT INKA ekspor 340 unit Wagon ke Selandia Baru dengan fasilitas USD 8,5 juta. Sinergi ini perkuat industri strategis dan perekonomian nasional.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602729/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal</t>
+          <t>https://finance.detik.com/moneter/d-8603549/lpei-kucurkan-us-8-5-juta-danai-ekspor-gerbong-barang-ke-selandia-baru</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal-1785754770623_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eximbank-danai-ekspor-pt-inka-ke-selandia-baru-1785820259573_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4054,28 +4054,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Impor RI Naik Tajam, Ini Biang Keroknya</t>
+          <t>Alarm Berbunyi di Rusia, Bank-bank Mulai Krisis Uang Tunai!</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 12:03:30 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai impor Indonesia meningkat tajam pada Juni 2026 mencapai US$ 25,9 miliar atau naik 34,27%.</t>
+          <t>Bank-bank Rusia menghadapi tekanan likuiditas rubel, membatasi pembelian obligasi pemerintah. Defisit anggaran meningkat.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603040/impor-ri-naik-tajam-ini-biang-keroknya</t>
+          <t>https://finance.detik.com/moneter/d-8603535/alarm-berbunyi-di-rusia-bank-bank-mulai-krisis-uang-tunai</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/09/tanjung-priok-tetap-sibuk-di-tengah-tekanan-dolar-harapan-ekspor-menguat-1780979463918_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/01/ini-yang-bikin-warga-rusia-panik-serbu-atm-bank-buat-tarik-uang_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4087,33 +4087,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PSSI Cuan Rp 722 Miliar, Tetap Terbuka Bantuan dari Pemerintah</t>
+          <t>BSI dan Danantara Perkuat Ekosistem UMKM agar Pelaku Usaha Naik Kelas</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:30:30 +0700</t>
+          <t>Tue, 04 Aug 2026 11:51:53 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PSSI sukses mengumpulkan pendapatan fantastis Rp722 miliar. Angka tersebut sudah cukup buat PSSI, tetapi tetap terbuka jika ada tawaran bantuan pemerintah.</t>
+          <t>PT Bank Syariah Indonesia (BSI) dan Danantara memperkuat UMKM melalui 35 Sentra dan 4 UMKM Center, mendukung pembiayaan, digitalisasi, dan sertifikasi halal.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604319/pssi-cuan-rp-722-miliar-tetap-terbuka-bantuan-dari-pemerintah</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603515/bsi-dan-danantara-perkuat-ekosistem-umkm-agar-pelaku-usaha-naik-kelas</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menpora-erick-thohir-1783676745865.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/direktur-utama-bsi-anggoro-eko-cahyo-1785820807840_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4125,33 +4125,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Indonesia Punya 2 Srikandi di Asia Cross Country Rally 2026</t>
+          <t>Tak Mau Kehilangan Guru Berkualitas, Singapura Naikkan Gaji hingga 9%</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:25:00 +0700</t>
+          <t>Tue, 04 Aug 2026 11:48:03 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Asia Cross Country Rally 2026 rupanya menarik minat para pereli wanita Indonesia. Mereka adalah Lody Natasha dan Satsy Laksamana.</t>
+          <t>Pemerintah Singapura akan menaikkan gaji guru dan tenaga pendidik 2-9% mulai 1 Oktober 2026, untuk menarik dan mempertahankan tenaga pendidik berkualitas.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604616/indonesia-punya-2-srikandi-di-asia-cross-country-rally-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603511/tak-mau-kehilangan-guru-berkualitas-singapura-naikkan-gaji-hingga-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/lody-natasha-dan-satsy-laksamana-1785860860805_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/21/pendidikan-nilai-1750494841214_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4163,33 +4163,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
+          <t>Trump Bantu Jepang Selamatkan Yen, Apa Untungnya buat AS?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:00:00 +0700</t>
+          <t>Tue, 04 Aug 2026 11:43:30 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Final Piala Presiden 2026 akhirnya mendapatkan kontestannya. Persib Bandung vs Persebaya Surabaya akan tersaji di partai puncak.</t>
+          <t>Presiden AS Donald Trump mengatakan, intervensi ini dilakukan atas permintaan pemerintah Jepang.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604606/final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603507/trump-bantu-jepang-selamatkan-yen-apa-untungnya-buat-as</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492015_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4201,33 +4201,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Piala AFF: Indonesia Dijagokan Taklukkan Singapura, Lolos ke Semifinal</t>
+          <t>Peresmian Pabrik Baterai EV di Karawang Tinggal Tunggu Jadwal Prabowo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:40:30 +0700</t>
+          <t>Tue, 04 Aug 2026 11:11:33 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Timnas Indonesia akan dijamu Timnas Singapura dalam laga penentuan tiket ke semifinal Piala AFF 2026. Garuda dijagokan mengalahkan The Lions.</t>
+          <t>Menteri ESDM Bahlil mengumumkan pabrik baterai listrik di Karawang siap diresmikan, tinggal menunggu jadwal Presiden. Investasi mencapai US$5,9 miliar.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604294/piala-aff-indonesia-dijagokan-taklukkan-singapura-lolos-ke-semifinal</t>
+          <t>https://finance.detik.com/energi/d-8603463/peresmian-pabrik-baterai-ev-di-karawang-tinggal-tunggu-jadwal-prabowo</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/menteri-esdm-bahlil-lahadalia-1784186781817_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4239,33 +4239,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cara Memen Agar Mobilnya Siap Taklukkan Medan Berat AXCR 2026</t>
+          <t>RI-Thailand Sepakat Genjot Perdagangan Tembus Rp 360 Triliun</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:25:00 +0700</t>
+          <t>Tue, 04 Aug 2026 11:02:03 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Memen Harianto akan membawa nama Indonesia di Asia Cross Country Rally (AXCR) 2026. Dia melakukan persiapan secara maksimal, terutama untuk mobilnya.</t>
+          <t>Indonesia dan Thailand sepakat menggenjot perdagangan dengan target Rp 360 triliun pada 2030.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604594/cara-memen-agar-mobilnya-siap-taklukkan-medan-berat-axcr-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603447/ri-thailand-sepakat-genjot-perdagangan-tembus-rp-360-triliun</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/memen-harianto-1785860948781_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/presiden-prabowo-subianto-menggelar-jamuan-santap-malam-resmi-untuk-pm-kerajaan-thailand-anutin-charnvirakul-foto-rusman-biro--1785806274579_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4277,33 +4277,33 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Persebaya Vs Arema: Bajul Ijo Menang 1-0, Lolos ke Final Piala Presiden</t>
+          <t>Mengenang Burhanuddin 'Bur' Maras, Tokoh Migas dan Pendiri Lekom Maras</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:17:39 +0700</t>
+          <t>Tue, 04 Aug 2026 11:00:37 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya meraih kemenangan 1-0 atas Arema FC di semifinal Piala Presiden 2026. Persebaya lolos ke final untuk menghadapi Persib Bandung.</t>
+          <t>Burhanuddin 'Bur' Maras, pendiri PT Lekom Maras, wafat di usia 90 tahun. Ia dikenal sebagai tokoh penting di industri perminyakan dan politik Indonesia.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604584/persebaya-vs-arema-bajul-ijo-menang-1-0-lolos-ke-final-piala-presiden</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603445/mengenang-burhanuddin-bur-maras-tokoh-migas-dan-pendiri-lekom-maras</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/burhanuddin-bur-maras-1785815972293.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4315,33 +4315,33 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hasil Piala AFF 2026: Thailand Atasi Filipina 1-0</t>
+          <t>Krisis Iran Memanas, Warga Teheran Tetap Jalani Aktivitas di Tengah Ketegangan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:58:26 +0700</t>
+          <t>Tue, 04 Aug 2026 11:00:34 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Thailand melanjutkan start positifnya di Piala AFF 2026. Tim War Elephants menang tipis 1-0 atas Filipina dan menguasai pucuk klasemen Grup B.</t>
+          <t>Krisis Iran menjadi sorotan dunia. Di tengah ketegangan politik dan hubungan internasional, warga Teheran tetap menjalani aktivitas sehari-hari.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604566/hasil-piala-aff-2026-thailand-atasi-filipina-1-0</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8602911/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan-1785761340975_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4353,33 +4353,33 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vicario dan Suzuki Diincar Juventus, Buffon Bilang Begini!</t>
+          <t>Buruh Batalkan Rencana Demo di DPR Senin Depan, Takut Ada Penyusup</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:45:05 +0700</t>
+          <t>Tue, 04 Aug 2026 10:48:57 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Juventus dikabarkan menjadikan Guglielmo Vicario dan Zion Suzuki sebagai kandidat kiper anyar. Bagaimana menurut Gianluigi Buffon?</t>
+          <t>KBPBI menunda aksi unjuk rasa di depan DPR untuk mendesak RUU Ketenagakerjaan. Keputusan diambil untuk menghindari potensi penyusup dan menjaga ketertiban.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604289/vicario-dan-suzuki-diincar-juventus-buffon-bilang-begini</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603423/buruh-batalkan-rencana-demo-di-dpr-senin-depan-takut-ada-penyusup</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/04/gianluigi-buffon_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/presiden-konfederasi-serikat-pekerja-seluruh-indonesia-kspsi-andi-gani-1758528973493_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4391,33 +4391,33 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pelajaran dari Singapura Sukses Antar Vietnam Cukur Indonesia</t>
+          <t>Setelah Naik Beruntun, Harga Emas Antam Akhirnya Turun</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:30:15 +0700</t>
+          <t>Tue, 04 Aug 2026 09:51:02 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vietnam banyak belajar dari hasil imbang melawan Singapura. Pemilihan strategi yang tepat sukses antar Vietnam mencukur Timnas Indonesia 3-0.</t>
+          <t>Harga emas Antam hari ini turun Rp 7.000 per gram menjadi Rp 2.603.000. Rincian harga emas dari 0,5 gram hingga 1.000 gram juga disajikan.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604285/pelajaran-dari-singapura-sukses-antar-vietnam-cukur-indonesia</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603360/setelah-naik-beruntun-harga-emas-antam-akhirnya-turun</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/13/emas-batangan-1763011692898_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4429,33 +4429,33 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PBSI Cari Pasangan untuk Adnan Maulana</t>
+          <t>Mitratel Cetak Laba Rp 1,11 T</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:20:37 +0700</t>
+          <t>Tue, 04 Aug 2026 09:48:19 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PP PBSI masih mencari pasangan untuk Adnan Maulana. Itu setelah rekan tandemnya yang lama, Indah Cahya Sari Jamil, dipasangkan dengan pemain lain.</t>
+          <t>PT Dayamitra Telekomunikasi Tbk (MTEL) alias Mitratel membukukan kinerja positif hingga akhir Juni 2026.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8604509/pbsi-cari-pasangan-untuk-adnan-maulana</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603358/mitratel-cetak-laba-rp-1-11-t</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/02/adnan-maulanaindah-cahya-sari-jamil-1780382604246_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/17/potret-tower-mitratel-yang-manfaatkan-panel-surya-5_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4467,33 +4467,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Matthijs de Ligt Belum Bisa Gabung ke MU</t>
+          <t>Dolar AS Tembus Rp 18.000 Pagi Ini</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:15:40 +0700</t>
+          <t>Tue, 04 Aug 2026 09:33:38 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Manchester United masih belum bisa diperkuat bek tengahnya, Matthijs de Ligt. Dirinya masih belum pulih setelah operasi cedera punggung.</t>
+          <t>Dolar AS bergerak menguat 0,06% ke level Rp 18.000 di awal pembukaan perdagangan.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603854/matthijs-de-ligt-belum-bisa-gabung-ke-mu</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603345/dolar-as-tembus-rp-18-000-pagi-ini</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/07/matthijs-de-ligt-1775546584882.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338333_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4505,33 +4505,33 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jelang Lawan Singapura, Timnas Indonesia Butuh Pemulihan Moral</t>
+          <t>IHSG Dibuka Menguat ke 6.255</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 09:29:37 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Timnas Indonesia sangat terpukul usai kalah 0-3 dari Vietnam. Skuad Garuda kini harus memulihkan moral jelang melawan Singapura.</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604284/jelang-lawan-singapura-timnas-indonesia-butuh-pemulihan-moral</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603339/ihsg-dibuka-menguat-ke-6-255</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/30/ihsg-rebound-usai-dua-hari-anjlok-seiring-pengunduran-diri-dirut-bei-1769748663323_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4543,33 +4543,33 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jorge Martin Tak Sabar Lanjutkan Duel Sengit Perebutan Gelar MotoGP 2026!</t>
+          <t>Empat Sistem Karantina Diperkuat, Ekspor Ikan Hias Indonesia Makin Mendunia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:50:40 +0700</t>
+          <t>Tue, 04 Aug 2026 09:00:23 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jorge Martin antusias menatap paruh kedua MotoGP 2026. Ia yakin persaingan gelar juara dunia akan semakin sengit karena lima pebalap hanya terpaut 24 poin.</t>
+          <t>Barantin memperkuat empat sistem karantina untuk meningkatkan daya saing dan kepercayaan pasar global terhadap ikan hias Indonesia.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604324/jorge-martin-tak-sabar-lanjutkan-duel-sengit-perebutan-gelar-motogp-2026</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8602609/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/moto-motogp-ned-1782675298213_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia-1785750239859_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4581,33 +4581,33 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mulai Tahun Depan Piala Presiden untuk Timnas Indonesia, Tidak Lagi Klub</t>
+          <t>Bos BGN Buka Suara soal Putusan MK Anggaran MBG dan Pendidikan Dipisah</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:45:15 +0700</t>
+          <t>Tue, 04 Aug 2026 08:50:38 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ketum PSSI Erick Thohir mengungkapkan Piala Presiden mulai tahun depan tidak lagi menjadi turnamen pramusim klub, melainkan jadi agenda Timnas Indonesia.</t>
+          <t>Kami ini adalah lembaga operasional. Tentu saja kami akan melaksanakan apapun kebijakan dari pemerintah, kata Sudaryono.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604194/mulai-tahun-depan-piala-presiden-untuk-timnas-indonesia-tidak-lagi-klub</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603305/bos-bgn-buka-suara-soal-putusan-mk-anggaran-mbg-dan-pendidikan-dipisah</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053334_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4619,33 +4619,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kovacic: Anderson Bikin Lini Tengah Man City Lebih Bertenaga</t>
+          <t>TLKM Catat Kinerja Semester I-2026, BUVA dan TAPG Umumkan Aksi Korporasi</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:30:50 +0700</t>
+          <t>Tue, 04 Aug 2026 08:45:59 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mateo Kovacic antusias dengan Elliott Anderson, meski itu juga berarti persaingan lini tengah Manchester City kian ketat. Ia yakin tim makin kuat.</t>
+          <t>TLKM membukukan pendapatan Rp75,9 triliun dan laba Rp10,6 triliun pada semester I-2026. BUVA siapkan rights issue, sementara TAPG tetapkan dividen interim.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604197/kovacic-anderson-bikin-lini-tengah-man-city-lebih-bertenaga</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603300/tlkm-catat-kinerja-semester-i-2026-buva-dan-tapg-umumkan-aksi-korporasi</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/29/elliott-anderson-1764354213557_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bursa-dan-valas-1785806578-1785806579142.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4657,33 +4657,33 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Usai Indonesia Dihajar Vietnam, Hubner Saling Sindir dengan Do Hoang Hen</t>
+          <t>Trump Tak Suka Exxon &amp;amp; Chevron Untung Gede Gara-gara Harga Minyak Tinggi</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:15:00 +0700</t>
+          <t>Tue, 04 Aug 2026 08:17:17 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dihajar Timnas Vietnam dalam laga lanjutan Piala AFF 2026. Justin Hubner saling sindir dengan pemain Golden Star Warriors, Do Hoang Hen.</t>
+          <t>Mereka meraup terlalu banyak uang dari kelangkaan ini. Saya tidak menyukainya, ujar Trump.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604196/usai-indonesia-dihajar-vietnam-hubner-saling-sindir-dengan-do-hoang-hen</t>
+          <t>https://finance.detik.com/energi/d-8603261/trump-tak-suka-exxon-chevron-untung-gede-gara-gara-harga-minyak-tinggi</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513456_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4695,33 +4695,33 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Buffon Percaya sama Mancini, Semoga Italia Lolos ke Piala Dunia</t>
+          <t>Tips Aman Pakai QRIS agar Terhindar dari Penipuan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:00:40 +0700</t>
+          <t>Tue, 04 Aug 2026 08:05:09 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sepakbola Italia bergejolak belakangan ini dalam penunjukan pelatih baru. Buffon mau drama itu berakhir, percayakan ke juru taktik baru Roberto Mancini.</t>
+          <t>QRIS adalah metode pembayaran digital praktis. Pelajari tips aman bertransaksi, cara menggunakan QRIS, dan cara mengenali penipuan untuk keamanan Anda.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604208/buffon-percaya-sama-mancini-semoga-italia-lolos-ke-piala-dunia</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8602406/tips-aman-pakai-qris-agar-terhindar-dari-penipuan</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/03/gianluigi-buffon-1748885612603.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/tips-aman-pakai-qris-agar-terhindar-dari-penipuan-1785745583872.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4733,33 +4733,33 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Marco Bezzecchi Belum 100%, tapi Siap Comeback di MotoGP Inggris 2026!</t>
+          <t>Pernak-pernik HUT Ke-81 RI Mulai Diburu di Pasar Asemka</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:50:50 +0700</t>
+          <t>Tue, 04 Aug 2026 08:00:44 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Marco Bezzecchi siap kembali balapan di MotoGP Inggris 2026 meski mengaku belum pulih 100 persen usai menjalani operasi tulang selangka dan lutut.</t>
+          <t>Permintaan pernak-pernik kemerdekaan mulai meningkat menjelang HUT Ke-81 RI. Pedagang Pasar Asemka mencatat penjualan naik sekitar 20 persen sejak akhir Juli.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604281/marco-bezzecchi-belum-100-tapi-siap-comeback-di-motogp-inggris-2026</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8601820/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/15/motor-motogp-germany-1784050516185_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka-1785728519984_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4771,33 +4771,33 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vietnam 'Oper' Tekanan ke Indonesia</t>
+          <t>KSP &amp;amp; Bahlil  Buka Suara soal Ekspor 'Harta Karun' RI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:40:30 +0700</t>
+          <t>Tue, 04 Aug 2026 07:25:00 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vietnam datang dengan tekanan dan kini melemparnya ke Indonesia. Mampukah skuad Garuda merespons tekanan itu dan keluar dari posisi terjepit.</t>
+          <t>Kantor Staf Presiden (KSP) buka suara terkait soal harta karun Indonesia yakni logam tanah jarang.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604184/vietnam-oper-tekanan-ke-indonesia</t>
+          <t>https://finance.detik.com/energi/d-8603108/ksp-bahlil-buka-suara-soal-ekspor-harta-karun-ri</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/09/logam-tanah-jarang-jadi-harta-karun-yang-diincar-dunia-3_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4809,33 +4809,33 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Liverpool Enggan Jual Gakpo, tapi Kalau Tottenham Kasih Harga Bagus...</t>
+          <t>Musim Cuan 17 Agustus Dimulai, Pedagang Bendera Mulai Gelar Lapak</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:20:45 +0700</t>
+          <t>Tue, 04 Aug 2026 06:56:08 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur meminati Cody Gakpo dari Liverpool. The Reds mau mempertahankan sang winger, tapi bakal goyah kalau dikasih harga bagus.</t>
+          <t>Pedagang bendera di Jakarta mulai ramai menjelang HUT ke-81 RI, namun penjualan menurun.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604186/liverpool-enggan-jual-gakpo-tapi-kalau-tottenham-kasih-harga-bagus</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603046/musim-cuan-17-agustus-dimulai-pedagang-bendera-mulai-gelar-lapak</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/05/cody-gakpo-1754352181260.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pedagang-bendera-1785742448675_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4847,33 +4847,33 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Detak Jantung Marc Marquez Bisa Ungkap Kans Juara MotoGP 2026</t>
+          <t>Pameran Wastra Sultra Dorong Ekonomi Kreatif Perajin Lokal</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:10:20 +0700</t>
+          <t>Tue, 04 Aug 2026 06:30:56 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Detak jantung Marc Marquez saat MotoGP Inggris diyakini bisa menjadi indikator keberhasilan pemulihan fisiknya terkait kans mengejar gelar dunia MotoGP 2026.</t>
+          <t>Pameran kain tenun dan baju adat Sultra di Museum Sultra menjadi upaya melestarikan wastra sekaligus mengenalkan kekayaan budaya daerah.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604170/detak-jantung-marc-marquez-bisa-ungkap-kans-juara-motogp-2026</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8602729/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-1783860046236_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal-1785754770623_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4885,33 +4885,33 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>John Herdman: Indonesia Asyik di Depan, Jadi Lupa Pertahanan</t>
+          <t>Impor RI Naik Tajam, Ini Biang Keroknya</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:00:50 +0700</t>
+          <t>Tue, 04 Aug 2026 05:55:02 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pelatih Timnas Indonesia John Herdman menyebut timnya terlalu asyik main di depan saat jumpa Vietnam. Hasilnya timnya malah kecolongan di lini pertahanan.</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai impor Indonesia meningkat tajam pada Juni 2026 mencapai US$ 25,9 miliar atau naik 34,27%.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604183/john-herdman-indonesia-asyik-di-depan-jadi-lupa-pertahanan</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603040/impor-ri-naik-tajam-ini-biang-keroknya</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/27/gaya-nyentrik-john-herdman-kawal-timnas-garuda-1774628369095.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/09/tanjung-priok-tetap-sibuk-di-tengah-tekanan-dolar-harapan-ekspor-menguat-1780979463918_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Singapura Vs Indonesia: Ulangan Situasi di Manila Sedekade Lalu</t>
+          <t>PSSI Cuan Rp 722 Miliar, Tetap Terbuka Bantuan dari Pemerintah</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:40:45 +0700</t>
+          <t>Tue, 04 Aug 2026 23:30:30 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Indonesia menjalani laga hidup dan mati melawan Singapura di Piala AFF 2026. Laga ini menjadi ulangan persaingan Garuda melawan The Lions sedekade lalu.</t>
+          <t>PSSI sukses mengumpulkan pendapatan fantastis Rp722 miliar. Angka tersebut sudah cukup buat PSSI, tetapi tetap terbuka jika ada tawaran bantuan pemerintah.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603914/singapura-vs-indonesia-ulangan-situasi-di-manila-sedekade-lalu</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604319/pssi-cuan-rp-722-miliar-tetap-terbuka-bantuan-dari-pemerintah</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/11/26/54e9d3f7-5e6d-46d8-b5d2-e2d0149535a8_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menpora-erick-thohir-1783676745865.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4966,28 +4966,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Malut United Resmi Ganti Nama Jadi Java United, Pindah Markas ke Semarang</t>
+          <t>Indonesia Punya 2 Srikandi di Asia Cross Country Rally 2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:30:00 +0700</t>
+          <t>Tue, 04 Aug 2026 23:25:00 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Malut United resmi berganti nama menjadi Java United dan memindahkan markas dari Ternate ke Semarang.</t>
+          <t>Asia Cross Country Rally 2026 rupanya menarik minat para pereli wanita Indonesia. Mereka adalah Lody Natasha dan Satsy Laksamana.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604279/malut-united-resmi-ganti-nama-jadi-java-united-pindah-markas-ke-semarang</t>
+          <t>https://sport.detik.com/sport-lain/d-8604616/indonesia-punya-2-srikandi-di-asia-cross-country-rally-2026</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/java-united-1785770401869_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/lody-natasha-dan-satsy-laksamana-1785860860805_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5004,28 +5004,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Chelsea Mulai Bersih-bersih</t>
+          <t>Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:20:15 +0700</t>
+          <t>Tue, 04 Aug 2026 23:00:00 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chelsea punya 40 pemain di dalam skuadnya. Bursa transfer musim panas 2026 masih buka sampai 1 September, Si Biru kini saatnya bersih-bersih.</t>
+          <t>Final Piala Presiden 2026 akhirnya mendapatkan kontestannya. Persib Bandung vs Persebaya Surabaya akan tersaji di partai puncak.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603920/chelsea-mulai-bersih-bersih</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604606/final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/09/chelsea-1778261458229.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492015_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5042,28 +5042,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RI Bawa Pulang 15 Medali dari Kejuaraan Asia MMA, Kini Fokus Asian Games 2026</t>
+          <t>Piala AFF: Indonesia Dijagokan Taklukkan Singapura, Lolos ke Semifinal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:10:25 +0700</t>
+          <t>Tue, 04 Aug 2026 22:40:30 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tim MMA Indonesia meraih 15 medali, termasuk lima emas, di GAMMA Asian Championships 2026.</t>
+          <t>Timnas Indonesia akan dijamu Timnas Singapura dalam laga penentuan tiket ke semifinal Piala AFF 2026. Garuda dijagokan mengalahkan The Lions.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604192/ri-bawa-pulang-15-medali-dari-kejuaraan-asia-mma-kini-fokus-asian-games-2026</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604294/piala-aff-indonesia-dijagokan-taklukkan-singapura-lolos-ke-semifinal</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gamma-asian-championships-2026-1785838947680_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5080,28 +5080,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Erick Thohir: Saya Tetap Percaya pada John Herdman</t>
+          <t>Cara Memen Agar Mobilnya Siap Taklukkan Medan Berat AXCR 2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 22:25:00 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Timnas Indonesia kalah 0-3 dari Vietnam, kans ke semifinal Piala AFF 2026 terancam. Ketum PSSI Erick Thohir membela pelatih John Herdman.</t>
+          <t>Memen Harianto akan membawa nama Indonesia di Asia Cross Country Rally (AXCR) 2026. Dia melakukan persiapan secara maksimal, terutama untuk mobilnya.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603911/erick-thohir-saya-tetap-percaya-pada-john-herdman</t>
+          <t>https://sport.detik.com/sport-lain/d-8604594/cara-memen-agar-mobilnya-siap-taklukkan-medan-berat-axcr-2026</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/13/selamat-datang-john-herdman-pelatih-baru-timnas-indonesia-1768277980430.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/memen-harianto-1785860948781_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5118,28 +5118,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dirumorkan Kembali ke Italia, Kovacic: Man City Masih Mengandalkanku</t>
+          <t>Persebaya Vs Arema: Bajul Ijo Menang 1-0, Lolos ke Final Piala Presiden</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:45:40 +0700</t>
+          <t>Tue, 04 Aug 2026 22:17:39 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mateo Kovacic dirumorkan kembali ke Italia, dengan kabar Juventus dan Inter Milan meminati. Tapi gelandang senior itu bilang masih diandalkan Manchester City.</t>
+          <t>Persebaya Surabaya meraih kemenangan 1-0 atas Arema FC di semifinal Piala Presiden 2026. Persebaya lolos ke final untuk menghadapi Persib Bandung.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603894/dirumorkan-kembali-ke-italia-kovacic-man-city-masih-mengandalkanku</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604584/persebaya-vs-arema-bajul-ijo-menang-1-0-lolos-ke-final-piala-presiden</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/20/wolverhampton-wanderers-manchester-city_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5156,28 +5156,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Persib Vs Persija: Menang 2-1, Maung Bandung ke Final Piala Presiden 2026</t>
+          <t>Hasil Piala AFF 2026: Thailand Atasi Filipina 1-0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:31:55 +0700</t>
+          <t>Tue, 04 Aug 2026 21:58:26 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Persib Bandung mengalahkan Persija Jakarta di semifinal Piala Presiden 2026. Pasukan Igor Tolic pun melaju ke final.</t>
+          <t>Thailand melanjutkan start positifnya di Piala AFF 2026. Tim War Elephants menang tipis 1-0 atas Filipina dan menguasai pucuk klasemen Grup B.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604212/persib-vs-persija-menang-2-1-maung-bandung-ke-final-piala-presiden-2026</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604566/hasil-piala-aff-2026-thailand-atasi-filipina-1-0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5194,28 +5194,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bagas Maulana Dinilai Cocok ke Ganda Campuran, Ini Alasannya</t>
+          <t>Vicario dan Suzuki Diincar Juventus, Buffon Bilang Begini!</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:20:10 +0700</t>
+          <t>Tue, 04 Aug 2026 21:45:05 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Pelatih ganda putra Antonius Budi Ariantho menjelaskan alasan Bagas Maulana dipindahkan ke sektor ganda campuran.</t>
+          <t>Juventus dikabarkan menjadikan Guglielmo Vicario dan Zion Suzuki sebagai kandidat kiper anyar. Bagaimana menurut Gianluigi Buffon?</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8604165/bagas-maulana-dinilai-cocok-ke-ganda-campuran-ini-alasannya</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604289/vicario-dan-suzuki-diincar-juventus-buffon-bilang-begini</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/12/bagas-maulana-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/04/gianluigi-buffon_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5232,28 +5232,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Vietnam Tahu Caranya Keluar dari Tekanan</t>
+          <t>Pelajaran dari Singapura Sukses Antar Vietnam Cukur Indonesia</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:15:15 +0700</t>
+          <t>Tue, 04 Aug 2026 21:30:15 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Vietnam datang ke Indonesia dengan tekanan besar usai ditahan Singapura. The Golden Star Warriors merespons dengan cemerlang.</t>
+          <t>Vietnam banyak belajar dari hasil imbang melawan Singapura. Pemilihan strategi yang tepat sukses antar Vietnam mencukur Timnas Indonesia 3-0.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603861/vietnam-tahu-caranya-keluar-dari-tekanan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604285/pelajaran-dari-singapura-sukses-antar-vietnam-cukur-indonesia</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5270,28 +5270,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dear Liverpool, Ini Isak yang Baru</t>
+          <t>PBSI Cari Pasangan untuk Adnan Maulana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:00:25 +0700</t>
+          <t>Tue, 04 Aug 2026 21:20:37 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Alexander Isak mengaku sudah pulih 100 persen. Sang striker siap berikan yang terbaik buat Liverpool di musim baru!</t>
+          <t>PP PBSI masih mencari pasangan untuk Adnan Maulana. Itu setelah rekan tandemnya yang lama, Indah Cahya Sari Jamil, dipasangkan dengan pemain lain.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603859/dear-liverpool-ini-isak-yang-baru</t>
+          <t>https://sport.detik.com/raket/d-8604509/pbsi-cari-pasangan-untuk-adnan-maulana</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/alexander-isak-1778251850354.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/02/adnan-maulanaindah-cahya-sari-jamil-1780382604246_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5308,28 +5308,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Timnas Indonesia Masih Berani Main High Pressing, John?</t>
+          <t>Matthijs de Ligt Belum Bisa Gabung ke MU</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:40:40 +0700</t>
+          <t>Tue, 04 Aug 2026 21:15:40 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Timnas Indonesia sangat buruk dalam transisi bertahan dengan permainan high pressing. Pelatih John Herdman apakah akan mengubah cara bermain Garuda?</t>
+          <t>Manchester United masih belum bisa diperkuat bek tengahnya, Matthijs de Ligt. Dirinya masih belum pulih setelah operasi cedera punggung.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603770/timnas-indonesia-masih-berani-main-high-pressing-john</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603854/matthijs-de-ligt-belum-bisa-gabung-ke-mu</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/07/matthijs-de-ligt-1775546584882.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5346,28 +5346,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Piala AFF: Indonesia Pernah Lima Kali Gagal ke Semifinal</t>
+          <t>Jelang Lawan Singapura, Timnas Indonesia Butuh Pemulihan Moral</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:20:15 +0700</t>
+          <t>Tue, 04 Aug 2026 21:00:30 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Timnas Indonesia sedang di ujung tanduk di Piala AFF 2026. Sepanjang sejarah pesta sepakbola ASEAN, Skuad Garuda pernah lima kali gagal ke semifinal.</t>
+          <t>Timnas Indonesia sangat terpukul usai kalah 0-3 dari Vietnam. Skuad Garuda kini harus memulihkan moral jelang melawan Singapura.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603776/piala-aff-indonesia-pernah-lima-kali-gagal-ke-semifinal</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604284/jelang-lawan-singapura-timnas-indonesia-butuh-pemulihan-moral</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5384,28 +5384,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Welbeck Kemarin Hobi Jebol Chelsea, Kini Jagoan Baru The Blues</t>
+          <t>Jorge Martin Tak Sabar Lanjutkan Duel Sengit Perebutan Gelar MotoGP 2026!</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:00:15 +0700</t>
+          <t>Tue, 04 Aug 2026 20:50:40 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chelsea resmi mendatangkan Danny Welbeck. Sang striker veteran lumayan hobi jebol gawang The Blues dulu, tapi kini diharapkan jadi jagoan.</t>
+          <t>Jorge Martin antusias menatap paruh kedua MotoGP 2026. Ia yakin persaingan gelar juara dunia akan semakin sengit karena lima pebalap hanya terpaut 24 poin.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8603780/welbeck-kemarin-hobi-jebol-chelsea-kini-jagoan-baru-the-blues</t>
+          <t>https://sport.detik.com/moto-gp/d-8604324/jorge-martin-tak-sabar-lanjutkan-duel-sengit-perebutan-gelar-motogp-2026</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/danny-welbeckchelseabursa-transfer-chelsea-1785602779561.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/moto-motogp-ned-1782675298213_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5422,28 +5422,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ini Sebab PBSI Belum Rilis Daftar Pemain di Asian Games</t>
+          <t>Mulai Tahun Depan Piala Presiden untuk Timnas Indonesia, Tidak Lagi Klub</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:50:00 +0700</t>
+          <t>Tue, 04 Aug 2026 20:45:15 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nama-nama pebulutangkis Indonesia yang akan diturunkan di Asian Games 2026 belum final. PBSI masih akan melihat hasil dari Kejuaraan Dunia pada 17-23 Agustus.</t>
+          <t>Ketum PSSI Erick Thohir mengungkapkan Piala Presiden mulai tahun depan tidak lagi menjadi turnamen pramusim klub, melainkan jadi agenda Timnas Indonesia.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8603931/ini-sebab-pbsi-belum-rilis-daftar-pemain-di-asian-games</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604194/mulai-tahun-depan-piala-presiden-untuk-timnas-indonesia-tidak-lagi-klub</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/26/logo-pbsi.webp?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5460,28 +5460,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>John Herdman ke Suporter: Kita Menang Bersama, Kalah Juga Bersama</t>
+          <t>Kovacic: Anderson Bikin Lini Tengah Man City Lebih Bertenaga</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:40:25 +0700</t>
+          <t>Tue, 04 Aug 2026 20:30:50 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dihajar Timnas Vietnam saat menjalani laga kandang di Piala AFF 2026. John Herdman berjanji Skuad Garuda akan bangkit.</t>
+          <t>Mateo Kovacic antusias dengan Elliott Anderson, meski itu juga berarti persaingan lini tengah Manchester City kian ketat. Ia yakin tim makin kuat.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603741/john-herdman-ke-suporter-kita-menang-bersama-kalah-juga-bersama</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604197/kovacic-anderson-bikin-lini-tengah-man-city-lebih-bertenaga</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/31/herdman-janji-bangkit-usai-kekalahan-targetkan-indonesia-ke-piala-dunia-2030-1774891836257_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/29/elliott-anderson-1764354213557_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5498,28 +5498,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Awas MU, Bayern Munich Minati Benjamin Sesko</t>
+          <t>Usai Indonesia Dihajar Vietnam, Hubner Saling Sindir dengan Do Hoang Hen</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:20:10 +0700</t>
+          <t>Tue, 04 Aug 2026 20:15:00 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bayern Munich menaruh minat pada striker Man United, Benjamin Sesko. Tapi Bayern enggak mau buru-buru merekrutnya dulu, mungkin beberapa tahun mendatang nanti.</t>
+          <t>Timnas Indonesia dihajar Timnas Vietnam dalam laga lanjutan Piala AFF 2026. Justin Hubner saling sindir dengan pemain Golden Star Warriors, Do Hoang Hen.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603737/awas-mu-bayern-munich-minati-benjamin-sesko</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604196/usai-indonesia-dihajar-vietnam-hubner-saling-sindir-dengan-do-hoang-hen</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/02/benjamin-sesko-1772389311489.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513456_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5536,28 +5536,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Viet Anh Berdarah-Darah untuk Tuntaskan Dendam ke Indonesia</t>
+          <t>Buffon Percaya sama Mancini, Semoga Italia Lolos ke Piala Dunia</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:00:45 +0700</t>
+          <t>Tue, 04 Aug 2026 20:00:40 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vietnam sukses membabat Indonesia 3-0 dalam laga Grup A Piala AFF 2026. Bek Bui Hoang Viet Anh sangat puas Golden Star Warriors berhasil balas dendam.</t>
+          <t>Sepakbola Italia bergejolak belakangan ini dalam penunjukan pelatih baru. Buffon mau drama itu berakhir, percayakan ke juru taktik baru Roberto Mancini.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603740/viet-anh-berdarah-darah-untuk-tuntaskan-dendam-ke-indonesia</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604208/buffon-percaya-sama-mancini-semoga-italia-lolos-ke-piala-dunia</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/03/gianluigi-buffon-1748885612603.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5574,28 +5574,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Asian Games 2026: Bulutangkis Beregu Putra Jadi Asa Indonesia Raih Emas</t>
+          <t>Marco Bezzecchi Belum 100%, tapi Siap Comeback di MotoGP Inggris 2026!</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:51:15 +0700</t>
+          <t>Tue, 04 Aug 2026 19:50:50 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chef de Mission Indonesia Todotua Pasaribu berharap bulutangkis bisa mendapatkan medali emas di Asian Games 2026. Secara khusus nomor ganda putra.</t>
+          <t>Marco Bezzecchi siap kembali balapan di MotoGP Inggris 2026 meski mengaku belum pulih 100 persen usai menjalani operasi tulang selangka dan lutut.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8603821/asian-games-2026-bulutangkis-beregu-putra-jadi-asa-indonesia-raih-emas</t>
+          <t>https://sport.detik.com/moto-gp/d-8604281/marco-bezzecchi-belum-100-tapi-siap-comeback-di-motogp-inggris-2026</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/06/ilustrasi-bulutangkis.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/15/motor-motogp-germany-1784050516185_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5612,28 +5612,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bermain Buruk, Indonesia Dipecundangi Vietnam!</t>
+          <t>Vietnam 'Oper' Tekanan ke Indonesia</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:44:50 +0700</t>
+          <t>Tue, 04 Aug 2026 19:40:30 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Apakah Indonesia bisa menjaga asa untuk tampil di semifinal Piala AFF 2026?</t>
+          <t>Vietnam datang dengan tekanan dan kini melemparnya ke Indonesia. Mampukah skuad Garuda merespons tekanan itu dan keluar dari posisi terjepit.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/sepakbola-indonesia/d-8603690/bermain-buruk-indonesia-dipecundangi-vietnam</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604184/vietnam-oper-tekanan-ke-indonesia</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detiksore-4-agustus-2026-1785825691822_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5650,28 +5650,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Marselino Ferdinan Tak Bisa Main di Piala AFF 2026!</t>
+          <t>Liverpool Enggan Jual Gakpo, tapi Kalau Tottenham Kasih Harga Bagus...</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:40:10 +0700</t>
+          <t>Tue, 04 Aug 2026 19:20:45 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kabar buruk menghampiri Timnas Indonesia di tengah gelaran Piala AFF 2026. Marselino Ferdinan tak bisa memperkuat Skuad Garuda!</t>
+          <t>Tottenham Hotspur meminati Cody Gakpo dari Liverpool. The Reds mau mempertahankan sang winger, tapi bakal goyah kalau dikasih harga bagus.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603636/marselino-ferdinan-tak-bisa-main-di-piala-aff-2026</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604186/liverpool-enggan-jual-gakpo-tapi-kalau-tottenham-kasih-harga-bagus</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/12/marselino-ferdinan_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/05/cody-gakpo-1754352181260.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5688,28 +5688,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Usai Permalukan Indonesia, Vietnam Dapat Bonus Rp1,37 Miliar</t>
+          <t>Detak Jantung Marc Marquez Bisa Ungkap Kans Juara MotoGP 2026</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:20:10 +0700</t>
+          <t>Tue, 04 Aug 2026 19:10:20 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Timnas Vietnam mempermalukan Timnas Indonesia di Piala AFF 2026. Golden Star Warriors mendapat bonus 2 miliar dong atau setara Rp1,37 miliar.</t>
+          <t>Detak jantung Marc Marquez saat MotoGP Inggris diyakini bisa menjadi indikator keberhasilan pemulihan fisiknya terkait kans mengejar gelar dunia MotoGP 2026.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603633/usai-permalukan-indonesia-vietnam-dapat-bonus-rp1-37-miliar</t>
+          <t>https://sport.detik.com/moto-gp/d-8604170/detak-jantung-marc-marquez-bisa-ungkap-kans-juara-motogp-2026</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-1783860046236_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5726,28 +5726,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Presiden FIFA Batal Naik Gaji 500 Persen</t>
+          <t>John Herdman: Indonesia Asyik di Depan, Jadi Lupa Pertahanan</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:00:15 +0700</t>
+          <t>Tue, 04 Aug 2026 19:00:50 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Presiden FIFA Gianni Infantino diketahui bakal naik gaji 525 persen andai wacana jual saham Piala Dunia sukses. Wacana itu batal, nggak gaji naik deh!</t>
+          <t>Pelatih Timnas Indonesia John Herdman menyebut timnya terlalu asyik main di depan saat jumpa Vietnam. Hasilnya timnya malah kecolongan di lini pertahanan.</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603662/presiden-fifa-batal-naik-gaji-500-persen</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604183/john-herdman-indonesia-asyik-di-depan-jadi-lupa-pertahanan</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/16/gianni-infantino.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/27/gaya-nyentrik-john-herdman-kawal-timnas-garuda-1774628369095.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5764,28 +5764,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sebuah Perenungan Rizky Ridho</t>
+          <t>Singapura Vs Indonesia: Ulangan Situasi di Manila Sedekade Lalu</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:40 +0700</t>
+          <t>Tue, 04 Aug 2026 18:40:45 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rizky Ridho mengakui kesalahannya dalam kekalahan Indonesia dari Vietnam. Dia akan mencoba merenungkannya untuk berbenah di laga selanjutnya.</t>
+          <t>Indonesia menjalani laga hidup dan mati melawan Singapura di Piala AFF 2026. Laga ini menjadi ulangan persaingan Garuda melawan The Lions sedekade lalu.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603568/sebuah-perenungan-rizky-ridho</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603914/singapura-vs-indonesia-ulangan-situasi-di-manila-sedekade-lalu</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/11/26/54e9d3f7-5e6d-46d8-b5d2-e2d0149535a8_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5802,28 +5802,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bagas Maulana ke Ganda Campuran, Tandem sama Indah Cahya</t>
+          <t>Malut United Resmi Ganti Nama Jadi Java United, Pindah Markas ke Semarang</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:35:30 +0700</t>
+          <t>Tue, 04 Aug 2026 18:30:00 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PBSI kembali jajal kombinasi baru di sektor ganda campuran. Kali ini, Bagas Maulana dipasangkan dengan Indah Cahya Sari Jamil!</t>
+          <t>Malut United resmi berganti nama menjadi Java United dan memindahkan markas dari Ternate ke Semarang.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8603660/bagas-maulana-ke-ganda-campuran-tandem-sama-indah-cahya</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604279/malut-united-resmi-ganti-nama-jadi-java-united-pindah-markas-ke-semarang</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/22/fajarfikri-kalahkan-bagasleo-di-indonesia-masters-2026-1769070561744.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/java-united-1785770401869_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5840,28 +5840,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jika Arsenal Dapatkan Vinicius...</t>
+          <t>Chelsea Mulai Bersih-bersih</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:20:25 +0700</t>
+          <t>Tue, 04 Aug 2026 18:20:15 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Situasi Vinicius Jr di Madrid masih tanda tanya, rumor Arsenal mau merekrutnya juga terus mencuat. Wilshere bakal girang betul andai The Gunners mendapatkannya.</t>
+          <t>Chelsea punya 40 pemain di dalam skuadnya. Bursa transfer musim panas 2026 masih buka sampai 1 September, Si Biru kini saatnya bersih-bersih.</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603570/jika-arsenal-dapatkan-vinicius</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603920/chelsea-mulai-bersih-bersih</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/02/vinicius-jr.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/09/chelsea-1778261458229.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5878,28 +5878,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Indonesia Vs Vietnam: Sayap-sayap Lemah Garuda</t>
+          <t>RI Bawa Pulang 15 Medali dari Kejuaraan Asia MMA, Kini Fokus Asian Games 2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 18:10:25 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibenamkan Timnas Vietnam di Piala AFF 2026. Sayap-sayap Garuda terlihat lemah di hadapan Golden Star Warriors.</t>
+          <t>Tim MMA Indonesia meraih 15 medali, termasuk lima emas, di GAMMA Asian Championships 2026.</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603566/indonesia-vs-vietnam-sayap-sayap-lemah-garuda</t>
+          <t>https://sport.detik.com/sport-lain/d-8604192/ri-bawa-pulang-15-medali-dari-kejuaraan-asia-mma-kini-fokus-asian-games-2026</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gamma-asian-championships-2026-1785838947680_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5916,28 +5916,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Posisi di FIFA Terancam, Infantino Minta Dukungan Trump?</t>
+          <t>Erick Thohir: Saya Tetap Percaya pada John Herdman</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:40:25 +0700</t>
+          <t>Tue, 04 Aug 2026 18:00:10 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Posisi Gianni Infantino di FIFA terancam usai geger wacana jual saham Piala Dunia. Pria asal Swiss itu kabarnya meminta dukungan Presiden AS Donald Trump.</t>
+          <t>Timnas Indonesia kalah 0-3 dari Vietnam, kans ke semifinal Piala AFF 2026 terancam. Ketum PSSI Erick Thohir membela pelatih John Herdman.</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603451/posisi-di-fifa-terancam-infantino-minta-dukungan-trump</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603911/erick-thohir-saya-tetap-percaya-pada-john-herdman</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/presiden-as-donald-trump-1783299814038_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/13/selamat-datang-john-herdman-pelatih-baru-timnas-indonesia-1768277980430.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5954,28 +5954,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Balik Latihan di Madrid, Vinicius Segera Perpanjang Kontrak</t>
+          <t>Dirumorkan Kembali ke Italia, Kovacic: Man City Masih Mengandalkanku</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:20:30 +0700</t>
+          <t>Tue, 04 Aug 2026 17:45:40 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vinicius Jr dilaporkan segera memperpanjang kontraknya setelah sudah kembali berlatih dengan Real Madrid. Ia memutuskan bertahan di El Real.</t>
+          <t>Mateo Kovacic dirumorkan kembali ke Italia, dengan kabar Juventus dan Inter Milan meminati. Tapi gelandang senior itu bilang masih diandalkan Manchester City.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/liga-spanyol/d-8603450/balik-latihan-di-madrid-vinicius-segera-perpanjang-kontrak</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603894/dirumorkan-kembali-ke-italia-kovacic-man-city-masih-mengandalkanku</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/21/vinicius-jr-1768973038339_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/20/wolverhampton-wanderers-manchester-city_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5992,28 +5992,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>8 Data Fakta usai Indonesia Dihantam Vietnam: Bulan Madu Herdman Selesai</t>
+          <t>Persib Vs Persija: Menang 2-1, Maung Bandung ke Final Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:00:20 +0700</t>
+          <t>Tue, 04 Aug 2026 17:31:55 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Timnas Indonesia menelan kekalahan telak dari Timnas Vietnam di Piala AFF 2026. Bulan madu John Herdman bersama Skuad Garuda selesai.</t>
+          <t>Persib Bandung mengalahkan Persija Jakarta di semifinal Piala Presiden 2026. Pasukan Igor Tolic pun melaju ke final.</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603448/8-data-fakta-usai-indonesia-dihantam-vietnam-bulan-madu-herdman-selesai</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604212/persib-vs-persija-menang-2-1-maung-bandung-ke-final-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6030,28 +6030,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Flick: Dear Barca, Mana Striker Barunya Nih?</t>
+          <t>Bagas Maulana Dinilai Cocok ke Ganda Campuran, Ini Alasannya</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:40:10 +0700</t>
+          <t>Tue, 04 Aug 2026 17:20:10 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Belum ada juga pemain baru datang untuk menggantikan Robert Lewandowski. Pelatih Barcelona Hansi Flick mencoba sabar menunggu.</t>
+          <t>Pelatih ganda putra Antonius Budi Ariantho menjelaskan alasan Bagas Maulana dipindahkan ke sektor ganda campuran.</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603267/flick-dear-barca-mana-striker-barunya-nih</t>
+          <t>https://sport.detik.com/raket/d-8604165/bagas-maulana-dinilai-cocok-ke-ganda-campuran-ini-alasannya</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hansi-flick-1785806312405_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/12/bagas-maulana-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6068,28 +6068,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Bikin Pantun untuk Fermin Aldeguer &amp;amp; Alex Marquez, Dapatkan Saldo E-Wallet</t>
+          <t>Vietnam Tahu Caranya Keluar dari Tekanan</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:22:46 +0700</t>
+          <t>Tue, 04 Aug 2026 17:15:15 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ikuti kuis kreatif dari detikcom dan Bold Riders! Buat pantun lucu untuk Fermin Aldeguer atau Alex Marquez dan menangkan saldo e-wallet Rp 250 ribu!</t>
+          <t>Vietnam datang ke Indonesia dengan tekanan besar usai ditahan Singapura. The Golden Star Warriors merespons dengan cemerlang.</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8603482/bikin-pantun-untuk-fermin-aldeguer-alex-marquez-dapatkan-saldo-e-wallet</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603861/vietnam-tahu-caranya-keluar-dari-tekanan</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/la-bold-1785817343343.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6106,28 +6106,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Direktur RB Leipzig: Kata Siapa Diomande Sudah 'Here We Go'?</t>
+          <t>Dear Liverpool, Ini Isak yang Baru</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:20:45 +0700</t>
+          <t>Tue, 04 Aug 2026 17:00:25 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Yan Diomande sempat diklaim tinggal selangkah lagi gabung Real Madrid. Kabar itu dibantah keras petinggi RB Leipzig.</t>
+          <t>Alexander Isak mengaku sudah pulih 100 persen. Sang striker siap berikan yang terbaik buat Liverpool di musim baru!</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603249/direktur-rb-leipzig-kata-siapa-diomande-sudah-here-we-go</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603859/dear-liverpool-ini-isak-yang-baru</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/yann-diomande-1785778891457_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/alexander-isak-1778251850354.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6144,28 +6144,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Jadwal Semifinal Piala Presiden: Persib Vs Persija, Persebaya Vs Arema</t>
+          <t>Timnas Indonesia Masih Berani Main High Pressing, John?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:00:41 +0700</t>
+          <t>Tue, 04 Aug 2026 16:40:40 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Jadwal semifinal Piala Presiden 2026 mempertemukan Persib vs Persija dan Persebaya vs Arema. Simak jadwal semifinal hingga final.</t>
+          <t>Timnas Indonesia sangat buruk dalam transisi bertahan dengan permainan high pressing. Pelatih John Herdman apakah akan mengubah cara bermain Garuda?</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603340/jadwal-semifinal-piala-presiden-persib-vs-persija-persebaya-vs-arema</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603770/timnas-indonesia-masih-berani-main-high-pressing-john</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/12/980f4b19-e319-452f-bd84-74e7316325ce_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6182,28 +6182,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Liverpool Disarankan Pulangkan Alexander-Arnold</t>
+          <t>Piala AFF: Indonesia Pernah Lima Kali Gagal ke Semifinal</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:40:35 +0700</t>
+          <t>Tue, 04 Aug 2026 16:20:15 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Liverpool disarankan memulangkan Trent Alexander-Arnold yang kesulitan di Real Madrid. Umpan silang akurat dari TAA dinilai sangat dibutuhkan Alexander Isak.</t>
+          <t>Timnas Indonesia sedang di ujung tanduk di Piala AFF 2026. Sepanjang sejarah pesta sepakbola ASEAN, Skuad Garuda pernah lima kali gagal ke semifinal.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603306/liverpool-disarankan-pulangkan-alexander-arnold</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603776/piala-aff-indonesia-pernah-lima-kali-gagal-ke-semifinal</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/13/trent-alexander-arnold-1773385024632_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6220,28 +6220,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>John Herdman Rasakan Kekalahan Kedua Latih Indonesia</t>
+          <t>Welbeck Kemarin Hobi Jebol Chelsea, Kini Jagoan Baru The Blues</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:20:30 +0700</t>
+          <t>Tue, 04 Aug 2026 16:00:15 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Timnas Indonesia jadi bulan-bulanan Vietnam di Piala AFF 2026. Ini menjadi kekalahan kedua Garuda di bawah asuhan John Herdman.</t>
+          <t>Chelsea resmi mendatangkan Danny Welbeck. Sang striker veteran lumayan hobi jebol gawang The Blues dulu, tapi kini diharapkan jadi jagoan.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603299/john-herdman-rasakan-kekalahan-kedua-latih-indonesia</t>
+          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8603780/welbeck-kemarin-hobi-jebol-chelsea-kini-jagoan-baru-the-blues</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/john-herdman-1785718686520_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/danny-welbeckchelseabursa-transfer-chelsea-1785602779561.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6258,28 +6258,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Bernardo Silva Tak Masalah Mainkan Banyak Peran di Madrid</t>
+          <t>Ini Sebab PBSI Belum Rilis Daftar Pemain di Asian Games</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:00:20 +0700</t>
+          <t>Tue, 04 Aug 2026 15:50:00 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bernardo Silva siap dimainkan di berbagai posisi bersama Real Madrid. Ia punya kemampuan untuk memainkan sejumlah peran di lapangan.</t>
+          <t>Nama-nama pebulutangkis Indonesia yang akan diturunkan di Asian Games 2026 belum final. PBSI masih akan melihat hasil dari Kejuaraan Dunia pada 17-23 Agustus.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603262/bernardo-silva-tak-masalah-mainkan-banyak-peran-di-madrid</t>
+          <t>https://sport.detik.com/raket/d-8603931/ini-sebab-pbsi-belum-rilis-daftar-pemain-di-asian-games</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2288876689-1785802177577_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/26/logo-pbsi.webp?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6296,28 +6296,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Indonesia Dikalahkan Vietnam, John Herdman Minta Garuda Tetap Fokus</t>
+          <t>John Herdman ke Suporter: Kita Menang Bersama, Kalah Juga Bersama</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:40:30 +0700</t>
+          <t>Tue, 04 Aug 2026 15:40:25 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Timnas Indonesia kalah 0-3 dari Vietnam pada matchday ketiga Piala AFF 2026. Pelatih Garuda John Herdman meminta timnya untuk tetap fokus.</t>
+          <t>Timnas Indonesia dihajar Timnas Vietnam saat menjalani laga kandang di Piala AFF 2026. John Herdman berjanji Skuad Garuda akan bangkit.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603309/indonesia-dikalahkan-vietnam-john-herdman-minta-garuda-tetap-fokus</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603741/john-herdman-ke-suporter-kita-menang-bersama-kalah-juga-bersama</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/31/herdman-janji-bangkit-usai-kekalahan-targetkan-indonesia-ke-piala-dunia-2030-1774891836257_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6334,28 +6334,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ferran Mau Saja Bertahan di Barca Asalkan...</t>
+          <t>Awas MU, Bayern Munich Minati Benjamin Sesko</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:20:05 +0700</t>
+          <t>Tue, 04 Aug 2026 15:20:10 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ferran Torres tidak masalah jika akhirnya bertahan di Barcelona. Tapi, ada satu syarat yang harus dipenuhi Los Cules, apa itu?</t>
+          <t>Bayern Munich menaruh minat pada striker Man United, Benjamin Sesko. Tapi Bayern enggak mau buru-buru merekrutnya dulu, mungkin beberapa tahun mendatang nanti.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603308/ferran-mau-saja-bertahan-di-barca-asalkan</t>
+          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603737/awas-mu-bayern-munich-minati-benjamin-sesko</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ferran-torres-1785808347370_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/02/benjamin-sesko-1772389311489.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6372,28 +6372,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Persiapan Vietnam Biasa Saja, tapi Bisa Bantai Indonesia</t>
+          <t>Viet Anh Berdarah-Darah untuk Tuntaskan Dendam ke Indonesia</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 15:00:45 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Timnas Vietnam mengganyang Indonesia di Piala AFF 2026. Pelatih Kim Sang-sik mengaku tak mempersiapkan timnya secara khusus sebelum pertandingan.</t>
+          <t>Vietnam sukses membabat Indonesia 3-0 dalam laga Grup A Piala AFF 2026. Bek Bui Hoang Viet Anh sangat puas Golden Star Warriors berhasil balas dendam.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603248/persiapan-vietnam-biasa-saja-tapi-bisa-bantai-indonesia</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603740/viet-anh-berdarah-darah-untuk-tuntaskan-dendam-ke-indonesia</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/timnas-vietnam-1785766971799_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6410,28 +6410,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tinggalkan Madrid, Gonzalo Garcia Gabung Fulham</t>
+          <t>Asian Games 2026: Bulutangkis Beregu Putra Jadi Asa Indonesia Raih Emas</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:30:20 +0700</t>
+          <t>Tue, 04 Aug 2026 14:51:15 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Gonzalo Garcia resmi meninggalkan Real Madrid. Penyerang muda Spanyol itu melanjutkan kariernya bersama Fulham.</t>
+          <t>Chef de Mission Indonesia Todotua Pasaribu berharap bulutangkis bisa mendapatkan medali emas di Asian Games 2026. Secara khusus nomor ganda putra.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603244/tinggalkan-madrid-gonzalo-garcia-gabung-fulham</t>
+          <t>https://sport.detik.com/raket/d-8603821/asian-games-2026-bulutangkis-beregu-putra-jadi-asa-indonesia-raih-emas</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gonzalo-garcia-1785804604431_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/06/ilustrasi-bulutangkis.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6448,28 +6448,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Kualifikasi GTR Ultra Tutup 7 Agustus, Jangan Sampai Gagal Ikut Trail Run Ini</t>
+          <t>Bermain Buruk, Indonesia Dipecundangi Vietnam!</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:15:47 +0700</t>
+          <t>Tue, 04 Aug 2026 14:44:50 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kabar penting buat pelari trail, pendaftaran kualifikasi GTR Ultra 2026 resmi akan ditutup 7 Agustus 2026 pukul 23.30 WIB.</t>
+          <t>Apakah Indonesia bisa menjaga asa untuk tampil di semifinal Piala AFF 2026?</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sportstyle/d-8603071/kualifikasi-gtr-ultra-tutup-7-agustus-jangan-sampai-gagal-ikut-trail-run-ini</t>
+          <t>https://sport.detik.com/sepakbola/sepakbola-indonesia/d-8603690/bermain-buruk-indonesia-dipecundangi-vietnam</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/gtr-ultra-2026-1773216163821_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detiksore-4-agustus-2026-1785825691822_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6486,28 +6486,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Bantai Indonesia, Vietnam Lanjutkan Rekor Tak Terkalahkan Sejak 2024</t>
+          <t>Marselino Ferdinan Tak Bisa Main di Piala AFF 2026!</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 14:40:10 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vietnam melanjutkan catatan tak terkalahkan usai menumbangkan Indonesia. Golden Star Warriors tak terkalahkan dalam 21 laga terakhir.</t>
+          <t>Kabar buruk menghampiri Timnas Indonesia di tengah gelaran Piala AFF 2026. Marselino Ferdinan tak bisa memperkuat Skuad Garuda!</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603202/bantai-indonesia-vietnam-lanjutkan-rekor-tak-terkalahkan-sejak-2024</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603636/marselino-ferdinan-tak-bisa-main-di-piala-aff-2026</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/12/marselino-ferdinan_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6524,23 +6524,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Nguyen Hai Long Bobol Indonesia, Pamer Patch Emas Vietnam</t>
+          <t>Usai Permalukan Indonesia, Vietnam Dapat Bonus Rp1,37 Miliar</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:30:40 +0700</t>
+          <t>Tue, 04 Aug 2026 14:20:10 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Pemain Vietnam Nguyen Hai Long membobol gawang Timnas Indonesia. Dia merayakan golnya dengan memamerkan patch emas tanda juara bertahan Piala AFF.</t>
+          <t>Timnas Vietnam mempermalukan Timnas Indonesia di Piala AFF 2026. Golden Star Warriors mendapat bonus 2 miliar dong atau setara Rp1,37 miliar.</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603197/nguyen-hai-long-bobol-indonesia-pamer-patch-emas-vietnam</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603633/usai-permalukan-indonesia-vietnam-dapat-bonus-rp1-37-miliar</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6562,28 +6562,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Henderson Pilih Chelsea karena Xabi Alonso</t>
+          <t>Presiden FIFA Batal Naik Gaji 500 Persen</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 14:00:15 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Nama besar Xabi Alonso di sepakbola tentu jadi magnet untuk banyak pesepakbola, tak terkecuali Jordan Henderson. Alonso jadi alasannya gabung Chelsea.</t>
+          <t>Presiden FIFA Gianni Infantino diketahui bakal naik gaji 525 persen andai wacana jual saham Piala Dunia sukses. Wacana itu batal, nggak gaji naik deh!</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603196/henderson-pilih-chelsea-karena-xabi-alonso</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603662/presiden-fifa-batal-naik-gaji-500-persen</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jordan-henderson-1785800731761_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/16/gianni-infantino.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6600,28 +6600,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Statistik Indonesia Vs Vietnam: Efektivitas Jadi Pembeda</t>
+          <t>Sebuah Perenungan Rizky Ridho</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:30:45 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:40 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Statistik saat Timnas Indonesia kalah 0-3 dari Vietnam. Tim Garuda tumpul di depan dan rapuh di belakang hingga kalah telak di kandang.</t>
+          <t>Rizky Ridho mengakui kesalahannya dalam kekalahan Indonesia dari Vietnam. Dia akan mencoba merenungkannya untuk berbenah di laga selanjutnya.</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603163/statistik-indonesia-vs-vietnam-efektivitas-jadi-pembeda</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603568/sebuah-perenungan-rizky-ridho</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513806_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6638,28 +6638,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Pochettino Teken Kontrak Baru, Latih Timnas AS sampai 2030</t>
+          <t>Bagas Maulana ke Ganda Campuran, Tandem sama Indah Cahya</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 13:35:30 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Karier Mauricio Pochettino sebagai pelatih Timnas Amerika Serikat masih panjang. Pria asal Argentina itu baru saja meneken kontrak baru.</t>
+          <t>PBSI kembali jajal kombinasi baru di sektor ganda campuran. Kali ini, Bagas Maulana dipasangkan dengan Indah Cahya Sari Jamil!</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8603160/pochettino-teken-kontrak-baru-latih-timnas-as-sampai-2030</t>
+          <t>https://sport.detik.com/raket/d-8603660/bagas-maulana-ke-ganda-campuran-tandem-sama-indah-cahya</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/mauricio-pochettino-1785784945554_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/22/fajarfikri-kalahkan-bagasleo-di-indonesia-masters-2026-1769070561744.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6676,28 +6676,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Indonesia Susah Banget Tembus Pertahanan Vietnam</t>
+          <t>Jika Arsenal Dapatkan Vinicius...</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 13:20:25 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Timnas Indonesia mati kutu saat menjamu Vietnam dalam lanjutan Piala AFF 2026. Garuda kesulitan menembus pertahanan lawan dan jadi bulan-bulanan. Duh!</t>
+          <t>Situasi Vinicius Jr di Madrid masih tanda tanya, rumor Arsenal mau merekrutnya juga terus mencuat. Wilshere bakal girang betul andai The Gunners mendapatkannya.</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603148/indonesia-susah-banget-tembus-pertahanan-vietnam</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603570/jika-arsenal-dapatkan-vinicius</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/02/vinicius-jr.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Indonesia Digebuk Vietnam, Nadeo: Kami Main Kurang Bagus</t>
+          <t>Indonesia Vs Vietnam: Sayap-sayap Lemah Garuda</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 13:00:30 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Timnas Indonesia digebuk Vietnam di hadapan pendukung sendiri. Kiper Nadeo Argawinata mewakili rekan setimnya meminta maaf atas hasil buruk tersebut.</t>
+          <t>Timnas Indonesia dibenamkan Timnas Vietnam di Piala AFF 2026. Sayap-sayap Garuda terlihat lemah di hadapan Golden Star Warriors.</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603151/indonesia-digebuk-vietnam-nadeo-kami-main-kurang-bagus</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603566/indonesia-vs-vietnam-sayap-sayap-lemah-garuda</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nadeo-argawinata-1785776694751_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6752,28 +6752,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>'Arsenal Sudah Pasti Mau Pertahankan Gelar, Tekanan Ada di Rival'</t>
+          <t>Posisi di FIFA Terancam, Infantino Minta Dukungan Trump?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 12:40:25 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Christos Tzolis menyatakan bahwa Arsenal siap untuk mempertahankan gelar. Pemain baru Meriam London itu menyebut tekanan ada di rival.</t>
+          <t>Posisi Gianni Infantino di FIFA terancam usai geger wacana jual saham Piala Dunia. Pria asal Swiss itu kabarnya meminta dukungan Presiden AS Donald Trump.</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603149/arsenal-sudah-pasti-mau-pertahankan-gelar-tekanan-ada-di-rival</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603451/posisi-di-fifa-terancam-infantino-minta-dukungan-trump</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/arsenal-1785694598503_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/presiden-as-donald-trump-1783299814038_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6790,28 +6790,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Jelang Tampil di AXCR 2026, Memen Harianto Dapat 'Tenaga' Baru</t>
+          <t>Balik Latihan di Madrid, Vinicius Segera Perpanjang Kontrak</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:45:20 +0700</t>
+          <t>Tue, 04 Aug 2026 12:20:30 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Memen Harianto terus mempersiapkan diri jelang Asia Cross Country Rally (AXCR) 2026. Memen mendapat suntikan tenaga baru, apa itu?</t>
+          <t>Vinicius Jr dilaporkan segera memperpanjang kontraknya setelah sudah kembali berlatih dengan Real Madrid. Ia memutuskan bertahan di El Real.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8603162/jelang-tampil-di-axcr-2026-memen-harianto-dapat-tenaga-baru</t>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/liga-spanyol/d-8603450/balik-latihan-di-madrid-vinicius-segera-perpanjang-kontrak</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/indonesia-cross-country-rally-team-1785786307522_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/21/vinicius-jr-1768973038339_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6828,38 +6828,874 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Erick Thohir Maju Jadi Ketum PSSI Lagi Tahun Depan?</t>
+          <t>8 Data Fakta usai Indonesia Dihantam Vietnam: Bulan Madu Herdman Selesai</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 12:00:20 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
+          <t>Timnas Indonesia menelan kekalahan telak dari Timnas Vietnam di Piala AFF 2026. Bulan madu John Herdman bersama Skuad Garuda selesai.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603448/8-data-fakta-usai-indonesia-dihantam-vietnam-bulan-madu-herdman-selesai</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Flick: Dear Barca, Mana Striker Barunya Nih?</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:40:10 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Belum ada juga pemain baru datang untuk menggantikan Robert Lewandowski. Pelatih Barcelona Hansi Flick mencoba sabar menunggu.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603267/flick-dear-barca-mana-striker-barunya-nih</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hansi-flick-1785806312405_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Bikin Pantun untuk Fermin Aldeguer &amp;amp; Alex Marquez, Dapatkan Saldo E-Wallet</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:22:46 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Ikuti kuis kreatif dari detikcom dan Bold Riders! Buat pantun lucu untuk Fermin Aldeguer atau Alex Marquez dan menangkan saldo e-wallet Rp 250 ribu!</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8603482/bikin-pantun-untuk-fermin-aldeguer-alex-marquez-dapatkan-saldo-e-wallet</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/la-bold-1785817343343.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Direktur RB Leipzig: Kata Siapa Diomande Sudah 'Here We Go'?</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:20:45 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Yan Diomande sempat diklaim tinggal selangkah lagi gabung Real Madrid. Kabar itu dibantah keras petinggi RB Leipzig.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603249/direktur-rb-leipzig-kata-siapa-diomande-sudah-here-we-go</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/yann-diomande-1785778891457_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Jadwal Semifinal Piala Presiden: Persib Vs Persija, Persebaya Vs Arema</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:00:41 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Jadwal semifinal Piala Presiden 2026 mempertemukan Persib vs Persija dan Persebaya vs Arema. Simak jadwal semifinal hingga final.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603340/jadwal-semifinal-piala-presiden-persib-vs-persija-persebaya-vs-arema</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/12/980f4b19-e319-452f-bd84-74e7316325ce_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Liverpool Disarankan Pulangkan Alexander-Arnold</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:40:35 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Liverpool disarankan memulangkan Trent Alexander-Arnold yang kesulitan di Real Madrid. Umpan silang akurat dari TAA dinilai sangat dibutuhkan Alexander Isak.</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603306/liverpool-disarankan-pulangkan-alexander-arnold</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/13/trent-alexander-arnold-1773385024632_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>John Herdman Rasakan Kekalahan Kedua Latih Indonesia</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:20:30 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia jadi bulan-bulanan Vietnam di Piala AFF 2026. Ini menjadi kekalahan kedua Garuda di bawah asuhan John Herdman.</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603299/john-herdman-rasakan-kekalahan-kedua-latih-indonesia</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/john-herdman-1785718686520_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Bernardo Silva Tak Masalah Mainkan Banyak Peran di Madrid</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:00:20 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Bernardo Silva siap dimainkan di berbagai posisi bersama Real Madrid. Ia punya kemampuan untuk memainkan sejumlah peran di lapangan.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603262/bernardo-silva-tak-masalah-mainkan-banyak-peran-di-madrid</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2288876689-1785802177577_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Indonesia Dikalahkan Vietnam, John Herdman Minta Garuda Tetap Fokus</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia kalah 0-3 dari Vietnam pada matchday ketiga Piala AFF 2026. Pelatih Garuda John Herdman meminta timnya untuk tetap fokus.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603309/indonesia-dikalahkan-vietnam-john-herdman-minta-garuda-tetap-fokus</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Ferran Mau Saja Bertahan di Barca Asalkan...</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:20:05 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Ferran Torres tidak masalah jika akhirnya bertahan di Barcelona. Tapi, ada satu syarat yang harus dipenuhi Los Cules, apa itu?</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603308/ferran-mau-saja-bertahan-di-barca-asalkan</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ferran-torres-1785808347370_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Persiapan Vietnam Biasa Saja, tapi Bisa Bantai Indonesia</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Timnas Vietnam mengganyang Indonesia di Piala AFF 2026. Pelatih Kim Sang-sik mengaku tak mempersiapkan timnya secara khusus sebelum pertandingan.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603248/persiapan-vietnam-biasa-saja-tapi-bisa-bantai-indonesia</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/timnas-vietnam-1785766971799_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Tinggalkan Madrid, Gonzalo Garcia Gabung Fulham</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Gonzalo Garcia resmi meninggalkan Real Madrid. Penyerang muda Spanyol itu melanjutkan kariernya bersama Fulham.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603244/tinggalkan-madrid-gonzalo-garcia-gabung-fulham</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gonzalo-garcia-1785804604431_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Kualifikasi GTR Ultra Tutup 7 Agustus, Jangan Sampai Gagal Ikut Trail Run Ini</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:15:47 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Kabar penting buat pelari trail, pendaftaran kualifikasi GTR Ultra 2026 resmi akan ditutup 7 Agustus 2026 pukul 23.30 WIB.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sportstyle/d-8603071/kualifikasi-gtr-ultra-tutup-7-agustus-jangan-sampai-gagal-ikut-trail-run-ini</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/gtr-ultra-2026-1773216163821_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Bantai Indonesia, Vietnam Lanjutkan Rekor Tak Terkalahkan Sejak 2024</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Vietnam melanjutkan catatan tak terkalahkan usai menumbangkan Indonesia. Golden Star Warriors tak terkalahkan dalam 21 laga terakhir.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603202/bantai-indonesia-vietnam-lanjutkan-rekor-tak-terkalahkan-sejak-2024</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Nguyen Hai Long Bobol Indonesia, Pamer Patch Emas Vietnam</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:30:40 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Pemain Vietnam Nguyen Hai Long membobol gawang Timnas Indonesia. Dia merayakan golnya dengan memamerkan patch emas tanda juara bertahan Piala AFF.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603197/nguyen-hai-long-bobol-indonesia-pamer-patch-emas-vietnam</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Henderson Pilih Chelsea karena Xabi Alonso</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Nama besar Xabi Alonso di sepakbola tentu jadi magnet untuk banyak pesepakbola, tak terkecuali Jordan Henderson. Alonso jadi alasannya gabung Chelsea.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603196/henderson-pilih-chelsea-karena-xabi-alonso</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jordan-henderson-1785800731761_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Statistik Indonesia Vs Vietnam: Efektivitas Jadi Pembeda</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Statistik saat Timnas Indonesia kalah 0-3 dari Vietnam. Tim Garuda tumpul di depan dan rapuh di belakang hingga kalah telak di kandang.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603163/statistik-indonesia-vs-vietnam-efektivitas-jadi-pembeda</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513806_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Pochettino Teken Kontrak Baru, Latih Timnas AS sampai 2030</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Karier Mauricio Pochettino sebagai pelatih Timnas Amerika Serikat masih panjang. Pria asal Argentina itu baru saja meneken kontrak baru.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8603160/pochettino-teken-kontrak-baru-latih-timnas-as-sampai-2030</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/mauricio-pochettino-1785784945554_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Indonesia Susah Banget Tembus Pertahanan Vietnam</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia mati kutu saat menjamu Vietnam dalam lanjutan Piala AFF 2026. Garuda kesulitan menembus pertahanan lawan dan jadi bulan-bulanan. Duh!</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603148/indonesia-susah-banget-tembus-pertahanan-vietnam</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Indonesia Digebuk Vietnam, Nadeo: Kami Main Kurang Bagus</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia digebuk Vietnam di hadapan pendukung sendiri. Kiper Nadeo Argawinata mewakili rekan setimnya meminta maaf atas hasil buruk tersebut.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603151/indonesia-digebuk-vietnam-nadeo-kami-main-kurang-bagus</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nadeo-argawinata-1785776694751_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>'Arsenal Sudah Pasti Mau Pertahankan Gelar, Tekanan Ada di Rival'</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Christos Tzolis menyatakan bahwa Arsenal siap untuk mempertahankan gelar. Pemain baru Meriam London itu menyebut tekanan ada di rival.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603149/arsenal-sudah-pasti-mau-pertahankan-gelar-tekanan-ada-di-rival</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/arsenal-1785694598503_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Jelang Tampil di AXCR 2026, Memen Harianto Dapat 'Tenaga' Baru</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:45:20 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Memen Harianto terus mempersiapkan diri jelang Asia Cross Country Rally (AXCR) 2026. Memen mendapat suntikan tenaga baru, apa itu?</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sport-lain/d-8603162/jelang-tampil-di-axcr-2026-memen-harianto-dapat-tenaga-baru</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/indonesia-cross-country-rally-team-1785786307522_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Erick Thohir Maju Jadi Ketum PSSI Lagi Tahun Depan?</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
           <t>Erick Thohir tidak menutup peluang mencalonkan diri kembali menjadi Ketua Umum PSSI. Tapi sebelum itu, ia akan berkonsultasi dengan pemerintah dan FIFA dulu.</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603147/erick-thohir-maju-jadi-ketum-pssi-lagi-tahun-depan</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pssi-1785758655620_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H191" t="inlineStr">
         <is>
           <t>Detik</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H169"/>
+  <autoFilter ref="A1:H191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-04.xlsx
+++ b/data/berita_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2187,33 +2187,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mayat Mutilasi dalam Karung di Depok Dikira Sampah, Sempat Dibakar Warga</t>
+          <t>PSSI Cuan Rp 722 Miliar, Tetap Terbuka Bantuan dari Pemerintah</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:36:14 +0700</t>
+          <t>Tue, 04 Aug 2026 23:30:30 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jasad termutilasi di Depok, terbungkus karung. Mayat korban sempat dikira sampah oleh warga.</t>
+          <t>PSSI sukses mengumpulkan pendapatan fantastis Rp722 miliar. Angka tersebut sudah cukup buat PSSI, tetapi tetap terbuka jika ada tawaran bantuan pemerintah.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604492/mayat-mutilasi-dalam-karung-di-depok-dikira-sampah-sempat-dibakar-warga</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604319/pssi-cuan-rp-722-miliar-tetap-terbuka-bantuan-dari-pemerintah</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/9def71f1-1c47-4d30-8a60-a8c3521d9475_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menpora-erick-thohir-1783676745865.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2225,33 +2225,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hujan Deras Guyur Bogor, 1 Pohon Tumbang Timpa Atap Rumah Warga</t>
+          <t>Indonesia Punya 2 Srikandi di Asia Cross Country Rally 2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:35:19 +0700</t>
+          <t>Tue, 04 Aug 2026 23:25:00 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hujan deras melanda kawasan Desa Cijayanti, Kecamatan Babakan Madang, Bogor, Jawa Barat. Akibatnya, sebuah pohon tumbang kemudian menimpa rumah warga.</t>
+          <t>Asia Cross Country Rally 2026 rupanya menarik minat para pereli wanita Indonesia. Mereka adalah Lody Natasha dan Satsy Laksamana.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604491/hujan-deras-guyur-bogor-1-pohon-tumbang-timpa-atap-rumah-warga</t>
+          <t>https://sport.detik.com/sport-lain/d-8604616/indonesia-punya-2-srikandi-di-asia-cross-country-rally-2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pohon-tumbang-timpa-rumah-warga-di-bogor-dokistimewa-1785850485303_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/lody-natasha-dan-satsy-laksamana-1785860860805_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2263,33 +2263,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tambak Modern Udang Vaname Hadirkan Solusi Budi Daya Efisien</t>
+          <t>Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:00:40 +0700</t>
+          <t>Tue, 04 Aug 2026 23:00:00 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Budi daya udang vaname dengan sistem tertutup dikembangkan di kawasan industri Semarang. Teknologi ini menghemat air juga meningkatkan produktivitas tambak.</t>
+          <t>Final Piala Presiden 2026 akhirnya mendapatkan kontestannya. Persib Bandung vs Persebaya Surabaya akan tersaji di partai puncak.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603831/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604606/final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien-1785830418949_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492015_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2301,33 +2301,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Harga Minyak Langsung Turun Usai AS-Iran Setop Serangan</t>
+          <t>Piala AFF: Indonesia Dijagokan Taklukkan Singapura, Lolos ke Semifinal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:35:07 +0700</t>
+          <t>Tue, 04 Aug 2026 22:40:30 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Harga minyak dunia turun nyaris 4% pada Selasa (4/8/2026) dan menyentuh level terendah dalam tiga pekan.</t>
+          <t>Timnas Indonesia akan dijamu Timnas Singapura dalam laga penentuan tiket ke semifinal Piala AFF 2026. Garuda dijagokan mengalahkan The Lions.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604597/harga-minyak-langsung-turun-usai-as-iran-setop-serangan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604294/piala-aff-indonesia-dijagokan-taklukkan-singapura-lolos-ke-semifinal</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/24/harga-minyak-dunia-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2339,33 +2339,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>604.923 Rekening Terkait Scam Diblokir!</t>
+          <t>Cara Memen Agar Mobilnya Siap Taklukkan Medan Berat AXCR 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:11:04 +0700</t>
+          <t>Tue, 04 Aug 2026 22:25:00 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OJK bersama Indonesia Anti-Scam Center (IASC) terus memperkuat upaya pemberantasan kasus keuangan ilegal dan penipuan di sektor jasa keuangan.</t>
+          <t>Memen Harianto akan membawa nama Indonesia di Asia Cross Country Rally (AXCR) 2026. Dia melakukan persiapan secara maksimal, terutama untuk mobilnya.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604576/604-923-rekening-terkait-scam-diblokir</t>
+          <t>https://sport.detik.com/sport-lain/d-8604594/cara-memen-agar-mobilnya-siap-taklukkan-medan-berat-axcr-2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/24/ilustrasi-telepon-scam-atau-penipuan-1766569797414_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/memen-harianto-1785860948781_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2377,33 +2377,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Warga RI Doyan Pakai Paylater, Ini Buktinya</t>
+          <t>Persebaya Vs Arema: Bajul Ijo Menang 1-0, Lolos ke Final Piala Presiden</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:14:02 +0700</t>
+          <t>Tue, 04 Aug 2026 22:17:39 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Penggunaan layanan Buy Now Pay Later (BNPL) atau paylater masih meningkat.</t>
+          <t>Persebaya Surabaya meraih kemenangan 1-0 atas Arema FC di semifinal Piala Presiden 2026. Persebaya lolos ke final untuk menghadapi Persib Bandung.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604532/warga-ri-doyan-pakai-paylater-ini-buktinya</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604584/persebaya-vs-arema-bajul-ijo-menang-1-0-lolos-ke-final-piala-presiden</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/10/27/ilustrasi-paylater_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2415,33 +2415,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Izin Tambang Berakhir 2041, Freeport Ajukan Perpanjangan ke Pemerintah</t>
+          <t>Hasil Piala AFF 2026: Thailand Atasi Filipina 1-0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:42:26 +0700</t>
+          <t>Tue, 04 Aug 2026 21:58:26 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Freeport Indonesia telah mengajukan permohonan perpanjangan IUPK untuk melanjutkan operasi tambang Grasberg setelah izin yang berlaku saat ini berakhir 2041.</t>
+          <t>Thailand melanjutkan start positifnya di Piala AFF 2026. Tim War Elephants menang tipis 1-0 atas Filipina dan menguasai pucuk klasemen Grup B.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604497/izin-tambang-berakhir-2041-freeport-ajukan-perpanjangan-ke-pemerintah</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604566/hasil-piala-aff-2026-thailand-atasi-filipina-1-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/11/mengintip-tambang-sedalam-17-km-di-perut-bumi-papua-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2453,33 +2453,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mendes: Kopdes Merah Putih Penggerak Ekonomi Desa</t>
+          <t>Vicario dan Suzuki Diincar Juventus, Buffon Bilang Begini!</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:19:08 +0700</t>
+          <t>Tue, 04 Aug 2026 21:45:05 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pemerintah menargetkan pembangunan 30.000 Koperasi Desa/Kelurahan Merah Putih (KDKMP) pada tahun ini.</t>
+          <t>Juventus dikabarkan menjadikan Guglielmo Vicario dan Zion Suzuki sebagai kandidat kiper anyar. Bagaimana menurut Gianluigi Buffon?</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604472/mendes-kopdes-merah-putih-penggerak-ekonomi-desa</t>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604289/vicario-dan-suzuki-diincar-juventus-buffon-bilang-begini</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menteri-desa-dan-pembangunan-daerah-tertinggal-pdt-1785853253837_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/04/gianluigi-buffon_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2491,33 +2491,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bursa Mineral Meluncur 1 Januari 2027, Ini Bocoran dari OJK</t>
+          <t>Pelajaran dari Singapura Sukses Antar Vietnam Cukur Indonesia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:00:15 +0700</t>
+          <t>Tue, 04 Aug 2026 21:30:15 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OJK buka-bukaan soal Bursa Mineral bakal meluncur 1 Januari 2027.</t>
+          <t>Vietnam banyak belajar dari hasil imbang melawan Singapura. Pemilihan strategi yang tepat sukses antar Vietnam mencukur Timnas Indonesia 3-0.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604418/bursa-mineral-meluncur-1-januari-2027-ini-bocoran-dari-ojk</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604285/pelajaran-dari-singapura-sukses-antar-vietnam-cukur-indonesia</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/18/friderica-widyasari-dewi-1781765532562_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2529,33 +2529,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bea Cukai Amankan 3 Warga Negara Malaysia Bawa Narkotika</t>
+          <t>PBSI Cari Pasangan untuk Adnan Maulana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:51:37 +0700</t>
+          <t>Tue, 04 Aug 2026 21:20:37 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Petugas Bea Cukai Bandara Soekarno-Hatta mengamankan ketamin dari 3 wanita penumpang pesawat diduga Warga Negara Malaysia.</t>
+          <t>PP PBSI masih mencari pasangan untuk Adnan Maulana. Itu setelah rekan tandemnya yang lama, Indah Cahya Sari Jamil, dipasangkan dengan pemain lain.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/ekonomi-bisnis/d-8604433/bea-cukai-amankan-3-warga-negara-malaysia-bawa-narkotika</t>
+          <t>https://sport.detik.com/raket/d-8604509/pbsi-cari-pasangan-untuk-adnan-maulana</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/ed32a201-0b77-4c2b-a370-0636977c2075_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/02/adnan-maulanaindah-cahya-sari-jamil-1780382604246_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2567,33 +2567,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Industri Kripto RI Terus Melonjak, Transaksinya Rp 28 T per Juni 2026</t>
+          <t>Matthijs de Ligt Belum Bisa Gabung ke MU</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:30:08 +0700</t>
+          <t>Tue, 04 Aug 2026 21:15:40 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aset kripto terus diminati di Indonesia, dengan 22,69 juta akun dan transaksi mencapai Rp 28,58 triliun pada Juni 2026. OJK tetap awasi perlindungan konsumen.</t>
+          <t>Manchester United masih belum bisa diperkuat bek tengahnya, Matthijs de Ligt. Dirinya masih belum pulih setelah operasi cedera punggung.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/fintech/d-8604314/industri-kripto-ri-terus-melonjak-transaksinya-rp-28-t-per-juni-2026</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603854/matthijs-de-ligt-belum-bisa-gabung-ke-mu</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/05/27/ilustrasi-bitcoin_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/07/matthijs-de-ligt-1775546584882.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2605,33 +2605,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sektor Jasa Keuangan Tetap Stabil, Kredit Perbankan Tumbuh 12,67%</t>
+          <t>Jelang Lawan Singapura, Timnas Indonesia Butuh Pemulihan Moral</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:19:21 +0700</t>
+          <t>Tue, 04 Aug 2026 21:00:30 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OJK menyatakan sektor jasa keuangan tetap stabil di tengah ketidakpastian global. Pertumbuhan kredit dan permodalan perbankan menunjukkan kinerja positif.</t>
+          <t>Timnas Indonesia sangat terpukul usai kalah 0-3 dari Vietnam. Skuad Garuda kini harus memulihkan moral jelang melawan Singapura.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604398/sektor-jasa-keuangan-tetap-stabil-kredit-perbankan-tumbuh-12-67</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604284/jelang-lawan-singapura-timnas-indonesia-butuh-pemulihan-moral</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ojk-1785845945964_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2643,33 +2643,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OJK Catat Total Aset Industri Asuransi RI Capai Rp Rp 1.184 triliun</t>
+          <t>Jorge Martin Tak Sabar Lanjutkan Duel Sengit Perebutan Gelar MotoGP 2026!</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:07:39 +0700</t>
+          <t>Tue, 04 Aug 2026 20:50:40 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OJK melaporkan total aset industri asuransi RI mencapai Rp 1.184 triliun per Juni 2026, dengan pertumbuhan stabil meski beberapa sektor mengalami kontraksi.</t>
+          <t>Jorge Martin antusias menatap paruh kedua MotoGP 2026. Ia yakin persaingan gelar juara dunia akan semakin sengit karena lima pebalap hanya terpaut 24 poin.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604257/ojk-catat-total-aset-industri-asuransi-ri-capai-rp-rp-1-184-triliun</t>
+          <t>https://sport.detik.com/moto-gp/d-8604324/jorge-martin-tak-sabar-lanjutkan-duel-sengit-perebutan-gelar-motogp-2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/14/ilustrasi-asuransi-kesehatan-1778737684617_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/moto-motogp-ned-1782675298213_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2681,33 +2681,33 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kredit Perbankan Tembus Rp 9.081 Triliun, Tumbuh 12,67%</t>
+          <t>Mulai Tahun Depan Piala Presiden untuk Timnas Indonesia, Tidak Lagi Klub</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:30:05 +0700</t>
+          <t>Tue, 04 Aug 2026 20:45:15 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kredit perbankan pada bulan Juni 2026 tumbuh 12,67% menjadi Rp 9.081 triliun.</t>
+          <t>Ketum PSSI Erick Thohir mengungkapkan Piala Presiden mulai tahun depan tidak lagi menjadi turnamen pramusim klub, melainkan jadi agenda Timnas Indonesia.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604271/kredit-perbankan-tembus-rp-9-081-triliun-tumbuh-12-67</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604194/mulai-tahun-depan-piala-presiden-untuk-timnas-indonesia-tidak-lagi-klub</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/02/10/uang-tunai-rupiah-4_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2719,33 +2719,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Utang Pinjol Warga RI Tembus Rp 105 Triliun!</t>
+          <t>Kovacic: Anderson Bikin Lini Tengah Man City Lebih Bertenaga</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:25:04 +0700</t>
+          <t>Tue, 04 Aug 2026 20:30:50 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OJK mencatat nilai pembiayaan pinjol mencapai Rp 105,14 triliun, atau tumbuh 25,88% secara tahunan pada bulan Juni 2026.</t>
+          <t>Mateo Kovacic antusias dengan Elliott Anderson, meski itu juga berarti persaingan lini tengah Manchester City kian ketat. Ia yakin tim makin kuat.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8604291/utang-pinjol-warga-ri-tembus-rp-105-triliun</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604197/kovacic-anderson-bikin-lini-tengah-man-city-lebih-bertenaga</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/02/04/b3a5ed4c-3141-4fed-a3ff-2bfc948f1b01_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/29/elliott-anderson-1764354213557_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2757,33 +2757,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BRILink Agen Permudah Perajin &amp;amp; Petani Alor Akses Layanan Perbankan</t>
+          <t>Usai Indonesia Dihajar Vietnam, Hubner Saling Sindir dengan Do Hoang Hen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:13:26 +0700</t>
+          <t>Tue, 04 Aug 2026 20:15:00 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kepulauan Alor, NTT, menawarkan keindahan dan tantangan. Kehadiran BRILink Agen mempermudah akses keuangan, mendukung kemandirian ekonomi masyarakat setempat.</t>
+          <t>Timnas Indonesia dihajar Timnas Vietnam dalam laga lanjutan Piala AFF 2026. Justin Hubner saling sindir dengan pemain Golden Star Warriors, Do Hoang Hen.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604269/brilink-agen-permudah-perajin-petani-alor-akses-layanan-perbankan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604196/usai-indonesia-dihajar-vietnam-hubner-saling-sindir-dengan-do-hoang-hen</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2017/12/05/4acc195a-ed44-44c8-88b3-7f629b73d63b_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513456_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2795,33 +2795,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>36 Ribu Rekening Judi Online Diblokir!</t>
+          <t>Buffon Percaya sama Mancini, Semoga Italia Lolos ke Piala Dunia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:00:20 +0700</t>
+          <t>Tue, 04 Aug 2026 20:00:40 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) sebut 36.735 rekening terkait judi online diblokir.</t>
+          <t>Sepakbola Italia bergejolak belakangan ini dalam penunjukan pelatih baru. Buffon mau drama itu berakhir, percayakan ke juru taktik baru Roberto Mancini.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604245/36-ribu-rekening-judi-online-diblokir</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604208/buffon-percaya-sama-mancini-semoga-italia-lolos-ke-piala-dunia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/27/ilustrasi-judi-online-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/03/gianluigi-buffon-1748885612603.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2833,33 +2833,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WIKA Sukses Catatkan Kontrak Baru Rp 6,91 Triliun hingga Juni 2026</t>
+          <t>Marco Bezzecchi Belum 100%, tapi Siap Comeback di MotoGP Inggris 2026!</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:45:19 +0700</t>
+          <t>Tue, 04 Aug 2026 19:50:50 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>WIKA raih kontrak baru Rp 6,91 triliun hingga Juni 2026, didorong proyek strategis di konstruksi dan infrastruktur. Optimis dukung pembangunan nasional.</t>
+          <t>Marco Bezzecchi siap kembali balapan di MotoGP Inggris 2026 meski mengaku belum pulih 100 persen usai menjalani operasi tulang selangka dan lutut.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/infrastruktur/d-8604234/wika-sukses-catatkan-kontrak-baru-rp-6-91-triliun-hingga-juni-2026</t>
+          <t>https://sport.detik.com/moto-gp/d-8604281/marco-bezzecchi-belum-100-tapi-siap-comeback-di-motogp-inggris-2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/wika-sukses-catatkan-kontrak-baru-rp-691-triliun-hingga-juni-2026-1785840143413_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/15/motor-motogp-germany-1784050516185_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2871,33 +2871,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gagal Dapat Diskon Moge Harley Davidson, Purbaya: Yah, Lemes Gue!</t>
+          <t>Vietnam 'Oper' Tekanan ke Indonesia</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:38:14 +0700</t>
+          <t>Tue, 04 Aug 2026 19:40:30 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa bercerita dirinya gagal membeli motor Harley Davidson dengan harga diskon karena dianggap gratifikasi.</t>
+          <t>Vietnam datang dengan tekanan dan kini melemparnya ke Indonesia. Mampukah skuad Garuda merespons tekanan itu dan keluar dari posisi terjepit.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604225/gagal-dapat-diskon-moge-harley-davidson-purbaya-yah-lemes-gue</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604184/vietnam-oper-tekanan-ke-indonesia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menkeu-purbaya-jajal-moge-harley-davidson-1785839816386_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2909,33 +2909,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bos OJK Blak-blakan Kondisi Sektor Keuangan RI di Tengah Gejolak Global</t>
+          <t>Liverpool Enggan Jual Gakpo, tapi Kalau Tottenham Kasih Harga Bagus...</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:16:02 +0700</t>
+          <t>Tue, 04 Aug 2026 19:20:45 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi buka-bukaan kondisi sektor keuangan di tengah gonjang-ganjing global.</t>
+          <t>Tottenham Hotspur meminati Cody Gakpo dari Liverpool. The Reds mau mempertahankan sang winger, tapi bakal goyah kalau dikasih harga bagus.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604173/bos-ojk-blak-blakan-kondisi-sektor-keuangan-ri-di-tengah-gejolak-global</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604186/liverpool-enggan-jual-gakpo-tapi-kalau-tottenham-kasih-harga-bagus</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/frederica-widyasari-dewi-1785765447950_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/05/cody-gakpo-1754352181260.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2947,33 +2947,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Prabowo Minta Harga BBM Subsidi Tak Naik</t>
+          <t>Detak Jantung Marc Marquez Bisa Ungkap Kans Juara MotoGP 2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:11:28 +0700</t>
+          <t>Tue, 04 Aug 2026 19:10:20 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Menteri ESDM Bahlil mengungkapkan kebijakan harga BBM bersubsidi tetap dipertahankan meski harga minyak dunia naik.</t>
+          <t>Detak jantung Marc Marquez saat MotoGP Inggris diyakini bisa menjadi indikator keberhasilan pemulihan fisiknya terkait kans mengejar gelar dunia MotoGP 2026.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604168/prabowo-minta-harga-bbm-subsidi-tak-naik</t>
+          <t>https://sport.detik.com/moto-gp/d-8604170/detak-jantung-marc-marquez-bisa-ungkap-kans-juara-motogp-2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/01/presiden-prabowo-subianto-dok-youtube-setpres-1782871893408_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-1783860046236_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2985,33 +2985,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OJK Kasih Denda Rp 91 Miliar ke 104 Pelaku Pasar Modal</t>
+          <t>John Herdman: Indonesia Asyik di Depan, Jadi Lupa Pertahanan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:03:56 +0700</t>
+          <t>Tue, 04 Aug 2026 19:00:50 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OJK menjatuhkan denda Rp 91 miliar kepada 104 pelaku pasar modal untuk penegakan ketentuan dan perlindungan konsumen. Sanksi administratif juga diterapkan.</t>
+          <t>Pelatih Timnas Indonesia John Herdman menyebut timnya terlalu asyik main di depan saat jumpa Vietnam. Hasilnya timnya malah kecolongan di lini pertahanan.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604151/ojk-kasih-denda-rp-91-miliar-ke-104-pelaku-pasar-modal</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604183/john-herdman-indonesia-asyik-di-depan-jadi-lupa-pertahanan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/12/30/59e6cb2c-4043-4878-a12b-89f4ab9e5a8e_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/27/gaya-nyentrik-john-herdman-kawal-timnas-garuda-1774628369095.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3023,33 +3023,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pelatihan Tata Rias Bekali Siswa Berkebutuhan Khusus Menuju Dunia Kerja</t>
+          <t>Singapura Vs Indonesia: Ulangan Situasi di Manila Sedekade Lalu</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:00:33 +0700</t>
+          <t>Tue, 04 Aug 2026 18:40:45 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pelatihan tata rias menjadi salah satu upaya memperluas kesempatan kerja bagi siswa berkebutuhan khusus. Peserta belajar keterampilan yang bernilai ekonomi.</t>
+          <t>Indonesia menjalani laga hidup dan mati melawan Singapura di Piala AFF 2026. Laga ini menjadi ulangan persaingan Garuda melawan The Lions sedekade lalu.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603579/pelatihan-tata-rias-bekali-siswa-berkebutuhan-khusus-menuju-dunia-kerja</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603914/singapura-vs-indonesia-ulangan-situasi-di-manila-sedekade-lalu</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pelatihan-tata-rias-bekali-siswa-disabilitas-menuju-dunia-kerja-1785821111786_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/11/26/54e9d3f7-5e6d-46d8-b5d2-e2d0149535a8_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3061,33 +3061,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Penjualan Mobil RI Kalah dari Malaysia, Purbaya Ungkap Biang Keroknya</t>
+          <t>Malut United Resmi Ganti Nama Jadi Java United, Pindah Markas ke Semarang</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:40:03 +0700</t>
+          <t>Tue, 04 Aug 2026 18:30:00 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa buka-bukaan soal biang kerok penjualan kendaraan alami pelemahan.</t>
+          <t>Malut United resmi berganti nama menjadi Java United dan memindahkan markas dari Ternate ke Semarang.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/industri/d-8604080/penjualan-mobil-ri-kalah-dari-malaysia-purbaya-ungkap-biang-keroknya</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604279/malut-united-resmi-ganti-nama-jadi-java-united-pindah-markas-ke-semarang</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/giias-2026-dipadati-pengunjung-deretan-mobil-baru-dan-ev-jadi-magnet-utama-1785427971780_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/java-united-1785770401869_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3099,33 +3099,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Insiden KM Mutiara Sentosa II, Sistem Keselamatan Kapal Diminta Dievaluasi</t>
+          <t>Chelsea Mulai Bersih-bersih</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:38:27 +0700</t>
+          <t>Tue, 04 Aug 2026 18:20:15 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Anggota DPR Sudjatmiko menyampaikan duka cita atas kebakaran KM Mutiara Sentosa II. Ia mendesak evaluasi keselamatan pelayaran untuk mencegah tragedi serupa.</t>
+          <t>Chelsea punya 40 pemain di dalam skuadnya. Bursa transfer musim panas 2026 masih buka sampai 1 September, Si Biru kini saatnya bersih-bersih.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604495/insiden-km-mutiara-sentosa-ii-sistem-keselamatan-kapal-diminta-dievaluasi</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603920/chelsea-mulai-bersih-bersih</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/09/chelsea-1778261458229.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3137,33 +3137,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Prabowo Perintahkan Bahlil Bereskan Listrik Padam di Kalimantan</t>
+          <t>RI Bawa Pulang 15 Medali dari Kejuaraan Asia MMA, Kini Fokus Asian Games 2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:36:06 +0700</t>
+          <t>Tue, 04 Aug 2026 18:10:25 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Presiden Prabowo minta pemadaman listrik di Kalimantan segera teratasi. Menteri ESDM Bahlil akan koordinasi dengan PLN untuk pemulihan cepat.</t>
+          <t>Tim MMA Indonesia meraih 15 medali, termasuk lima emas, di GAMMA Asian Championships 2026.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8604071/prabowo-perintahkan-bahlil-bereskan-listrik-padam-di-kalimantan</t>
+          <t>https://sport.detik.com/sport-lain/d-8604192/ri-bawa-pulang-15-medali-dari-kejuaraan-asia-mma-kini-fokus-asian-games-2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/20/prabowo-bahlil-1760968180889_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gamma-asian-championships-2026-1785838947680_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3175,33 +3175,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Insiden Kapal Berulang Jadi Momentum Evaluasi Keselamatan Pelayaran</t>
+          <t>Erick Thohir: Saya Tetap Percaya pada John Herdman</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:26:53 +0700</t>
+          <t>Tue, 04 Aug 2026 18:00:10 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deretan insiden kapal di Tanah Air menjadi pendorong untuk evaluasi sistem pengawasan keselamatan pelayaran.</t>
+          <t>Timnas Indonesia kalah 0-3 dari Vietnam, kans ke semifinal Piala AFF 2026 terancam. Ketum PSSI Erick Thohir membela pelatih John Herdman.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604051/insiden-kapal-berulang-jadi-momentum-evaluasi-keselamatan-pelayaran</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603911/erick-thohir-saya-tetap-percaya-pada-john-herdman</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/13/selamat-datang-john-herdman-pelatih-baru-timnas-indonesia-1768277980430.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3213,33 +3213,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trump Digugat Massal Gegara Tarif Impor, Indonesia Ikut Terseret</t>
+          <t>Dirumorkan Kembali ke Italia, Kovacic: Man City Masih Mengandalkanku</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:19:10 +0700</t>
+          <t>Tue, 04 Aug 2026 17:45:40 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sebanyak 25 negara bagian AS menggugat Trump atas tarif impor baru. Mereka menilai tarif tersebut ilegal dan meminta pengembalian bea masuk yang dibayarkan.</t>
+          <t>Mateo Kovacic dirumorkan kembali ke Italia, dengan kabar Juventus dan Inter Milan meminati. Tapi gelandang senior itu bilang masih diandalkan Manchester City.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604002/trump-digugat-massal-gegara-tarif-impor-indonesia-ikut-terseret</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603894/dirumorkan-kembali-ke-italia-kovacic-man-city-masih-mengandalkanku</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/20/wolverhampton-wanderers-manchester-city_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3251,33 +3251,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WFH ASN Sehari dalam Sepekan Diperpanjang</t>
+          <t>Persib Vs Persija: Menang 2-1, Maung Bandung ke Final Piala Presiden 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:15:06 +0700</t>
+          <t>Tue, 04 Aug 2026 17:31:55 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pemerintah memperpanjang kebijakan Work from Home (WFH) bagi Aparatur Sipil Negara (ASN) sehari dalam sepekan.</t>
+          <t>Persib Bandung mengalahkan Persija Jakarta di semifinal Piala Presiden 2026. Pasukan Igor Tolic pun melaju ke final.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603998/wfh-asn-sehari-dalam-sepekan-diperpanjang</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604212/persib-vs-persija-menang-2-1-maung-bandung-ke-final-piala-presiden-2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/07/11/27d3660c-abb0-424e-8871-e739c2b6cc4d_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3289,33 +3289,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IHSG Ditutup Menguat ke Level 6.391</t>
+          <t>Bagas Maulana Dinilai Cocok ke Ganda Campuran, Ini Alasannya</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:13:12 +0700</t>
+          <t>Tue, 04 Aug 2026 17:20:10 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IHSG ditutup menguat di level 6.319,6, naik 1,37%. Volume transaksi mencapai 33.150 miliar saham. Kinerja mingguan dan bulanan juga positif.</t>
+          <t>Pelatih ganda putra Antonius Budi Ariantho menjelaskan alasan Bagas Maulana dipindahkan ke sektor ganda campuran.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8604014/ihsg-ditutup-menguat-ke-level-6-391</t>
+          <t>https://sport.detik.com/raket/d-8604165/bagas-maulana-dinilai-cocok-ke-ganda-campuran-ini-alasannya</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/ihsg-terpuruk-kekhawatiran-pasar-meningkat-1780558039793_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/12/bagas-maulana-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3327,33 +3327,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kuba Gelap Gulita Lagi, Krisis Listrik Makin Parah</t>
+          <t>Vietnam Tahu Caranya Keluar dari Tekanan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:09:09 +0700</t>
+          <t>Tue, 04 Aug 2026 17:15:15 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Krisis listrik Kuba semakin parah dengan pemadaman berulang. Sanksi AS dan infrastruktur tua jadi penyebab utama, mempengaruhi jutaan warga.</t>
+          <t>Vietnam datang ke Indonesia dengan tekanan besar usai ditahan Singapura. The Golden Star Warriors merespons dengan cemerlang.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603992/kuba-gelap-gulita-lagi-krisis-listrik-makin-parah</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603861/vietnam-tahu-caranya-keluar-dari-tekanan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/situasi-di-havana-ibu-kota-kuba-saat-diselimuti-kegelapan-buntut-lumpuhnya-jaringan-listrik-negara-tersebut-1785751638653_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3365,33 +3365,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Suntik Dana Rp 400 T ke Perbankan, Purbaya: Kalau Kurang, Saya Tambah!</t>
+          <t>Dear Liverpool, Ini Isak yang Baru</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:01:28 +0700</t>
+          <t>Tue, 04 Aug 2026 17:00:25 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa bicara soal suntikan dana SAL ke perbankan Rp 400 triliun.</t>
+          <t>Alexander Isak mengaku sudah pulih 100 persen. Sang striker siap berikan yang terbaik buat Liverpool di musim baru!</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8603978/suntik-dana-rp-400-t-ke-perbankan-purbaya-kalau-kurang-saya-tambah</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603859/dear-liverpool-ini-isak-yang-baru</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/05/tawa-purbaya-pastikan-ekonomi-hingga-mei-2026-masih-solid-1780655487362_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/alexander-isak-1778251850354.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3403,33 +3403,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BPS Catat Deflasi Bulanan, Harga Komoditas Pangan Jadi Penentu</t>
+          <t>Timnas Indonesia Masih Berani Main High Pressing, John?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:00:57 +0700</t>
+          <t>Tue, 04 Aug 2026 16:40:40 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BPS mencatat deflasi bulanan sebesar 0,14 persen pada Juli 2026. Penurunan harga sejumlah bahan pangan menjadi faktor utama yang menekan Indeks Harga Konsumen.</t>
+          <t>Timnas Indonesia sangat buruk dalam transisi bertahan dengan permainan high pressing. Pelatih John Herdman apakah akan mengubah cara bermain Garuda?</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603527/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603770/timnas-indonesia-masih-berani-main-high-pressing-john</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu-1785819465759_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3441,33 +3441,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>66 Ribu UMKM Jalani Pembinaan, Fokus Bangun Nilai Jual Lewat Storytelling</t>
+          <t>Piala AFF: Indonesia Pernah Lima Kali Gagal ke Semifinal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:58:17 +0700</t>
+          <t>Tue, 04 Aug 2026 16:20:15 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pertamina Patra Niaga membina 66 ribu UMKM dengan fokus pada storytelling untuk meningkatkan nilai jual produk. Strategi ini dorong daya saing di pasar.</t>
+          <t>Timnas Indonesia sedang di ujung tanduk di Piala AFF 2026. Sepanjang sejarah pesta sepakbola ASEAN, Skuad Garuda pernah lima kali gagal ke semifinal.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/solusiukm/d-8604055/66-ribu-umkm-jalani-pembinaan-fokus-bangun-nilai-jual-lewat-storytelling</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603776/piala-aff-indonesia-pernah-lima-kali-gagal-ke-semifinal</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/30/ilustrasi-umkm-makanan-1748571534080_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3479,33 +3479,33 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pegadaian Raih Penghargaan Khusus di Ajang IDX Channel Anugerah ESG 2026</t>
+          <t>Welbeck Kemarin Hobi Jebol Chelsea, Kini Jagoan Baru The Blues</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:55:52 +0700</t>
+          <t>Tue, 04 Aug 2026 16:00:15 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pegadaian raih penghargaan IDX Channel Anugerah ESG 2026 untuk inovasi keuangan inklusif.</t>
+          <t>Chelsea resmi mendatangkan Danny Welbeck. Sang striker veteran lumayan hobi jebol gawang The Blues dulu, tapi kini diharapkan jadi jagoan.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603968/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026</t>
+          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8603780/welbeck-kemarin-hobi-jebol-chelsea-kini-jagoan-baru-the-blues</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026-1785833724891_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/danny-welbeckchelseabursa-transfer-chelsea-1785602779561.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3517,33 +3517,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pendapatan Chandra Asri Naik 83%, tapi Laba Malah Anjlok 77% Jadi Rp 6,6 T</t>
+          <t>Ini Sebab PBSI Belum Rilis Daftar Pemain di Asian Games</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:48:29 +0700</t>
+          <t>Tue, 04 Aug 2026 15:50:00 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PT Chandra Asri Pacific Tbk (TPIA) membukukan penurunan laba bersih seiring tumbuhnya pendapatan sepanjang semester I-2026.</t>
+          <t>Nama-nama pebulutangkis Indonesia yang akan diturunkan di Asian Games 2026 belum final. PBSI masih akan melihat hasil dari Kejuaraan Dunia pada 17-23 Agustus.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603945/pendapatan-chandra-asri-naik-83-tapi-laba-malah-anjlok-77-jadi-rp-6-6-t</t>
+          <t>https://sport.detik.com/raket/d-8603931/ini-sebab-pbsi-belum-rilis-daftar-pemain-di-asian-games</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/31/chandra-asri_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/26/logo-pbsi.webp?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3555,33 +3555,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rayuan Maut Purbaya ke Raksasa Otomotif Jepang</t>
+          <t>John Herdman ke Suporter: Kita Menang Bersama, Kalah Juga Bersama</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:21:30 +0700</t>
+          <t>Tue, 04 Aug 2026 15:40:25 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan rayuan maut agar raksasa otomotif Jepang, Toyota, pindahkan pabriknya ke Indonesia.</t>
+          <t>Timnas Indonesia dihajar Timnas Vietnam saat menjalani laga kandang di Piala AFF 2026. John Herdman berjanji Skuad Garuda akan bangkit.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/industri/d-8603875/rayuan-maut-purbaya-ke-raksasa-otomotif-jepang</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603741/john-herdman-ke-suporter-kita-menang-bersama-kalah-juga-bersama</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/menteri-keuangan-purbaya-yudhi-sadewa-1758533359856_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/31/herdman-janji-bangkit-usai-kekalahan-targetkan-indonesia-ke-piala-dunia-2030-1774891836257_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3593,33 +3593,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Moody's-Fitch Kasih Nilai Negatif ke Ekonomi RI, Purbaya: Mereka Offside!</t>
+          <t>Awas MU, Bayern Munich Minati Benjamin Sesko</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:43:15 +0700</t>
+          <t>Tue, 04 Aug 2026 15:20:10 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa menyebut lembaga rating Moody's dan Fitch salah ukur ekonomi Indonesia.</t>
+          <t>Bayern Munich menaruh minat pada striker Man United, Benjamin Sesko. Tapi Bayern enggak mau buru-buru merekrutnya dulu, mungkin beberapa tahun mendatang nanti.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603805/moodys-fitch-kasih-nilai-negatif-ke-ekonomi-ri-purbaya-mereka-offside</t>
+          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603737/awas-mu-bayern-munich-minati-benjamin-sesko</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/purbaya-garuk-kepala-apbn-april-2026-defisit-rp1644-triliun-1779201435955_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/02/benjamin-sesko-1772389311489.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3631,33 +3631,33 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Industri Alas Kaki Indonesia Bertahan di Tengah Tarif Impor AS</t>
+          <t>Viet Anh Berdarah-Darah untuk Tuntaskan Dendam ke Indonesia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 15:00:45 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Industri alas kaki Indonesia tetap menjaga optimisme di tengah kebijakan tarif impor Amerika Serikat. Pelaku usaha menilai daya saing produk masih terjaga.</t>
+          <t>Vietnam sukses membabat Indonesia 3-0 dalam laga Grup A Piala AFF 2026. Bek Bui Hoang Viet Anh sangat puas Golden Star Warriors berhasil balas dendam.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603497/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603740/viet-anh-berdarah-darah-untuk-tuntaskan-dendam-ke-indonesia</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as-1785818219683_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3669,33 +3669,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Apa Kabar Proyek Trans Papua 50 Km? Begini Progresnya</t>
+          <t>Asian Games 2026: Bulutangkis Beregu Putra Jadi Asa Indonesia Raih Emas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:58:11 +0700</t>
+          <t>Tue, 04 Aug 2026 14:51:15 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kementerian Pekerjaan Umum (PU) mengungkapkan progres pembangunan Jalan Trans Papua.</t>
+          <t>Chef de Mission Indonesia Todotua Pasaribu berharap bulutangkis bisa mendapatkan medali emas di Asian Games 2026. Secara khusus nomor ganda putra.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/infrastruktur/d-8603725/apa-kabar-proyek-trans-papua-50-km-begini-progresnya</t>
+          <t>https://sport.detik.com/raket/d-8603821/asian-games-2026-bulutangkis-beregu-putra-jadi-asa-indonesia-raih-emas</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pembangunan-trans-papua-1785826507044_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/06/ilustrasi-bulutangkis.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3707,33 +3707,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kapan Prabowo Luncurkan Insentif Kendaraan Listrik?</t>
+          <t>Bermain Buruk, Indonesia Dipecundangi Vietnam!</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:35:04 +0700</t>
+          <t>Tue, 04 Aug 2026 14:44:50 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa bilang dalam beberapa pekan ke depan insentif kendaraan listrik akan diluncurkan Presiden Prabowo Subianto.</t>
+          <t>Apakah Indonesia bisa menjaga asa untuk tampil di semifinal Piala AFF 2026?</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/industri/d-8603674/kapan-prabowo-luncurkan-insentif-kendaraan-listrik</t>
+          <t>https://sport.detik.com/sepakbola/sepakbola-indonesia/d-8603690/bermain-buruk-indonesia-dipecundangi-vietnam</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/06/tekan-biaya-transportasi-motor-listrik-jadi-andalan-baru-masyarakat-1775465692322_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detiksore-4-agustus-2026-1785825691822_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3745,33 +3745,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Proyek PLTS 100 GW Segera Dimulai, Bali Jadi Lokasi Pertama</t>
+          <t>Marselino Ferdinan Tak Bisa Main di Piala AFF 2026!</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:26:52 +0700</t>
+          <t>Tue, 04 Aug 2026 14:40:10 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Menteri ESDM Bahlil Lahadalia umumkan pembangunan PLTS 100 GW bertahap, dimulai di Bali. Proyek ini ditargetkan rampung dengan perencanaan matang.</t>
+          <t>Kabar buruk menghampiri Timnas Indonesia di tengah gelaran Piala AFF 2026. Marselino Ferdinan tak bisa memperkuat Skuad Garuda!</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603661/proyek-plts-100-gw-segera-dimulai-bali-jadi-lokasi-pertama</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603636/marselino-ferdinan-tak-bisa-main-di-piala-aff-2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/22/menteri-esdm-bahlil-lahadalia-eva-sdetikcom-1782133701407_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/12/marselino-ferdinan_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3783,33 +3783,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ketemu World Bank-IMF, Purbaya: I'm the Most Unlucky Minister in the World</t>
+          <t>Usai Permalukan Indonesia, Vietnam Dapat Bonus Rp1,37 Miliar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:10:09 +0700</t>
+          <t>Tue, 04 Aug 2026 14:20:10 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa curhat dirinya menjadi menteri paling kurang beruntung di dunia.</t>
+          <t>Timnas Vietnam mempermalukan Timnas Indonesia di Piala AFF 2026. Golden Star Warriors mendapat bonus 2 miliar dong atau setara Rp1,37 miliar.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603641/ketemu-world-bank-imf-purbaya-im-the-most-unlucky-minister-in-the-world</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603633/usai-permalukan-indonesia-vietnam-dapat-bonus-rp1-37-miliar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786140_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3821,33 +3821,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Peternakan dan Pertanian Terpadu di Sleman Perkuat Sistem Pangan Berkelanjutan</t>
+          <t>Presiden FIFA Batal Naik Gaji 500 Persen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 14:00:15 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Konsep integrated farming di Sleman menghubungkan peternakan, pertanian, dan pengolahan limbah. Sistem ini mendukung produksi lebih efisien dan berkelanjutan.</t>
+          <t>Presiden FIFA Gianni Infantino diketahui bakal naik gaji 525 persen andai wacana jual saham Piala Dunia sukses. Wacana itu batal, nggak gaji naik deh!</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8603467/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603662/presiden-fifa-batal-naik-gaji-500-persen</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan-1785816225367_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/16/gianni-infantino.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3859,33 +3859,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cara Scan QRIS Cross Border di Luar Negeri</t>
+          <t>Sebuah Perenungan Rizky Ridho</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:57:38 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:40 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DANA mendukung transaksi QRIS Cross Border di luar negeri, memudahkan pengguna berbelanja di Thailand, Malaysia, Jepang, dan negara lainnya tanpa uang tunai.</t>
+          <t>Rizky Ridho mengakui kesalahannya dalam kekalahan Indonesia dari Vietnam. Dia akan mencoba merenungkannya untuk berbenah di laga selanjutnya.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603628/cara-scan-qris-cross-border-di-luar-negeri</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603568/sebuah-perenungan-rizky-ridho</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ilustrasi-qris-1785823037090_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3897,33 +3897,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IHSG Tertahan di Level 6.200</t>
+          <t>Bagas Maulana ke Ganda Campuran, Tandem sama Indah Cahya</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:41:11 +0700</t>
+          <t>Tue, 04 Aug 2026 13:35:30 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HSG menguat 0,57% ke level 6.270,15 hingga penutupan perdagangan siang ini.</t>
+          <t>PBSI kembali jajal kombinasi baru di sektor ganda campuran. Kali ini, Bagas Maulana dipasangkan dengan Indah Cahya Sari Jamil!</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603595/ihsg-tertahan-di-level-6-200</t>
+          <t>https://sport.detik.com/raket/d-8603660/bagas-maulana-ke-ganda-campuran-tandem-sama-indah-cahya</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/18/ihsg-anjlok-ke-zona-merah-bursa-saham-melemah-tajam-1779098741182_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/22/fajarfikri-kalahkan-bagasleo-di-indonesia-masters-2026-1769070561744.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3935,33 +3935,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Magang Nasional Banjir Peminat, Pendaftar Tembus 732 Ribu!</t>
+          <t>Jika Arsenal Dapatkan Vinicius...</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:36:26 +0700</t>
+          <t>Tue, 04 Aug 2026 13:20:25 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Peminat Magang Nasional mencapai 732 ribu, namun hanya 50 ribu yang diterima.</t>
+          <t>Situasi Vinicius Jr di Madrid masih tanda tanya, rumor Arsenal mau merekrutnya juga terus mencuat. Wilshere bakal girang betul andai The Gunners mendapatkannya.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603589/magang-nasional-banjir-peminat-pendaftar-tembus-732-ribu</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603570/jika-arsenal-dapatkan-vinicius</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/program-magang-kerja-phr-batch-9-hadir-untuk-memberikan-pengalaman-profesional-pendampingan-dari-para-ahli-dan-kesempatan-berk-1781240776723_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/02/vinicius-jr.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3973,33 +3973,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Gelombang PHK Makin Besar di Singapura, 4.500 Orang Jadi Korban</t>
+          <t>Indonesia Vs Vietnam: Sayap-sayap Lemah Garuda</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:14:37 +0700</t>
+          <t>Tue, 04 Aug 2026 13:00:30 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gelombang PHK di Singapura meningkat pada kuartal II-2026, mencapai 4.500 pekerja. Meski demikian, total lapangan kerja justru bertambah 10.700.</t>
+          <t>Timnas Indonesia dibenamkan Timnas Vietnam di Piala AFF 2026. Sayap-sayap Garuda terlihat lemah di hadapan Golden Star Warriors.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603555/gelombang-phk-makin-besar-di-singapura-4-500-orang-jadi-korban</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603566/indonesia-vs-vietnam-sayap-sayap-lemah-garuda</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2020/10/27/ilustrasi-kena-phk_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4011,33 +4011,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LPEI Kucurkan US$ 8,5 Juta Danai Ekspor Gerbong Barang ke Selandia Baru</t>
+          <t>Posisi di FIFA Terancam, Infantino Minta Dukungan Trump?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:11:18 +0700</t>
+          <t>Tue, 04 Aug 2026 12:40:25 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LPEI dukung PT INKA ekspor 340 unit Wagon ke Selandia Baru dengan fasilitas USD 8,5 juta. Sinergi ini perkuat industri strategis dan perekonomian nasional.</t>
+          <t>Posisi Gianni Infantino di FIFA terancam usai geger wacana jual saham Piala Dunia. Pria asal Swiss itu kabarnya meminta dukungan Presiden AS Donald Trump.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8603549/lpei-kucurkan-us-8-5-juta-danai-ekspor-gerbong-barang-ke-selandia-baru</t>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603451/posisi-di-fifa-terancam-infantino-minta-dukungan-trump</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eximbank-danai-ekspor-pt-inka-ke-selandia-baru-1785820259573_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/presiden-as-donald-trump-1783299814038_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4049,33 +4049,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alarm Berbunyi di Rusia, Bank-bank Mulai Krisis Uang Tunai!</t>
+          <t>Balik Latihan di Madrid, Vinicius Segera Perpanjang Kontrak</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:03:30 +0700</t>
+          <t>Tue, 04 Aug 2026 12:20:30 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bank-bank Rusia menghadapi tekanan likuiditas rubel, membatasi pembelian obligasi pemerintah. Defisit anggaran meningkat.</t>
+          <t>Vinicius Jr dilaporkan segera memperpanjang kontraknya setelah sudah kembali berlatih dengan Real Madrid. Ia memutuskan bertahan di El Real.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8603535/alarm-berbunyi-di-rusia-bank-bank-mulai-krisis-uang-tunai</t>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/liga-spanyol/d-8603450/balik-latihan-di-madrid-vinicius-segera-perpanjang-kontrak</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/01/ini-yang-bikin-warga-rusia-panik-serbu-atm-bank-buat-tarik-uang_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/21/vinicius-jr-1768973038339_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4087,33 +4087,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BSI dan Danantara Perkuat Ekosistem UMKM agar Pelaku Usaha Naik Kelas</t>
+          <t>8 Data Fakta usai Indonesia Dihantam Vietnam: Bulan Madu Herdman Selesai</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:51:53 +0700</t>
+          <t>Tue, 04 Aug 2026 12:00:20 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PT Bank Syariah Indonesia (BSI) dan Danantara memperkuat UMKM melalui 35 Sentra dan 4 UMKM Center, mendukung pembiayaan, digitalisasi, dan sertifikasi halal.</t>
+          <t>Timnas Indonesia menelan kekalahan telak dari Timnas Vietnam di Piala AFF 2026. Bulan madu John Herdman bersama Skuad Garuda selesai.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603515/bsi-dan-danantara-perkuat-ekosistem-umkm-agar-pelaku-usaha-naik-kelas</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603448/8-data-fakta-usai-indonesia-dihantam-vietnam-bulan-madu-herdman-selesai</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/direktur-utama-bsi-anggoro-eko-cahyo-1785820807840_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4125,33 +4125,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tak Mau Kehilangan Guru Berkualitas, Singapura Naikkan Gaji hingga 9%</t>
+          <t>Flick: Dear Barca, Mana Striker Barunya Nih?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:48:03 +0700</t>
+          <t>Tue, 04 Aug 2026 11:40:10 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pemerintah Singapura akan menaikkan gaji guru dan tenaga pendidik 2-9% mulai 1 Oktober 2026, untuk menarik dan mempertahankan tenaga pendidik berkualitas.</t>
+          <t>Belum ada juga pemain baru datang untuk menggantikan Robert Lewandowski. Pelatih Barcelona Hansi Flick mencoba sabar menunggu.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603511/tak-mau-kehilangan-guru-berkualitas-singapura-naikkan-gaji-hingga-9</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603267/flick-dear-barca-mana-striker-barunya-nih</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/21/pendidikan-nilai-1750494841214_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hansi-flick-1785806312405_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4163,33 +4163,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Trump Bantu Jepang Selamatkan Yen, Apa Untungnya buat AS?</t>
+          <t>Bikin Pantun untuk Fermin Aldeguer &amp;amp; Alex Marquez, Dapatkan Saldo E-Wallet</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:43:30 +0700</t>
+          <t>Tue, 04 Aug 2026 11:22:46 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Presiden AS Donald Trump mengatakan, intervensi ini dilakukan atas permintaan pemerintah Jepang.</t>
+          <t>Ikuti kuis kreatif dari detikcom dan Bold Riders! Buat pantun lucu untuk Fermin Aldeguer atau Alex Marquez dan menangkan saldo e-wallet Rp 250 ribu!</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603507/trump-bantu-jepang-selamatkan-yen-apa-untungnya-buat-as</t>
+          <t>https://sport.detik.com/moto-gp/d-8603482/bikin-pantun-untuk-fermin-aldeguer-alex-marquez-dapatkan-saldo-e-wallet</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/la-bold-1785817343343.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4201,33 +4201,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Peresmian Pabrik Baterai EV di Karawang Tinggal Tunggu Jadwal Prabowo</t>
+          <t>Direktur RB Leipzig: Kata Siapa Diomande Sudah 'Here We Go'?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:11:33 +0700</t>
+          <t>Tue, 04 Aug 2026 11:20:45 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Menteri ESDM Bahlil mengumumkan pabrik baterai listrik di Karawang siap diresmikan, tinggal menunggu jadwal Presiden. Investasi mencapai US$5,9 miliar.</t>
+          <t>Yan Diomande sempat diklaim tinggal selangkah lagi gabung Real Madrid. Kabar itu dibantah keras petinggi RB Leipzig.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603463/peresmian-pabrik-baterai-ev-di-karawang-tinggal-tunggu-jadwal-prabowo</t>
+          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603249/direktur-rb-leipzig-kata-siapa-diomande-sudah-here-we-go</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/menteri-esdm-bahlil-lahadalia-1784186781817_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/yann-diomande-1785778891457_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4239,33 +4239,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RI-Thailand Sepakat Genjot Perdagangan Tembus Rp 360 Triliun</t>
+          <t>Jadwal Semifinal Piala Presiden: Persib Vs Persija, Persebaya Vs Arema</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:02:03 +0700</t>
+          <t>Tue, 04 Aug 2026 11:00:41 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Indonesia dan Thailand sepakat menggenjot perdagangan dengan target Rp 360 triliun pada 2030.</t>
+          <t>Jadwal semifinal Piala Presiden 2026 mempertemukan Persib vs Persija dan Persebaya vs Arema. Simak jadwal semifinal hingga final.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603447/ri-thailand-sepakat-genjot-perdagangan-tembus-rp-360-triliun</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603340/jadwal-semifinal-piala-presiden-persib-vs-persija-persebaya-vs-arema</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/presiden-prabowo-subianto-menggelar-jamuan-santap-malam-resmi-untuk-pm-kerajaan-thailand-anutin-charnvirakul-foto-rusman-biro--1785806274579_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/12/980f4b19-e319-452f-bd84-74e7316325ce_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4277,33 +4277,33 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mengenang Burhanuddin 'Bur' Maras, Tokoh Migas dan Pendiri Lekom Maras</t>
+          <t>Liverpool Disarankan Pulangkan Alexander-Arnold</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:00:37 +0700</t>
+          <t>Tue, 04 Aug 2026 10:40:35 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Burhanuddin 'Bur' Maras, pendiri PT Lekom Maras, wafat di usia 90 tahun. Ia dikenal sebagai tokoh penting di industri perminyakan dan politik Indonesia.</t>
+          <t>Liverpool disarankan memulangkan Trent Alexander-Arnold yang kesulitan di Real Madrid. Umpan silang akurat dari TAA dinilai sangat dibutuhkan Alexander Isak.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603445/mengenang-burhanuddin-bur-maras-tokoh-migas-dan-pendiri-lekom-maras</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603306/liverpool-disarankan-pulangkan-alexander-arnold</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/burhanuddin-bur-maras-1785815972293.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/13/trent-alexander-arnold-1773385024632_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4315,33 +4315,33 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Krisis Iran Memanas, Warga Teheran Tetap Jalani Aktivitas di Tengah Ketegangan</t>
+          <t>John Herdman Rasakan Kekalahan Kedua Latih Indonesia</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:00:34 +0700</t>
+          <t>Tue, 04 Aug 2026 10:20:30 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Krisis Iran menjadi sorotan dunia. Di tengah ketegangan politik dan hubungan internasional, warga Teheran tetap menjalani aktivitas sehari-hari.</t>
+          <t>Timnas Indonesia jadi bulan-bulanan Vietnam di Piala AFF 2026. Ini menjadi kekalahan kedua Garuda di bawah asuhan John Herdman.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602911/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603299/john-herdman-rasakan-kekalahan-kedua-latih-indonesia</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan-1785761340975_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/john-herdman-1785718686520_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4353,33 +4353,33 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Buruh Batalkan Rencana Demo di DPR Senin Depan, Takut Ada Penyusup</t>
+          <t>Bernardo Silva Tak Masalah Mainkan Banyak Peran di Madrid</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:48:57 +0700</t>
+          <t>Tue, 04 Aug 2026 10:00:20 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KBPBI menunda aksi unjuk rasa di depan DPR untuk mendesak RUU Ketenagakerjaan. Keputusan diambil untuk menghindari potensi penyusup dan menjaga ketertiban.</t>
+          <t>Bernardo Silva siap dimainkan di berbagai posisi bersama Real Madrid. Ia punya kemampuan untuk memainkan sejumlah peran di lapangan.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603423/buruh-batalkan-rencana-demo-di-dpr-senin-depan-takut-ada-penyusup</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603262/bernardo-silva-tak-masalah-mainkan-banyak-peran-di-madrid</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/presiden-konfederasi-serikat-pekerja-seluruh-indonesia-kspsi-andi-gani-1758528973493_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2288876689-1785802177577_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4391,33 +4391,33 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Setelah Naik Beruntun, Harga Emas Antam Akhirnya Turun</t>
+          <t>Indonesia Dikalahkan Vietnam, John Herdman Minta Garuda Tetap Fokus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:51:02 +0700</t>
+          <t>Tue, 04 Aug 2026 09:40:30 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Harga emas Antam hari ini turun Rp 7.000 per gram menjadi Rp 2.603.000. Rincian harga emas dari 0,5 gram hingga 1.000 gram juga disajikan.</t>
+          <t>Timnas Indonesia kalah 0-3 dari Vietnam pada matchday ketiga Piala AFF 2026. Pelatih Garuda John Herdman meminta timnya untuk tetap fokus.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603360/setelah-naik-beruntun-harga-emas-antam-akhirnya-turun</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603309/indonesia-dikalahkan-vietnam-john-herdman-minta-garuda-tetap-fokus</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/13/emas-batangan-1763011692898_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4429,33 +4429,33 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mitratel Cetak Laba Rp 1,11 T</t>
+          <t>Ferran Mau Saja Bertahan di Barca Asalkan...</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:48:19 +0700</t>
+          <t>Tue, 04 Aug 2026 09:20:05 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PT Dayamitra Telekomunikasi Tbk (MTEL) alias Mitratel membukukan kinerja positif hingga akhir Juni 2026.</t>
+          <t>Ferran Torres tidak masalah jika akhirnya bertahan di Barcelona. Tapi, ada satu syarat yang harus dipenuhi Los Cules, apa itu?</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603358/mitratel-cetak-laba-rp-1-11-t</t>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603308/ferran-mau-saja-bertahan-di-barca-asalkan</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/17/potret-tower-mitratel-yang-manfaatkan-panel-surya-5_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ferran-torres-1785808347370_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4467,33 +4467,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dolar AS Tembus Rp 18.000 Pagi Ini</t>
+          <t>Persiapan Vietnam Biasa Saja, tapi Bisa Bantai Indonesia</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:33:38 +0700</t>
+          <t>Tue, 04 Aug 2026 09:00:10 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dolar AS bergerak menguat 0,06% ke level Rp 18.000 di awal pembukaan perdagangan.</t>
+          <t>Timnas Vietnam mengganyang Indonesia di Piala AFF 2026. Pelatih Kim Sang-sik mengaku tak mempersiapkan timnya secara khusus sebelum pertandingan.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603345/dolar-as-tembus-rp-18-000-pagi-ini</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603248/persiapan-vietnam-biasa-saja-tapi-bisa-bantai-indonesia</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338333_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/timnas-vietnam-1785766971799_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4505,33 +4505,33 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IHSG Dibuka Menguat ke 6.255</t>
+          <t>Tinggalkan Madrid, Gonzalo Garcia Gabung Fulham</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:29:37 +0700</t>
+          <t>Tue, 04 Aug 2026 08:30:20 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
+          <t>Gonzalo Garcia resmi meninggalkan Real Madrid. Penyerang muda Spanyol itu melanjutkan kariernya bersama Fulham.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603339/ihsg-dibuka-menguat-ke-6-255</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603244/tinggalkan-madrid-gonzalo-garcia-gabung-fulham</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/30/ihsg-rebound-usai-dua-hari-anjlok-seiring-pengunduran-diri-dirut-bei-1769748663323_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gonzalo-garcia-1785804604431_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4543,33 +4543,33 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Empat Sistem Karantina Diperkuat, Ekspor Ikan Hias Indonesia Makin Mendunia</t>
+          <t>Kualifikasi GTR Ultra Tutup 7 Agustus, Jangan Sampai Gagal Ikut Trail Run Ini</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:00:23 +0700</t>
+          <t>Tue, 04 Aug 2026 08:15:47 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barantin memperkuat empat sistem karantina untuk meningkatkan daya saing dan kepercayaan pasar global terhadap ikan hias Indonesia.</t>
+          <t>Kabar penting buat pelari trail, pendaftaran kualifikasi GTR Ultra 2026 resmi akan ditutup 7 Agustus 2026 pukul 23.30 WIB.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602609/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia</t>
+          <t>https://sport.detik.com/sportstyle/d-8603071/kualifikasi-gtr-ultra-tutup-7-agustus-jangan-sampai-gagal-ikut-trail-run-ini</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia-1785750239859_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/gtr-ultra-2026-1773216163821_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4581,33 +4581,33 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bos BGN Buka Suara soal Putusan MK Anggaran MBG dan Pendidikan Dipisah</t>
+          <t>Bantai Indonesia, Vietnam Lanjutkan Rekor Tak Terkalahkan Sejak 2024</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:38 +0700</t>
+          <t>Tue, 04 Aug 2026 08:00:05 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kami ini adalah lembaga operasional. Tentu saja kami akan melaksanakan apapun kebijakan dari pemerintah, kata Sudaryono.</t>
+          <t>Vietnam melanjutkan catatan tak terkalahkan usai menumbangkan Indonesia. Golden Star Warriors tak terkalahkan dalam 21 laga terakhir.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603305/bos-bgn-buka-suara-soal-putusan-mk-anggaran-mbg-dan-pendidikan-dipisah</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603202/bantai-indonesia-vietnam-lanjutkan-rekor-tak-terkalahkan-sejak-2024</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053334_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4619,33 +4619,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TLKM Catat Kinerja Semester I-2026, BUVA dan TAPG Umumkan Aksi Korporasi</t>
+          <t>Nguyen Hai Long Bobol Indonesia, Pamer Patch Emas Vietnam</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:45:59 +0700</t>
+          <t>Tue, 04 Aug 2026 07:30:40 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>TLKM membukukan pendapatan Rp75,9 triliun dan laba Rp10,6 triliun pada semester I-2026. BUVA siapkan rights issue, sementara TAPG tetapkan dividen interim.</t>
+          <t>Pemain Vietnam Nguyen Hai Long membobol gawang Timnas Indonesia. Dia merayakan golnya dengan memamerkan patch emas tanda juara bertahan Piala AFF.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/bursa-dan-valas/d-8603300/tlkm-catat-kinerja-semester-i-2026-buva-dan-tapg-umumkan-aksi-korporasi</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603197/nguyen-hai-long-bobol-indonesia-pamer-patch-emas-vietnam</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bursa-dan-valas-1785806578-1785806579142.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4657,33 +4657,33 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Trump Tak Suka Exxon &amp;amp; Chevron Untung Gede Gara-gara Harga Minyak Tinggi</t>
+          <t>Henderson Pilih Chelsea karena Xabi Alonso</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:17:17 +0700</t>
+          <t>Tue, 04 Aug 2026 07:00:05 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mereka meraup terlalu banyak uang dari kelangkaan ini. Saya tidak menyukainya, ujar Trump.</t>
+          <t>Nama besar Xabi Alonso di sepakbola tentu jadi magnet untuk banyak pesepakbola, tak terkecuali Jordan Henderson. Alonso jadi alasannya gabung Chelsea.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603261/trump-tak-suka-exxon-chevron-untung-gede-gara-gara-harga-minyak-tinggi</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603196/henderson-pilih-chelsea-karena-xabi-alonso</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jordan-henderson-1785800731761_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4695,33 +4695,33 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tips Aman Pakai QRIS agar Terhindar dari Penipuan</t>
+          <t>Statistik Indonesia Vs Vietnam: Efektivitas Jadi Pembeda</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:05:09 +0700</t>
+          <t>Tue, 04 Aug 2026 06:30:45 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>QRIS adalah metode pembayaran digital praktis. Pelajari tips aman bertransaksi, cara menggunakan QRIS, dan cara mengenali penipuan untuk keamanan Anda.</t>
+          <t>Statistik saat Timnas Indonesia kalah 0-3 dari Vietnam. Tim Garuda tumpul di depan dan rapuh di belakang hingga kalah telak di kandang.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8602406/tips-aman-pakai-qris-agar-terhindar-dari-penipuan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603163/statistik-indonesia-vs-vietnam-efektivitas-jadi-pembeda</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/tips-aman-pakai-qris-agar-terhindar-dari-penipuan-1785745583872.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513806_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4733,33 +4733,33 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pernak-pernik HUT Ke-81 RI Mulai Diburu di Pasar Asemka</t>
+          <t>Pochettino Teken Kontrak Baru, Latih Timnas AS sampai 2030</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:00:44 +0700</t>
+          <t>Tue, 04 Aug 2026 06:00:30 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Permintaan pernak-pernik kemerdekaan mulai meningkat menjelang HUT Ke-81 RI. Pedagang Pasar Asemka mencatat penjualan naik sekitar 20 persen sejak akhir Juli.</t>
+          <t>Karier Mauricio Pochettino sebagai pelatih Timnas Amerika Serikat masih panjang. Pria asal Argentina itu baru saja meneken kontrak baru.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8601820/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka</t>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8603160/pochettino-teken-kontrak-baru-latih-timnas-as-sampai-2030</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka-1785728519984_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/mauricio-pochettino-1785784945554_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4771,33 +4771,33 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KSP &amp;amp; Bahlil  Buka Suara soal Ekspor 'Harta Karun' RI</t>
+          <t>Indonesia Susah Banget Tembus Pertahanan Vietnam</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:25:00 +0700</t>
+          <t>Tue, 04 Aug 2026 05:00:30 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kantor Staf Presiden (KSP) buka suara terkait soal harta karun Indonesia yakni logam tanah jarang.</t>
+          <t>Timnas Indonesia mati kutu saat menjamu Vietnam dalam lanjutan Piala AFF 2026. Garuda kesulitan menembus pertahanan lawan dan jadi bulan-bulanan. Duh!</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603108/ksp-bahlil-buka-suara-soal-ekspor-harta-karun-ri</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603148/indonesia-susah-banget-tembus-pertahanan-vietnam</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/09/logam-tanah-jarang-jadi-harta-karun-yang-diincar-dunia-3_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4809,33 +4809,33 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Musim Cuan 17 Agustus Dimulai, Pedagang Bendera Mulai Gelar Lapak</t>
+          <t>Indonesia Digebuk Vietnam, Nadeo: Kami Main Kurang Bagus</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:56:08 +0700</t>
+          <t>Tue, 04 Aug 2026 04:00:05 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pedagang bendera di Jakarta mulai ramai menjelang HUT ke-81 RI, namun penjualan menurun.</t>
+          <t>Timnas Indonesia digebuk Vietnam di hadapan pendukung sendiri. Kiper Nadeo Argawinata mewakili rekan setimnya meminta maaf atas hasil buruk tersebut.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603046/musim-cuan-17-agustus-dimulai-pedagang-bendera-mulai-gelar-lapak</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603151/indonesia-digebuk-vietnam-nadeo-kami-main-kurang-bagus</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pedagang-bendera-1785742448675_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nadeo-argawinata-1785776694751_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4847,33 +4847,33 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Pameran Wastra Sultra Dorong Ekonomi Kreatif Perajin Lokal</t>
+          <t>'Arsenal Sudah Pasti Mau Pertahankan Gelar, Tekanan Ada di Rival'</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:30:56 +0700</t>
+          <t>Tue, 04 Aug 2026 03:00:30 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pameran kain tenun dan baju adat Sultra di Museum Sultra menjadi upaya melestarikan wastra sekaligus mengenalkan kekayaan budaya daerah.</t>
+          <t>Christos Tzolis menyatakan bahwa Arsenal siap untuk mempertahankan gelar. Pemain baru Meriam London itu menyebut tekanan ada di rival.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602729/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal</t>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603149/arsenal-sudah-pasti-mau-pertahankan-gelar-tekanan-ada-di-rival</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal-1785754770623_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/arsenal-1785694598503_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4885,33 +4885,33 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Impor RI Naik Tajam, Ini Biang Keroknya</t>
+          <t>Jelang Tampil di AXCR 2026, Memen Harianto Dapat 'Tenaga' Baru</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 02:45:20 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai impor Indonesia meningkat tajam pada Juni 2026 mencapai US$ 25,9 miliar atau naik 34,27%.</t>
+          <t>Memen Harianto terus mempersiapkan diri jelang Asia Cross Country Rally (AXCR) 2026. Memen mendapat suntikan tenaga baru, apa itu?</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603040/impor-ri-naik-tajam-ini-biang-keroknya</t>
+          <t>https://sport.detik.com/sport-lain/d-8603162/jelang-tampil-di-axcr-2026-memen-harianto-dapat-tenaga-baru</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/09/tanjung-priok-tetap-sibuk-di-tengah-tekanan-dolar-harapan-ekspor-menguat-1780979463918_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/indonesia-cross-country-rally-team-1785786307522_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PSSI Cuan Rp 722 Miliar, Tetap Terbuka Bantuan dari Pemerintah</t>
+          <t>Erick Thohir Maju Jadi Ketum PSSI Lagi Tahun Depan?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:30:30 +0700</t>
+          <t>Tue, 04 Aug 2026 02:00:05 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PSSI sukses mengumpulkan pendapatan fantastis Rp722 miliar. Angka tersebut sudah cukup buat PSSI, tetapi tetap terbuka jika ada tawaran bantuan pemerintah.</t>
+          <t>Erick Thohir tidak menutup peluang mencalonkan diri kembali menjadi Ketua Umum PSSI. Tapi sebelum itu, ia akan berkonsultasi dengan pemerintah dan FIFA dulu.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604319/pssi-cuan-rp-722-miliar-tetap-terbuka-bantuan-dari-pemerintah</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603147/erick-thohir-maju-jadi-ketum-pssi-lagi-tahun-depan</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menpora-erick-thohir-1783676745865.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pssi-1785758655620_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4958,2744 +4958,8 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Indonesia Punya 2 Srikandi di Asia Cross Country Rally 2026</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 23:25:00 +0700</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Asia Cross Country Rally 2026 rupanya menarik minat para pereli wanita Indonesia. Mereka adalah Lody Natasha dan Satsy Laksamana.</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sport-lain/d-8604616/indonesia-punya-2-srikandi-di-asia-cross-country-rally-2026</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/lody-natasha-dan-satsy-laksamana-1785860860805_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 23:00:00 +0700</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Final Piala Presiden 2026 akhirnya mendapatkan kontestannya. Persib Bandung vs Persebaya Surabaya akan tersaji di partai puncak.</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604606/final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492015_169.png?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Piala AFF: Indonesia Dijagokan Taklukkan Singapura, Lolos ke Semifinal</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 22:40:30 +0700</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia akan dijamu Timnas Singapura dalam laga penentuan tiket ke semifinal Piala AFF 2026. Garuda dijagokan mengalahkan The Lions.</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604294/piala-aff-indonesia-dijagokan-taklukkan-singapura-lolos-ke-semifinal</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_43.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Cara Memen Agar Mobilnya Siap Taklukkan Medan Berat AXCR 2026</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 22:25:00 +0700</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Memen Harianto akan membawa nama Indonesia di Asia Cross Country Rally (AXCR) 2026. Dia melakukan persiapan secara maksimal, terutama untuk mobilnya.</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sport-lain/d-8604594/cara-memen-agar-mobilnya-siap-taklukkan-medan-berat-axcr-2026</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/memen-harianto-1785860948781_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Persebaya Vs Arema: Bajul Ijo Menang 1-0, Lolos ke Final Piala Presiden</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 22:17:39 +0700</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Persebaya Surabaya meraih kemenangan 1-0 atas Arema FC di semifinal Piala Presiden 2026. Persebaya lolos ke final untuk menghadapi Persib Bandung.</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604584/persebaya-vs-arema-bajul-ijo-menang-1-0-lolos-ke-final-piala-presiden</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Hasil Piala AFF 2026: Thailand Atasi Filipina 1-0</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 21:58:26 +0700</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Thailand melanjutkan start positifnya di Piala AFF 2026. Tim War Elephants menang tipis 1-0 atas Filipina dan menguasai pucuk klasemen Grup B.</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604566/hasil-piala-aff-2026-thailand-atasi-filipina-1-0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Vicario dan Suzuki Diincar Juventus, Buffon Bilang Begini!</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 21:45:05 +0700</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Juventus dikabarkan menjadikan Guglielmo Vicario dan Zion Suzuki sebagai kandidat kiper anyar. Bagaimana menurut Gianluigi Buffon?</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604289/vicario-dan-suzuki-diincar-juventus-buffon-bilang-begini</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/04/gianluigi-buffon_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Pelajaran dari Singapura Sukses Antar Vietnam Cukur Indonesia</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 21:30:15 +0700</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Vietnam banyak belajar dari hasil imbang melawan Singapura. Pemilihan strategi yang tepat sukses antar Vietnam mencukur Timnas Indonesia 3-0.</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604285/pelajaran-dari-singapura-sukses-antar-vietnam-cukur-indonesia</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>PBSI Cari Pasangan untuk Adnan Maulana</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 21:20:37 +0700</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>PP PBSI masih mencari pasangan untuk Adnan Maulana. Itu setelah rekan tandemnya yang lama, Indah Cahya Sari Jamil, dipasangkan dengan pemain lain.</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/raket/d-8604509/pbsi-cari-pasangan-untuk-adnan-maulana</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/02/adnan-maulanaindah-cahya-sari-jamil-1780382604246_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Matthijs de Ligt Belum Bisa Gabung ke MU</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 21:15:40 +0700</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Manchester United masih belum bisa diperkuat bek tengahnya, Matthijs de Ligt. Dirinya masih belum pulih setelah operasi cedera punggung.</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603854/matthijs-de-ligt-belum-bisa-gabung-ke-mu</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/07/matthijs-de-ligt-1775546584882.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Jelang Lawan Singapura, Timnas Indonesia Butuh Pemulihan Moral</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 21:00:30 +0700</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia sangat terpukul usai kalah 0-3 dari Vietnam. Skuad Garuda kini harus memulihkan moral jelang melawan Singapura.</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604284/jelang-lawan-singapura-timnas-indonesia-butuh-pemulihan-moral</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Jorge Martin Tak Sabar Lanjutkan Duel Sengit Perebutan Gelar MotoGP 2026!</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 20:50:40 +0700</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Jorge Martin antusias menatap paruh kedua MotoGP 2026. Ia yakin persaingan gelar juara dunia akan semakin sengit karena lima pebalap hanya terpaut 24 poin.</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/moto-gp/d-8604324/jorge-martin-tak-sabar-lanjutkan-duel-sengit-perebutan-gelar-motogp-2026</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/moto-motogp-ned-1782675298213_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Mulai Tahun Depan Piala Presiden untuk Timnas Indonesia, Tidak Lagi Klub</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 20:45:15 +0700</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Ketum PSSI Erick Thohir mengungkapkan Piala Presiden mulai tahun depan tidak lagi menjadi turnamen pramusim klub, melainkan jadi agenda Timnas Indonesia.</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604194/mulai-tahun-depan-piala-presiden-untuk-timnas-indonesia-tidak-lagi-klub</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Kovacic: Anderson Bikin Lini Tengah Man City Lebih Bertenaga</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 20:30:50 +0700</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Mateo Kovacic antusias dengan Elliott Anderson, meski itu juga berarti persaingan lini tengah Manchester City kian ketat. Ia yakin tim makin kuat.</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604197/kovacic-anderson-bikin-lini-tengah-man-city-lebih-bertenaga</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/29/elliott-anderson-1764354213557_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Usai Indonesia Dihajar Vietnam, Hubner Saling Sindir dengan Do Hoang Hen</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 20:15:00 +0700</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia dihajar Timnas Vietnam dalam laga lanjutan Piala AFF 2026. Justin Hubner saling sindir dengan pemain Golden Star Warriors, Do Hoang Hen.</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604196/usai-indonesia-dihajar-vietnam-hubner-saling-sindir-dengan-do-hoang-hen</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513456_43.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Buffon Percaya sama Mancini, Semoga Italia Lolos ke Piala Dunia</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 20:00:40 +0700</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Sepakbola Italia bergejolak belakangan ini dalam penunjukan pelatih baru. Buffon mau drama itu berakhir, percayakan ke juru taktik baru Roberto Mancini.</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604208/buffon-percaya-sama-mancini-semoga-italia-lolos-ke-piala-dunia</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/03/gianluigi-buffon-1748885612603.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Marco Bezzecchi Belum 100%, tapi Siap Comeback di MotoGP Inggris 2026!</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 19:50:50 +0700</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Marco Bezzecchi siap kembali balapan di MotoGP Inggris 2026 meski mengaku belum pulih 100 persen usai menjalani operasi tulang selangka dan lutut.</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/moto-gp/d-8604281/marco-bezzecchi-belum-100-tapi-siap-comeback-di-motogp-inggris-2026</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/15/motor-motogp-germany-1784050516185_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Vietnam 'Oper' Tekanan ke Indonesia</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 19:40:30 +0700</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Vietnam datang dengan tekanan dan kini melemparnya ke Indonesia. Mampukah skuad Garuda merespons tekanan itu dan keluar dari posisi terjepit.</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604184/vietnam-oper-tekanan-ke-indonesia</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Liverpool Enggan Jual Gakpo, tapi Kalau Tottenham Kasih Harga Bagus...</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 19:20:45 +0700</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur meminati Cody Gakpo dari Liverpool. The Reds mau mempertahankan sang winger, tapi bakal goyah kalau dikasih harga bagus.</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604186/liverpool-enggan-jual-gakpo-tapi-kalau-tottenham-kasih-harga-bagus</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/05/cody-gakpo-1754352181260.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Detak Jantung Marc Marquez Bisa Ungkap Kans Juara MotoGP 2026</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 19:10:20 +0700</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Detak jantung Marc Marquez saat MotoGP Inggris diyakini bisa menjadi indikator keberhasilan pemulihan fisiknya terkait kans mengejar gelar dunia MotoGP 2026.</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/moto-gp/d-8604170/detak-jantung-marc-marquez-bisa-ungkap-kans-juara-motogp-2026</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-1783860046236_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>John Herdman: Indonesia Asyik di Depan, Jadi Lupa Pertahanan</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 19:00:50 +0700</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Pelatih Timnas Indonesia John Herdman menyebut timnya terlalu asyik main di depan saat jumpa Vietnam. Hasilnya timnya malah kecolongan di lini pertahanan.</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604183/john-herdman-indonesia-asyik-di-depan-jadi-lupa-pertahanan</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/27/gaya-nyentrik-john-herdman-kawal-timnas-garuda-1774628369095.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Singapura Vs Indonesia: Ulangan Situasi di Manila Sedekade Lalu</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 18:40:45 +0700</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Indonesia menjalani laga hidup dan mati melawan Singapura di Piala AFF 2026. Laga ini menjadi ulangan persaingan Garuda melawan The Lions sedekade lalu.</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603914/singapura-vs-indonesia-ulangan-situasi-di-manila-sedekade-lalu</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/11/26/54e9d3f7-5e6d-46d8-b5d2-e2d0149535a8_169.jpg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Malut United Resmi Ganti Nama Jadi Java United, Pindah Markas ke Semarang</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 18:30:00 +0700</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Malut United resmi berganti nama menjadi Java United dan memindahkan markas dari Ternate ke Semarang.</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604279/malut-united-resmi-ganti-nama-jadi-java-united-pindah-markas-ke-semarang</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/java-united-1785770401869_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Chelsea Mulai Bersih-bersih</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 18:20:15 +0700</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Chelsea punya 40 pemain di dalam skuadnya. Bursa transfer musim panas 2026 masih buka sampai 1 September, Si Biru kini saatnya bersih-bersih.</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603920/chelsea-mulai-bersih-bersih</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/09/chelsea-1778261458229.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>RI Bawa Pulang 15 Medali dari Kejuaraan Asia MMA, Kini Fokus Asian Games 2026</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 18:10:25 +0700</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Tim MMA Indonesia meraih 15 medali, termasuk lima emas, di GAMMA Asian Championships 2026.</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sport-lain/d-8604192/ri-bawa-pulang-15-medali-dari-kejuaraan-asia-mma-kini-fokus-asian-games-2026</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gamma-asian-championships-2026-1785838947680_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Erick Thohir: Saya Tetap Percaya pada John Herdman</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 18:00:10 +0700</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia kalah 0-3 dari Vietnam, kans ke semifinal Piala AFF 2026 terancam. Ketum PSSI Erick Thohir membela pelatih John Herdman.</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603911/erick-thohir-saya-tetap-percaya-pada-john-herdman</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/13/selamat-datang-john-herdman-pelatih-baru-timnas-indonesia-1768277980430.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Dirumorkan Kembali ke Italia, Kovacic: Man City Masih Mengandalkanku</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 17:45:40 +0700</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Mateo Kovacic dirumorkan kembali ke Italia, dengan kabar Juventus dan Inter Milan meminati. Tapi gelandang senior itu bilang masih diandalkan Manchester City.</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603894/dirumorkan-kembali-ke-italia-kovacic-man-city-masih-mengandalkanku</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/20/wolverhampton-wanderers-manchester-city_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Persib Vs Persija: Menang 2-1, Maung Bandung ke Final Piala Presiden 2026</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 17:31:55 +0700</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Persib Bandung mengalahkan Persija Jakarta di semifinal Piala Presiden 2026. Pasukan Igor Tolic pun melaju ke final.</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604212/persib-vs-persija-menang-2-1-maung-bandung-ke-final-piala-presiden-2026</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Bagas Maulana Dinilai Cocok ke Ganda Campuran, Ini Alasannya</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 17:20:10 +0700</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Pelatih ganda putra Antonius Budi Ariantho menjelaskan alasan Bagas Maulana dipindahkan ke sektor ganda campuran.</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/raket/d-8604165/bagas-maulana-dinilai-cocok-ke-ganda-campuran-ini-alasannya</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/12/bagas-maulana-1_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Vietnam Tahu Caranya Keluar dari Tekanan</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 17:15:15 +0700</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Vietnam datang ke Indonesia dengan tekanan besar usai ditahan Singapura. The Golden Star Warriors merespons dengan cemerlang.</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603861/vietnam-tahu-caranya-keluar-dari-tekanan</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Dear Liverpool, Ini Isak yang Baru</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 17:00:25 +0700</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Alexander Isak mengaku sudah pulih 100 persen. Sang striker siap berikan yang terbaik buat Liverpool di musim baru!</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603859/dear-liverpool-ini-isak-yang-baru</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/alexander-isak-1778251850354.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia Masih Berani Main High Pressing, John?</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 16:40:40 +0700</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia sangat buruk dalam transisi bertahan dengan permainan high pressing. Pelatih John Herdman apakah akan mengubah cara bermain Garuda?</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603770/timnas-indonesia-masih-berani-main-high-pressing-john</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Piala AFF: Indonesia Pernah Lima Kali Gagal ke Semifinal</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 16:20:15 +0700</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia sedang di ujung tanduk di Piala AFF 2026. Sepanjang sejarah pesta sepakbola ASEAN, Skuad Garuda pernah lima kali gagal ke semifinal.</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603776/piala-aff-indonesia-pernah-lima-kali-gagal-ke-semifinal</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_43.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Welbeck Kemarin Hobi Jebol Chelsea, Kini Jagoan Baru The Blues</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 16:00:15 +0700</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Chelsea resmi mendatangkan Danny Welbeck. Sang striker veteran lumayan hobi jebol gawang The Blues dulu, tapi kini diharapkan jadi jagoan.</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8603780/welbeck-kemarin-hobi-jebol-chelsea-kini-jagoan-baru-the-blues</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/danny-welbeckchelseabursa-transfer-chelsea-1785602779561.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Ini Sebab PBSI Belum Rilis Daftar Pemain di Asian Games</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 15:50:00 +0700</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Nama-nama pebulutangkis Indonesia yang akan diturunkan di Asian Games 2026 belum final. PBSI masih akan melihat hasil dari Kejuaraan Dunia pada 17-23 Agustus.</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/raket/d-8603931/ini-sebab-pbsi-belum-rilis-daftar-pemain-di-asian-games</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/26/logo-pbsi.webp?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>John Herdman ke Suporter: Kita Menang Bersama, Kalah Juga Bersama</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 15:40:25 +0700</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia dihajar Timnas Vietnam saat menjalani laga kandang di Piala AFF 2026. John Herdman berjanji Skuad Garuda akan bangkit.</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603741/john-herdman-ke-suporter-kita-menang-bersama-kalah-juga-bersama</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/31/herdman-janji-bangkit-usai-kekalahan-targetkan-indonesia-ke-piala-dunia-2030-1774891836257_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Awas MU, Bayern Munich Minati Benjamin Sesko</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 15:20:10 +0700</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Bayern Munich menaruh minat pada striker Man United, Benjamin Sesko. Tapi Bayern enggak mau buru-buru merekrutnya dulu, mungkin beberapa tahun mendatang nanti.</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603737/awas-mu-bayern-munich-minati-benjamin-sesko</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/02/benjamin-sesko-1772389311489.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Viet Anh Berdarah-Darah untuk Tuntaskan Dendam ke Indonesia</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 15:00:45 +0700</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Vietnam sukses membabat Indonesia 3-0 dalam laga Grup A Piala AFF 2026. Bek Bui Hoang Viet Anh sangat puas Golden Star Warriors berhasil balas dendam.</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603740/viet-anh-berdarah-darah-untuk-tuntaskan-dendam-ke-indonesia</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Asian Games 2026: Bulutangkis Beregu Putra Jadi Asa Indonesia Raih Emas</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:51:15 +0700</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Chef de Mission Indonesia Todotua Pasaribu berharap bulutangkis bisa mendapatkan medali emas di Asian Games 2026. Secara khusus nomor ganda putra.</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/raket/d-8603821/asian-games-2026-bulutangkis-beregu-putra-jadi-asa-indonesia-raih-emas</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/06/ilustrasi-bulutangkis.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Bermain Buruk, Indonesia Dipecundangi Vietnam!</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:44:50 +0700</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Apakah Indonesia bisa menjaga asa untuk tampil di semifinal Piala AFF 2026?</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/sepakbola-indonesia/d-8603690/bermain-buruk-indonesia-dipecundangi-vietnam</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detiksore-4-agustus-2026-1785825691822_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Marselino Ferdinan Tak Bisa Main di Piala AFF 2026!</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:40:10 +0700</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Kabar buruk menghampiri Timnas Indonesia di tengah gelaran Piala AFF 2026. Marselino Ferdinan tak bisa memperkuat Skuad Garuda!</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603636/marselino-ferdinan-tak-bisa-main-di-piala-aff-2026</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/12/marselino-ferdinan_43.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Usai Permalukan Indonesia, Vietnam Dapat Bonus Rp1,37 Miliar</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:20:10 +0700</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Timnas Vietnam mempermalukan Timnas Indonesia di Piala AFF 2026. Golden Star Warriors mendapat bonus 2 miliar dong atau setara Rp1,37 miliar.</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603633/usai-permalukan-indonesia-vietnam-dapat-bonus-rp1-37-miliar</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Presiden FIFA Batal Naik Gaji 500 Persen</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:00:15 +0700</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Presiden FIFA Gianni Infantino diketahui bakal naik gaji 525 persen andai wacana jual saham Piala Dunia sukses. Wacana itu batal, nggak gaji naik deh!</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603662/presiden-fifa-batal-naik-gaji-500-persen</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/16/gianni-infantino.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Sebuah Perenungan Rizky Ridho</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 13:40:40 +0700</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Rizky Ridho mengakui kesalahannya dalam kekalahan Indonesia dari Vietnam. Dia akan mencoba merenungkannya untuk berbenah di laga selanjutnya.</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603568/sebuah-perenungan-rizky-ridho</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Bagas Maulana ke Ganda Campuran, Tandem sama Indah Cahya</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 13:35:30 +0700</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>PBSI kembali jajal kombinasi baru di sektor ganda campuran. Kali ini, Bagas Maulana dipasangkan dengan Indah Cahya Sari Jamil!</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/raket/d-8603660/bagas-maulana-ke-ganda-campuran-tandem-sama-indah-cahya</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/22/fajarfikri-kalahkan-bagasleo-di-indonesia-masters-2026-1769070561744.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Jika Arsenal Dapatkan Vinicius...</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 13:20:25 +0700</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Situasi Vinicius Jr di Madrid masih tanda tanya, rumor Arsenal mau merekrutnya juga terus mencuat. Wilshere bakal girang betul andai The Gunners mendapatkannya.</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603570/jika-arsenal-dapatkan-vinicius</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/02/vinicius-jr.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Indonesia Vs Vietnam: Sayap-sayap Lemah Garuda</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 13:00:30 +0700</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia dibenamkan Timnas Vietnam di Piala AFF 2026. Sayap-sayap Garuda terlihat lemah di hadapan Golden Star Warriors.</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603566/indonesia-vs-vietnam-sayap-sayap-lemah-garuda</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_43.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Posisi di FIFA Terancam, Infantino Minta Dukungan Trump?</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 12:40:25 +0700</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Posisi Gianni Infantino di FIFA terancam usai geger wacana jual saham Piala Dunia. Pria asal Swiss itu kabarnya meminta dukungan Presiden AS Donald Trump.</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603451/posisi-di-fifa-terancam-infantino-minta-dukungan-trump</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/presiden-as-donald-trump-1783299814038_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Balik Latihan di Madrid, Vinicius Segera Perpanjang Kontrak</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 12:20:30 +0700</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Vinicius Jr dilaporkan segera memperpanjang kontraknya setelah sudah kembali berlatih dengan Real Madrid. Ia memutuskan bertahan di El Real.</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/liga-spanyol/d-8603450/balik-latihan-di-madrid-vinicius-segera-perpanjang-kontrak</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/21/vinicius-jr-1768973038339_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>8 Data Fakta usai Indonesia Dihantam Vietnam: Bulan Madu Herdman Selesai</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 12:00:20 +0700</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia menelan kekalahan telak dari Timnas Vietnam di Piala AFF 2026. Bulan madu John Herdman bersama Skuad Garuda selesai.</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603448/8-data-fakta-usai-indonesia-dihantam-vietnam-bulan-madu-herdman-selesai</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735_43.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Flick: Dear Barca, Mana Striker Barunya Nih?</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 11:40:10 +0700</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Belum ada juga pemain baru datang untuk menggantikan Robert Lewandowski. Pelatih Barcelona Hansi Flick mencoba sabar menunggu.</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603267/flick-dear-barca-mana-striker-barunya-nih</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hansi-flick-1785806312405_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Bikin Pantun untuk Fermin Aldeguer &amp;amp; Alex Marquez, Dapatkan Saldo E-Wallet</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 11:22:46 +0700</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Ikuti kuis kreatif dari detikcom dan Bold Riders! Buat pantun lucu untuk Fermin Aldeguer atau Alex Marquez dan menangkan saldo e-wallet Rp 250 ribu!</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/moto-gp/d-8603482/bikin-pantun-untuk-fermin-aldeguer-alex-marquez-dapatkan-saldo-e-wallet</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/la-bold-1785817343343.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Direktur RB Leipzig: Kata Siapa Diomande Sudah 'Here We Go'?</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 11:20:45 +0700</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Yan Diomande sempat diklaim tinggal selangkah lagi gabung Real Madrid. Kabar itu dibantah keras petinggi RB Leipzig.</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603249/direktur-rb-leipzig-kata-siapa-diomande-sudah-here-we-go</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/yann-diomande-1785778891457_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Jadwal Semifinal Piala Presiden: Persib Vs Persija, Persebaya Vs Arema</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 11:00:41 +0700</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Jadwal semifinal Piala Presiden 2026 mempertemukan Persib vs Persija dan Persebaya vs Arema. Simak jadwal semifinal hingga final.</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603340/jadwal-semifinal-piala-presiden-persib-vs-persija-persebaya-vs-arema</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/12/980f4b19-e319-452f-bd84-74e7316325ce_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Liverpool Disarankan Pulangkan Alexander-Arnold</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 10:40:35 +0700</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Liverpool disarankan memulangkan Trent Alexander-Arnold yang kesulitan di Real Madrid. Umpan silang akurat dari TAA dinilai sangat dibutuhkan Alexander Isak.</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603306/liverpool-disarankan-pulangkan-alexander-arnold</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/13/trent-alexander-arnold-1773385024632_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>John Herdman Rasakan Kekalahan Kedua Latih Indonesia</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 10:20:30 +0700</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia jadi bulan-bulanan Vietnam di Piala AFF 2026. Ini menjadi kekalahan kedua Garuda di bawah asuhan John Herdman.</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603299/john-herdman-rasakan-kekalahan-kedua-latih-indonesia</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/john-herdman-1785718686520_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Bernardo Silva Tak Masalah Mainkan Banyak Peran di Madrid</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 10:00:20 +0700</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Bernardo Silva siap dimainkan di berbagai posisi bersama Real Madrid. Ia punya kemampuan untuk memainkan sejumlah peran di lapangan.</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603262/bernardo-silva-tak-masalah-mainkan-banyak-peran-di-madrid</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2288876689-1785802177577_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Indonesia Dikalahkan Vietnam, John Herdman Minta Garuda Tetap Fokus</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 09:40:30 +0700</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia kalah 0-3 dari Vietnam pada matchday ketiga Piala AFF 2026. Pelatih Garuda John Herdman meminta timnya untuk tetap fokus.</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603309/indonesia-dikalahkan-vietnam-john-herdman-minta-garuda-tetap-fokus</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Ferran Mau Saja Bertahan di Barca Asalkan...</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 09:20:05 +0700</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Ferran Torres tidak masalah jika akhirnya bertahan di Barcelona. Tapi, ada satu syarat yang harus dipenuhi Los Cules, apa itu?</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603308/ferran-mau-saja-bertahan-di-barca-asalkan</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ferran-torres-1785808347370_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Persiapan Vietnam Biasa Saja, tapi Bisa Bantai Indonesia</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 09:00:10 +0700</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Timnas Vietnam mengganyang Indonesia di Piala AFF 2026. Pelatih Kim Sang-sik mengaku tak mempersiapkan timnya secara khusus sebelum pertandingan.</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603248/persiapan-vietnam-biasa-saja-tapi-bisa-bantai-indonesia</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/timnas-vietnam-1785766971799_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Tinggalkan Madrid, Gonzalo Garcia Gabung Fulham</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:30:20 +0700</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Gonzalo Garcia resmi meninggalkan Real Madrid. Penyerang muda Spanyol itu melanjutkan kariernya bersama Fulham.</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603244/tinggalkan-madrid-gonzalo-garcia-gabung-fulham</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gonzalo-garcia-1785804604431_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Kualifikasi GTR Ultra Tutup 7 Agustus, Jangan Sampai Gagal Ikut Trail Run Ini</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:15:47 +0700</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Kabar penting buat pelari trail, pendaftaran kualifikasi GTR Ultra 2026 resmi akan ditutup 7 Agustus 2026 pukul 23.30 WIB.</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sportstyle/d-8603071/kualifikasi-gtr-ultra-tutup-7-agustus-jangan-sampai-gagal-ikut-trail-run-ini</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/gtr-ultra-2026-1773216163821_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Bantai Indonesia, Vietnam Lanjutkan Rekor Tak Terkalahkan Sejak 2024</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:00:05 +0700</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Vietnam melanjutkan catatan tak terkalahkan usai menumbangkan Indonesia. Golden Star Warriors tak terkalahkan dalam 21 laga terakhir.</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603202/bantai-indonesia-vietnam-lanjutkan-rekor-tak-terkalahkan-sejak-2024</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Nguyen Hai Long Bobol Indonesia, Pamer Patch Emas Vietnam</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 07:30:40 +0700</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Pemain Vietnam Nguyen Hai Long membobol gawang Timnas Indonesia. Dia merayakan golnya dengan memamerkan patch emas tanda juara bertahan Piala AFF.</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603197/nguyen-hai-long-bobol-indonesia-pamer-patch-emas-vietnam</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Henderson Pilih Chelsea karena Xabi Alonso</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 07:00:05 +0700</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Nama besar Xabi Alonso di sepakbola tentu jadi magnet untuk banyak pesepakbola, tak terkecuali Jordan Henderson. Alonso jadi alasannya gabung Chelsea.</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603196/henderson-pilih-chelsea-karena-xabi-alonso</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jordan-henderson-1785800731761_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Statistik Indonesia Vs Vietnam: Efektivitas Jadi Pembeda</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:30:45 +0700</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Statistik saat Timnas Indonesia kalah 0-3 dari Vietnam. Tim Garuda tumpul di depan dan rapuh di belakang hingga kalah telak di kandang.</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603163/statistik-indonesia-vs-vietnam-efektivitas-jadi-pembeda</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513806_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Pochettino Teken Kontrak Baru, Latih Timnas AS sampai 2030</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:00:30 +0700</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Karier Mauricio Pochettino sebagai pelatih Timnas Amerika Serikat masih panjang. Pria asal Argentina itu baru saja meneken kontrak baru.</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8603160/pochettino-teken-kontrak-baru-latih-timnas-as-sampai-2030</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/mauricio-pochettino-1785784945554_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Indonesia Susah Banget Tembus Pertahanan Vietnam</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:00:30 +0700</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia mati kutu saat menjamu Vietnam dalam lanjutan Piala AFF 2026. Garuda kesulitan menembus pertahanan lawan dan jadi bulan-bulanan. Duh!</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603148/indonesia-susah-banget-tembus-pertahanan-vietnam</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Indonesia Digebuk Vietnam, Nadeo: Kami Main Kurang Bagus</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:00:05 +0700</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Timnas Indonesia digebuk Vietnam di hadapan pendukung sendiri. Kiper Nadeo Argawinata mewakili rekan setimnya meminta maaf atas hasil buruk tersebut.</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603151/indonesia-digebuk-vietnam-nadeo-kami-main-kurang-bagus</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nadeo-argawinata-1785776694751_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>'Arsenal Sudah Pasti Mau Pertahankan Gelar, Tekanan Ada di Rival'</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:00:30 +0700</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Christos Tzolis menyatakan bahwa Arsenal siap untuk mempertahankan gelar. Pemain baru Meriam London itu menyebut tekanan ada di rival.</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603149/arsenal-sudah-pasti-mau-pertahankan-gelar-tekanan-ada-di-rival</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/arsenal-1785694598503_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Jelang Tampil di AXCR 2026, Memen Harianto Dapat 'Tenaga' Baru</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:45:20 +0700</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Memen Harianto terus mempersiapkan diri jelang Asia Cross Country Rally (AXCR) 2026. Memen mendapat suntikan tenaga baru, apa itu?</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sport-lain/d-8603162/jelang-tampil-di-axcr-2026-memen-harianto-dapat-tenaga-baru</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/indonesia-cross-country-rally-team-1785786307522_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Erick Thohir Maju Jadi Ketum PSSI Lagi Tahun Depan?</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:00:05 +0700</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Erick Thohir tidak menutup peluang mencalonkan diri kembali menjadi Ketua Umum PSSI. Tapi sebelum itu, ia akan berkonsultasi dengan pemerintah dan FIFA dulu.</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603147/erick-thohir-maju-jadi-ketum-pssi-lagi-tahun-depan</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pssi-1785758655620_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H191"/>
+  <autoFilter ref="A1:H119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-04.xlsx
+++ b/data/berita_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2035,33 +2035,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mayat Mutilasi di Depok Diautopsi ke RS Polri, Identitas Belum Diketahui</t>
+          <t>Tambak Modern Udang Vaname Hadirkan Solusi Budi Daya Efisien</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:05:44 +0700</t>
+          <t>Tue, 04 Aug 2026 23:00:40 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Made menjelaskan potongan tubuh korban tidak berada di lokasi. Saat ini polisi masih melakukan penyelidikan dengan pemeriksaan dokter forensik RS Polri.</t>
+          <t>Budi daya udang vaname dengan sistem tertutup dikembangkan di kawasan industri Semarang. Teknologi ini menghemat air juga meningkatkan produktivitas tambak.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604519/mayat-mutilasi-di-depok-diautopsi-ke-rs-polri-identitas-belum-diketahui</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603831/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/23/penemuan-mayat-perempuan-duduk-di-melaya_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tambak-modern-udang-vaname-hadirkan-solusi-budi-daya-efisien-1785830418949_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2073,33 +2073,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Saat Netanyahu Sebut Gaza Sama dengan Korut</t>
+          <t>Harga Minyak Langsung Turun Usai AS-Iran Setop Serangan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:01:48 +0700</t>
+          <t>Tue, 04 Aug 2026 22:35:07 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Perdana Menteri (PM) Israel Benjamin Netanyahu kembali bikin pernyataan kontroversial. Dia menyamakan Jalur Gaza di Palestina dengan Korea Utara (Korut).</t>
+          <t>Harga minyak dunia turun nyaris 4% pada Selasa (4/8/2026) dan menyentuh level terendah dalam tiga pekan.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.detik.com/internasional/d-8604514/saat-netanyahu-sebut-gaza-sama-dengan-korut</t>
+          <t>https://finance.detik.com/moneter/d-8604597/harga-minyak-langsung-turun-usai-as-iran-setop-serangan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/29/2288038725-1785305349518_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/24/harga-minyak-dunia-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2111,33 +2111,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DPD RI Raih Penghargaan Opini WTP ke-20 Berturut-turut dari BPK</t>
+          <t>604.923 Rekening Terkait Scam Diblokir!</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:59:59 +0700</t>
+          <t>Tue, 04 Aug 2026 22:11:04 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>DPD RI meraih Opini WTP ke-20 dari BPK RI, mencerminkan tata kelola keuangan yang transparan dan akuntabel. Komitmen untuk perbaikan berkelanjutan ditekankan.</t>
+          <t>OJK bersama Indonesia Anti-Scam Center (IASC) terus memperkuat upaya pemberantasan kasus keuangan ilegal dan penipuan di sektor jasa keuangan.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604511/dpd-ri-raih-penghargaan-opini-wtp-ke-20-berturut-turut-dari-bpk</t>
+          <t>https://finance.detik.com/moneter/d-8604576/604-923-rekening-terkait-scam-diblokir</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/dpd-raih-opini-wtp-dari-bpk-1785851361404_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/24/ilustrasi-telepon-scam-atau-penipuan-1766569797414_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2149,33 +2149,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Terobosan BPA Kejagung, Kini Punya Sistem AI Awasi Proses Pemulihan Aset</t>
+          <t>Warga RI Doyan Pakai Paylater, Ini Buktinya</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:59:40 +0700</t>
+          <t>Tue, 04 Aug 2026 21:14:02 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BPA Kejagung adakan FGD untuk terapkan AI dalam pemulihan aset. Fokus pada manajemen risiko dan transformasi penegakan hukum menuju Visi 2035.</t>
+          <t>Penggunaan layanan Buy Now Pay Later (BNPL) atau paylater masih meningkat.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8604513/terobosan-bpa-kejagung-kini-punya-sistem-ai-awasi-proses-pemulihan-aset</t>
+          <t>https://finance.detik.com/moneter/d-8604532/warga-ri-doyan-pakai-paylater-ini-buktinya</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/kepala-bpa-kejaksaan-ri-patris-yusrian-jaya-1785852815388_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/10/27/ilustrasi-paylater_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2187,33 +2187,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PSSI Cuan Rp 722 Miliar, Tetap Terbuka Bantuan dari Pemerintah</t>
+          <t>Izin Tambang Berakhir 2041, Freeport Ajukan Perpanjangan ke Pemerintah</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:30:30 +0700</t>
+          <t>Tue, 04 Aug 2026 20:42:26 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSSI sukses mengumpulkan pendapatan fantastis Rp722 miliar. Angka tersebut sudah cukup buat PSSI, tetapi tetap terbuka jika ada tawaran bantuan pemerintah.</t>
+          <t>Freeport Indonesia telah mengajukan permohonan perpanjangan IUPK untuk melanjutkan operasi tambang Grasberg setelah izin yang berlaku saat ini berakhir 2041.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604319/pssi-cuan-rp-722-miliar-tetap-terbuka-bantuan-dari-pemerintah</t>
+          <t>https://finance.detik.com/energi/d-8604497/izin-tambang-berakhir-2041-freeport-ajukan-perpanjangan-ke-pemerintah</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menpora-erick-thohir-1783676745865.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/11/mengintip-tambang-sedalam-17-km-di-perut-bumi-papua-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2225,33 +2225,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Indonesia Punya 2 Srikandi di Asia Cross Country Rally 2026</t>
+          <t>Mendes: Kopdes Merah Putih Penggerak Ekonomi Desa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:25:00 +0700</t>
+          <t>Tue, 04 Aug 2026 20:19:08 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Asia Cross Country Rally 2026 rupanya menarik minat para pereli wanita Indonesia. Mereka adalah Lody Natasha dan Satsy Laksamana.</t>
+          <t>Pemerintah menargetkan pembangunan 30.000 Koperasi Desa/Kelurahan Merah Putih (KDKMP) pada tahun ini.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604616/indonesia-punya-2-srikandi-di-asia-cross-country-rally-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604472/mendes-kopdes-merah-putih-penggerak-ekonomi-desa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/lody-natasha-dan-satsy-laksamana-1785860860805_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menteri-desa-dan-pembangunan-daerah-tertinggal-pdt-1785853253837_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2263,33 +2263,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
+          <t>Bursa Mineral Meluncur 1 Januari 2027, Ini Bocoran dari OJK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:00:00 +0700</t>
+          <t>Tue, 04 Aug 2026 20:00:15 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Final Piala Presiden 2026 akhirnya mendapatkan kontestannya. Persib Bandung vs Persebaya Surabaya akan tersaji di partai puncak.</t>
+          <t>OJK buka-bukaan soal Bursa Mineral bakal meluncur 1 Januari 2027.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604606/final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
+          <t>https://finance.detik.com/energi/d-8604418/bursa-mineral-meluncur-1-januari-2027-ini-bocoran-dari-ojk</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492015_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/18/friderica-widyasari-dewi-1781765532562_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2301,33 +2301,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Piala AFF: Indonesia Dijagokan Taklukkan Singapura, Lolos ke Semifinal</t>
+          <t>Bea Cukai Amankan 3 Warga Negara Malaysia Bawa Narkotika</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:40:30 +0700</t>
+          <t>Tue, 04 Aug 2026 19:51:37 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Timnas Indonesia akan dijamu Timnas Singapura dalam laga penentuan tiket ke semifinal Piala AFF 2026. Garuda dijagokan mengalahkan The Lions.</t>
+          <t>Petugas Bea Cukai Bandara Soekarno-Hatta mengamankan ketamin dari 3 wanita penumpang pesawat diduga Warga Negara Malaysia.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604294/piala-aff-indonesia-dijagokan-taklukkan-singapura-lolos-ke-semifinal</t>
+          <t>https://finance.detik.com/ekonomi-bisnis/d-8604433/bea-cukai-amankan-3-warga-negara-malaysia-bawa-narkotika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/08/07/ed32a201-0b77-4c2b-a370-0636977c2075_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2339,33 +2339,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cara Memen Agar Mobilnya Siap Taklukkan Medan Berat AXCR 2026</t>
+          <t>Industri Kripto RI Terus Melonjak, Transaksinya Rp 28 T per Juni 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:25:00 +0700</t>
+          <t>Tue, 04 Aug 2026 19:30:08 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Memen Harianto akan membawa nama Indonesia di Asia Cross Country Rally (AXCR) 2026. Dia melakukan persiapan secara maksimal, terutama untuk mobilnya.</t>
+          <t>Aset kripto terus diminati di Indonesia, dengan 22,69 juta akun dan transaksi mencapai Rp 28,58 triliun pada Juni 2026. OJK tetap awasi perlindungan konsumen.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604594/cara-memen-agar-mobilnya-siap-taklukkan-medan-berat-axcr-2026</t>
+          <t>https://finance.detik.com/fintech/d-8604314/industri-kripto-ri-terus-melonjak-transaksinya-rp-28-t-per-juni-2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/memen-harianto-1785860948781_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/05/27/ilustrasi-bitcoin_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2377,33 +2377,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Persebaya Vs Arema: Bajul Ijo Menang 1-0, Lolos ke Final Piala Presiden</t>
+          <t>Sektor Jasa Keuangan Tetap Stabil, Kredit Perbankan Tumbuh 12,67%</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:17:39 +0700</t>
+          <t>Tue, 04 Aug 2026 19:19:21 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya meraih kemenangan 1-0 atas Arema FC di semifinal Piala Presiden 2026. Persebaya lolos ke final untuk menghadapi Persib Bandung.</t>
+          <t>OJK menyatakan sektor jasa keuangan tetap stabil di tengah ketidakpastian global. Pertumbuhan kredit dan permodalan perbankan menunjukkan kinerja positif.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604584/persebaya-vs-arema-bajul-ijo-menang-1-0-lolos-ke-final-piala-presiden</t>
+          <t>https://finance.detik.com/moneter/d-8604398/sektor-jasa-keuangan-tetap-stabil-kredit-perbankan-tumbuh-12-67</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ojk-1785845945964_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2415,33 +2415,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hasil Piala AFF 2026: Thailand Atasi Filipina 1-0</t>
+          <t>OJK Catat Total Aset Industri Asuransi RI Capai Rp Rp 1.184 triliun</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:58:26 +0700</t>
+          <t>Tue, 04 Aug 2026 19:07:39 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Thailand melanjutkan start positifnya di Piala AFF 2026. Tim War Elephants menang tipis 1-0 atas Filipina dan menguasai pucuk klasemen Grup B.</t>
+          <t>OJK melaporkan total aset industri asuransi RI mencapai Rp 1.184 triliun per Juni 2026, dengan pertumbuhan stabil meski beberapa sektor mengalami kontraksi.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604566/hasil-piala-aff-2026-thailand-atasi-filipina-1-0</t>
+          <t>https://finance.detik.com/moneter/d-8604257/ojk-catat-total-aset-industri-asuransi-ri-capai-rp-rp-1-184-triliun</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/14/ilustrasi-asuransi-kesehatan-1778737684617_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2453,33 +2453,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vicario dan Suzuki Diincar Juventus, Buffon Bilang Begini!</t>
+          <t>Kredit Perbankan Tembus Rp 9.081 Triliun, Tumbuh 12,67%</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:45:05 +0700</t>
+          <t>Tue, 04 Aug 2026 18:30:05 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Juventus dikabarkan menjadikan Guglielmo Vicario dan Zion Suzuki sebagai kandidat kiper anyar. Bagaimana menurut Gianluigi Buffon?</t>
+          <t>Kredit perbankan pada bulan Juni 2026 tumbuh 12,67% menjadi Rp 9.081 triliun.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604289/vicario-dan-suzuki-diincar-juventus-buffon-bilang-begini</t>
+          <t>https://finance.detik.com/moneter/d-8604271/kredit-perbankan-tembus-rp-9-081-triliun-tumbuh-12-67</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/04/gianluigi-buffon_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/02/10/uang-tunai-rupiah-4_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2491,33 +2491,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pelajaran dari Singapura Sukses Antar Vietnam Cukur Indonesia</t>
+          <t>Utang Pinjol Warga RI Tembus Rp 105 Triliun!</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:30:15 +0700</t>
+          <t>Tue, 04 Aug 2026 18:25:04 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vietnam banyak belajar dari hasil imbang melawan Singapura. Pemilihan strategi yang tepat sukses antar Vietnam mencukur Timnas Indonesia 3-0.</t>
+          <t>OJK mencatat nilai pembiayaan pinjol mencapai Rp 105,14 triliun, atau tumbuh 25,88% secara tahunan pada bulan Juni 2026.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604285/pelajaran-dari-singapura-sukses-antar-vietnam-cukur-indonesia</t>
+          <t>https://finance.detik.com/moneter/d-8604291/utang-pinjol-warga-ri-tembus-rp-105-triliun</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/02/04/b3a5ed4c-3141-4fed-a3ff-2bfc948f1b01_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2529,33 +2529,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PBSI Cari Pasangan untuk Adnan Maulana</t>
+          <t>BRILink Agen Permudah Perajin &amp;amp; Petani Alor Akses Layanan Perbankan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:20:37 +0700</t>
+          <t>Tue, 04 Aug 2026 18:13:26 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PP PBSI masih mencari pasangan untuk Adnan Maulana. Itu setelah rekan tandemnya yang lama, Indah Cahya Sari Jamil, dipasangkan dengan pemain lain.</t>
+          <t>Kepulauan Alor, NTT, menawarkan keindahan dan tantangan. Kehadiran BRILink Agen mempermudah akses keuangan, mendukung kemandirian ekonomi masyarakat setempat.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8604509/pbsi-cari-pasangan-untuk-adnan-maulana</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604269/brilink-agen-permudah-perajin-petani-alor-akses-layanan-perbankan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/02/adnan-maulanaindah-cahya-sari-jamil-1780382604246_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/12/05/4acc195a-ed44-44c8-88b3-7f629b73d63b_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2567,33 +2567,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Matthijs de Ligt Belum Bisa Gabung ke MU</t>
+          <t>36 Ribu Rekening Judi Online Diblokir!</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:15:40 +0700</t>
+          <t>Tue, 04 Aug 2026 18:00:20 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Manchester United masih belum bisa diperkuat bek tengahnya, Matthijs de Ligt. Dirinya masih belum pulih setelah operasi cedera punggung.</t>
+          <t>Otoritas Jasa Keuangan (OJK) sebut 36.735 rekening terkait judi online diblokir.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603854/matthijs-de-ligt-belum-bisa-gabung-ke-mu</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604245/36-ribu-rekening-judi-online-diblokir</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/07/matthijs-de-ligt-1775546584882.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/27/ilustrasi-judi-online-1_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2605,33 +2605,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jelang Lawan Singapura, Timnas Indonesia Butuh Pemulihan Moral</t>
+          <t>WIKA Sukses Catatkan Kontrak Baru Rp 6,91 Triliun hingga Juni 2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 17:45:19 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Timnas Indonesia sangat terpukul usai kalah 0-3 dari Vietnam. Skuad Garuda kini harus memulihkan moral jelang melawan Singapura.</t>
+          <t>WIKA raih kontrak baru Rp 6,91 triliun hingga Juni 2026, didorong proyek strategis di konstruksi dan infrastruktur. Optimis dukung pembangunan nasional.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604284/jelang-lawan-singapura-timnas-indonesia-butuh-pemulihan-moral</t>
+          <t>https://finance.detik.com/infrastruktur/d-8604234/wika-sukses-catatkan-kontrak-baru-rp-6-91-triliun-hingga-juni-2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/wika-sukses-catatkan-kontrak-baru-rp-691-triliun-hingga-juni-2026-1785840143413_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2643,33 +2643,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jorge Martin Tak Sabar Lanjutkan Duel Sengit Perebutan Gelar MotoGP 2026!</t>
+          <t>Gagal Dapat Diskon Moge Harley Davidson, Purbaya: Yah, Lemes Gue!</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:50:40 +0700</t>
+          <t>Tue, 04 Aug 2026 17:38:14 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jorge Martin antusias menatap paruh kedua MotoGP 2026. Ia yakin persaingan gelar juara dunia akan semakin sengit karena lima pebalap hanya terpaut 24 poin.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa bercerita dirinya gagal membeli motor Harley Davidson dengan harga diskon karena dianggap gratifikasi.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604324/jorge-martin-tak-sabar-lanjutkan-duel-sengit-perebutan-gelar-motogp-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604225/gagal-dapat-diskon-moge-harley-davidson-purbaya-yah-lemes-gue</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/moto-motogp-ned-1782675298213_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/menkeu-purbaya-jajal-moge-harley-davidson-1785839816386_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2681,33 +2681,33 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mulai Tahun Depan Piala Presiden untuk Timnas Indonesia, Tidak Lagi Klub</t>
+          <t>Bos OJK Blak-blakan Kondisi Sektor Keuangan RI di Tengah Gejolak Global</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:45:15 +0700</t>
+          <t>Tue, 04 Aug 2026 17:16:02 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ketum PSSI Erick Thohir mengungkapkan Piala Presiden mulai tahun depan tidak lagi menjadi turnamen pramusim klub, melainkan jadi agenda Timnas Indonesia.</t>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi buka-bukaan kondisi sektor keuangan di tengah gonjang-ganjing global.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604194/mulai-tahun-depan-piala-presiden-untuk-timnas-indonesia-tidak-lagi-klub</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604173/bos-ojk-blak-blakan-kondisi-sektor-keuangan-ri-di-tengah-gejolak-global</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/frederica-widyasari-dewi-1785765447950_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2719,33 +2719,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kovacic: Anderson Bikin Lini Tengah Man City Lebih Bertenaga</t>
+          <t>Prabowo Minta Harga BBM Subsidi Tak Naik</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:30:50 +0700</t>
+          <t>Tue, 04 Aug 2026 17:11:28 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mateo Kovacic antusias dengan Elliott Anderson, meski itu juga berarti persaingan lini tengah Manchester City kian ketat. Ia yakin tim makin kuat.</t>
+          <t>Menteri ESDM Bahlil mengungkapkan kebijakan harga BBM bersubsidi tetap dipertahankan meski harga minyak dunia naik.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604197/kovacic-anderson-bikin-lini-tengah-man-city-lebih-bertenaga</t>
+          <t>https://finance.detik.com/energi/d-8604168/prabowo-minta-harga-bbm-subsidi-tak-naik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/29/elliott-anderson-1764354213557_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/01/presiden-prabowo-subianto-dok-youtube-setpres-1782871893408_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2757,33 +2757,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Usai Indonesia Dihajar Vietnam, Hubner Saling Sindir dengan Do Hoang Hen</t>
+          <t>OJK Kasih Denda Rp 91 Miliar ke 104 Pelaku Pasar Modal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:15:00 +0700</t>
+          <t>Tue, 04 Aug 2026 17:03:56 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dihajar Timnas Vietnam dalam laga lanjutan Piala AFF 2026. Justin Hubner saling sindir dengan pemain Golden Star Warriors, Do Hoang Hen.</t>
+          <t>OJK menjatuhkan denda Rp 91 miliar kepada 104 pelaku pasar modal untuk penegakan ketentuan dan perlindungan konsumen. Sanksi administratif juga diterapkan.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604196/usai-indonesia-dihajar-vietnam-hubner-saling-sindir-dengan-do-hoang-hen</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604151/ojk-kasih-denda-rp-91-miliar-ke-104-pelaku-pasar-modal</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513456_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/12/30/59e6cb2c-4043-4878-a12b-89f4ab9e5a8e_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2795,33 +2795,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Buffon Percaya sama Mancini, Semoga Italia Lolos ke Piala Dunia</t>
+          <t>Pelatihan Tata Rias Bekali Siswa Berkebutuhan Khusus Menuju Dunia Kerja</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:00:40 +0700</t>
+          <t>Tue, 04 Aug 2026 17:00:33 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sepakbola Italia bergejolak belakangan ini dalam penunjukan pelatih baru. Buffon mau drama itu berakhir, percayakan ke juru taktik baru Roberto Mancini.</t>
+          <t>Pelatihan tata rias menjadi salah satu upaya memperluas kesempatan kerja bagi siswa berkebutuhan khusus. Peserta belajar keterampilan yang bernilai ekonomi.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604208/buffon-percaya-sama-mancini-semoga-italia-lolos-ke-piala-dunia</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603579/pelatihan-tata-rias-bekali-siswa-berkebutuhan-khusus-menuju-dunia-kerja</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/03/gianluigi-buffon-1748885612603.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pelatihan-tata-rias-bekali-siswa-disabilitas-menuju-dunia-kerja-1785821111786_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2833,33 +2833,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Marco Bezzecchi Belum 100%, tapi Siap Comeback di MotoGP Inggris 2026!</t>
+          <t>Penjualan Mobil RI Kalah dari Malaysia, Purbaya Ungkap Biang Keroknya</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:50:50 +0700</t>
+          <t>Tue, 04 Aug 2026 16:40:03 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Marco Bezzecchi siap kembali balapan di MotoGP Inggris 2026 meski mengaku belum pulih 100 persen usai menjalani operasi tulang selangka dan lutut.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa buka-bukaan soal biang kerok penjualan kendaraan alami pelemahan.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604281/marco-bezzecchi-belum-100-tapi-siap-comeback-di-motogp-inggris-2026</t>
+          <t>https://finance.detik.com/industri/d-8604080/penjualan-mobil-ri-kalah-dari-malaysia-purbaya-ungkap-biang-keroknya</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/15/motor-motogp-germany-1784050516185_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/giias-2026-dipadati-pengunjung-deretan-mobil-baru-dan-ev-jadi-magnet-utama-1785427971780_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2871,33 +2871,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vietnam 'Oper' Tekanan ke Indonesia</t>
+          <t>Insiden KM Mutiara Sentosa II, Sistem Keselamatan Kapal Diminta Dievaluasi</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:40:30 +0700</t>
+          <t>Tue, 04 Aug 2026 16:38:27 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vietnam datang dengan tekanan dan kini melemparnya ke Indonesia. Mampukah skuad Garuda merespons tekanan itu dan keluar dari posisi terjepit.</t>
+          <t>Anggota DPR Sudjatmiko menyampaikan duka cita atas kebakaran KM Mutiara Sentosa II. Ia mendesak evaluasi keselamatan pelayaran untuk mencegah tragedi serupa.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604184/vietnam-oper-tekanan-ke-indonesia</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604495/insiden-km-mutiara-sentosa-ii-sistem-keselamatan-kapal-diminta-dievaluasi</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2909,33 +2909,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Liverpool Enggan Jual Gakpo, tapi Kalau Tottenham Kasih Harga Bagus...</t>
+          <t>Prabowo Perintahkan Bahlil Bereskan Listrik Padam di Kalimantan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:20:45 +0700</t>
+          <t>Tue, 04 Aug 2026 16:36:06 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur meminati Cody Gakpo dari Liverpool. The Reds mau mempertahankan sang winger, tapi bakal goyah kalau dikasih harga bagus.</t>
+          <t>Presiden Prabowo minta pemadaman listrik di Kalimantan segera teratasi. Menteri ESDM Bahlil akan koordinasi dengan PLN untuk pemulihan cepat.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604186/liverpool-enggan-jual-gakpo-tapi-kalau-tottenham-kasih-harga-bagus</t>
+          <t>https://finance.detik.com/energi/d-8604071/prabowo-perintahkan-bahlil-bereskan-listrik-padam-di-kalimantan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/05/cody-gakpo-1754352181260.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/20/prabowo-bahlil-1760968180889_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2947,33 +2947,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Detak Jantung Marc Marquez Bisa Ungkap Kans Juara MotoGP 2026</t>
+          <t>Insiden Kapal Berulang Jadi Momentum Evaluasi Keselamatan Pelayaran</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:10:20 +0700</t>
+          <t>Tue, 04 Aug 2026 16:26:53 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Detak jantung Marc Marquez saat MotoGP Inggris diyakini bisa menjadi indikator keberhasilan pemulihan fisiknya terkait kans mengejar gelar dunia MotoGP 2026.</t>
+          <t>Deretan insiden kapal di Tanah Air menjadi pendorong untuk evaluasi sistem pengawasan keselamatan pelayaran.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8604170/detak-jantung-marc-marquez-bisa-ungkap-kans-juara-motogp-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604051/insiden-kapal-berulang-jadi-momentum-evaluasi-keselamatan-pelayaran</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-1783860046236_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535416_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2985,33 +2985,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>John Herdman: Indonesia Asyik di Depan, Jadi Lupa Pertahanan</t>
+          <t>Trump Digugat Massal Gegara Tarif Impor, Indonesia Ikut Terseret</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:00:50 +0700</t>
+          <t>Tue, 04 Aug 2026 16:19:10 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pelatih Timnas Indonesia John Herdman menyebut timnya terlalu asyik main di depan saat jumpa Vietnam. Hasilnya timnya malah kecolongan di lini pertahanan.</t>
+          <t>Sebanyak 25 negara bagian AS menggugat Trump atas tarif impor baru. Mereka menilai tarif tersebut ilegal dan meminta pengembalian bea masuk yang dibayarkan.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604183/john-herdman-indonesia-asyik-di-depan-jadi-lupa-pertahanan</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8604002/trump-digugat-massal-gegara-tarif-impor-indonesia-ikut-terseret</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/27/gaya-nyentrik-john-herdman-kawal-timnas-garuda-1774628369095.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3023,33 +3023,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Singapura Vs Indonesia: Ulangan Situasi di Manila Sedekade Lalu</t>
+          <t>WFH ASN Sehari dalam Sepekan Diperpanjang</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:40:45 +0700</t>
+          <t>Tue, 04 Aug 2026 16:15:06 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Indonesia menjalani laga hidup dan mati melawan Singapura di Piala AFF 2026. Laga ini menjadi ulangan persaingan Garuda melawan The Lions sedekade lalu.</t>
+          <t>Pemerintah memperpanjang kebijakan Work from Home (WFH) bagi Aparatur Sipil Negara (ASN) sehari dalam sepekan.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603914/singapura-vs-indonesia-ulangan-situasi-di-manila-sedekade-lalu</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603998/wfh-asn-sehari-dalam-sepekan-diperpanjang</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/11/26/54e9d3f7-5e6d-46d8-b5d2-e2d0149535a8_169.jpg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/07/11/27d3660c-abb0-424e-8871-e739c2b6cc4d_169.jpg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3061,33 +3061,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Malut United Resmi Ganti Nama Jadi Java United, Pindah Markas ke Semarang</t>
+          <t>IHSG Ditutup Menguat ke Level 6.391</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:30:00 +0700</t>
+          <t>Tue, 04 Aug 2026 16:13:12 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Malut United resmi berganti nama menjadi Java United dan memindahkan markas dari Ternate ke Semarang.</t>
+          <t>IHSG ditutup menguat di level 6.319,6, naik 1,37%. Volume transaksi mencapai 33.150 miliar saham. Kinerja mingguan dan bulanan juga positif.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604279/malut-united-resmi-ganti-nama-jadi-java-united-pindah-markas-ke-semarang</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8604014/ihsg-ditutup-menguat-ke-level-6-391</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/java-united-1785770401869_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/04/ihsg-terpuruk-kekhawatiran-pasar-meningkat-1780558039793_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3099,33 +3099,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chelsea Mulai Bersih-bersih</t>
+          <t>Kuba Gelap Gulita Lagi, Krisis Listrik Makin Parah</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:20:15 +0700</t>
+          <t>Tue, 04 Aug 2026 16:09:09 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chelsea punya 40 pemain di dalam skuadnya. Bursa transfer musim panas 2026 masih buka sampai 1 September, Si Biru kini saatnya bersih-bersih.</t>
+          <t>Krisis listrik Kuba semakin parah dengan pemadaman berulang. Sanksi AS dan infrastruktur tua jadi penyebab utama, mempengaruhi jutaan warga.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603920/chelsea-mulai-bersih-bersih</t>
+          <t>https://finance.detik.com/energi/d-8603992/kuba-gelap-gulita-lagi-krisis-listrik-makin-parah</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/09/chelsea-1778261458229.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/situasi-di-havana-ibu-kota-kuba-saat-diselimuti-kegelapan-buntut-lumpuhnya-jaringan-listrik-negara-tersebut-1785751638653_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3137,33 +3137,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RI Bawa Pulang 15 Medali dari Kejuaraan Asia MMA, Kini Fokus Asian Games 2026</t>
+          <t>Suntik Dana Rp 400 T ke Perbankan, Purbaya: Kalau Kurang, Saya Tambah!</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:10:25 +0700</t>
+          <t>Tue, 04 Aug 2026 16:01:28 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tim MMA Indonesia meraih 15 medali, termasuk lima emas, di GAMMA Asian Championships 2026.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa bicara soal suntikan dana SAL ke perbankan Rp 400 triliun.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8604192/ri-bawa-pulang-15-medali-dari-kejuaraan-asia-mma-kini-fokus-asian-games-2026</t>
+          <t>https://finance.detik.com/moneter/d-8603978/suntik-dana-rp-400-t-ke-perbankan-purbaya-kalau-kurang-saya-tambah</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gamma-asian-championships-2026-1785838947680_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/05/tawa-purbaya-pastikan-ekonomi-hingga-mei-2026-masih-solid-1780655487362_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3175,33 +3175,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Erick Thohir: Saya Tetap Percaya pada John Herdman</t>
+          <t>BPS Catat Deflasi Bulanan, Harga Komoditas Pangan Jadi Penentu</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 16:00:57 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Timnas Indonesia kalah 0-3 dari Vietnam, kans ke semifinal Piala AFF 2026 terancam. Ketum PSSI Erick Thohir membela pelatih John Herdman.</t>
+          <t>BPS mencatat deflasi bulanan sebesar 0,14 persen pada Juli 2026. Penurunan harga sejumlah bahan pangan menjadi faktor utama yang menekan Indeks Harga Konsumen.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603911/erick-thohir-saya-tetap-percaya-pada-john-herdman</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603527/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/13/selamat-datang-john-herdman-pelatih-baru-timnas-indonesia-1768277980430.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bps-catat-deflasi-bulanan-harga-komoditas-pangan-jadi-penentu-1785819465759_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3213,33 +3213,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dirumorkan Kembali ke Italia, Kovacic: Man City Masih Mengandalkanku</t>
+          <t>66 Ribu UMKM Jalani Pembinaan, Fokus Bangun Nilai Jual Lewat Storytelling</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:45:40 +0700</t>
+          <t>Tue, 04 Aug 2026 15:58:17 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mateo Kovacic dirumorkan kembali ke Italia, dengan kabar Juventus dan Inter Milan meminati. Tapi gelandang senior itu bilang masih diandalkan Manchester City.</t>
+          <t>Pertamina Patra Niaga membina 66 ribu UMKM dengan fokus pada storytelling untuk meningkatkan nilai jual produk. Strategi ini dorong daya saing di pasar.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603894/dirumorkan-kembali-ke-italia-kovacic-man-city-masih-mengandalkanku</t>
+          <t>https://finance.detik.com/solusiukm/d-8604055/66-ribu-umkm-jalani-pembinaan-fokus-bangun-nilai-jual-lewat-storytelling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/20/wolverhampton-wanderers-manchester-city_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/30/ilustrasi-umkm-makanan-1748571534080_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3251,33 +3251,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Persib Vs Persija: Menang 2-1, Maung Bandung ke Final Piala Presiden 2026</t>
+          <t>Pegadaian Raih Penghargaan Khusus di Ajang IDX Channel Anugerah ESG 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:31:55 +0700</t>
+          <t>Tue, 04 Aug 2026 15:55:52 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Persib Bandung mengalahkan Persija Jakarta di semifinal Piala Presiden 2026. Pasukan Igor Tolic pun melaju ke final.</t>
+          <t>Pegadaian raih penghargaan IDX Channel Anugerah ESG 2026 untuk inovasi keuangan inklusif.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604212/persib-vs-persija-menang-2-1-maung-bandung-ke-final-piala-presiden-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603968/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pegadaian-raih-penghargaan-khusus-di-ajang-idx-channel-anugerah-esg-2026-1785833724891_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3289,33 +3289,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bagas Maulana Dinilai Cocok ke Ganda Campuran, Ini Alasannya</t>
+          <t>Pendapatan Chandra Asri Naik 83%, tapi Laba Malah Anjlok 77% Jadi Rp 6,6 T</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:20:10 +0700</t>
+          <t>Tue, 04 Aug 2026 15:48:29 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pelatih ganda putra Antonius Budi Ariantho menjelaskan alasan Bagas Maulana dipindahkan ke sektor ganda campuran.</t>
+          <t>PT Chandra Asri Pacific Tbk (TPIA) membukukan penurunan laba bersih seiring tumbuhnya pendapatan sepanjang semester I-2026.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8604165/bagas-maulana-dinilai-cocok-ke-ganda-campuran-ini-alasannya</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603945/pendapatan-chandra-asri-naik-83-tapi-laba-malah-anjlok-77-jadi-rp-6-6-t</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/12/bagas-maulana-1_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/31/chandra-asri_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3327,33 +3327,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vietnam Tahu Caranya Keluar dari Tekanan</t>
+          <t>Rayuan Maut Purbaya ke Raksasa Otomotif Jepang</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:15:15 +0700</t>
+          <t>Tue, 04 Aug 2026 15:21:30 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vietnam datang ke Indonesia dengan tekanan besar usai ditahan Singapura. The Golden Star Warriors merespons dengan cemerlang.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa memberikan rayuan maut agar raksasa otomotif Jepang, Toyota, pindahkan pabriknya ke Indonesia.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603861/vietnam-tahu-caranya-keluar-dari-tekanan</t>
+          <t>https://finance.detik.com/industri/d-8603875/rayuan-maut-purbaya-ke-raksasa-otomotif-jepang</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/menteri-keuangan-purbaya-yudhi-sadewa-1758533359856_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3365,33 +3365,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dear Liverpool, Ini Isak yang Baru</t>
+          <t>Moody's-Fitch Kasih Nilai Negatif ke Ekonomi RI, Purbaya: Mereka Offside!</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:00:25 +0700</t>
+          <t>Tue, 04 Aug 2026 14:43:15 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alexander Isak mengaku sudah pulih 100 persen. Sang striker siap berikan yang terbaik buat Liverpool di musim baru!</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa menyebut lembaga rating Moody's dan Fitch salah ukur ekonomi Indonesia.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603859/dear-liverpool-ini-isak-yang-baru</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603805/moodys-fitch-kasih-nilai-negatif-ke-ekonomi-ri-purbaya-mereka-offside</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/alexander-isak-1778251850354.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/purbaya-garuk-kepala-apbn-april-2026-defisit-rp1644-triliun-1779201435955_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3403,33 +3403,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timnas Indonesia Masih Berani Main High Pressing, John?</t>
+          <t>Industri Alas Kaki Indonesia Bertahan di Tengah Tarif Impor AS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:40:40 +0700</t>
+          <t>Tue, 04 Aug 2026 14:00:10 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Timnas Indonesia sangat buruk dalam transisi bertahan dengan permainan high pressing. Pelatih John Herdman apakah akan mengubah cara bermain Garuda?</t>
+          <t>Industri alas kaki Indonesia tetap menjaga optimisme di tengah kebijakan tarif impor Amerika Serikat. Pelaku usaha menilai daya saing produk masih terjaga.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603770/timnas-indonesia-masih-berani-main-high-pressing-john</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603497/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/industri-alas-kaki-indonesia-bertahan-di-tengah-tarif-impor-as-1785818219683_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3441,33 +3441,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Piala AFF: Indonesia Pernah Lima Kali Gagal ke Semifinal</t>
+          <t>Apa Kabar Proyek Trans Papua 50 Km? Begini Progresnya</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:20:15 +0700</t>
+          <t>Tue, 04 Aug 2026 13:58:11 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Timnas Indonesia sedang di ujung tanduk di Piala AFF 2026. Sepanjang sejarah pesta sepakbola ASEAN, Skuad Garuda pernah lima kali gagal ke semifinal.</t>
+          <t>Kementerian Pekerjaan Umum (PU) mengungkapkan progres pembangunan Jalan Trans Papua.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603776/piala-aff-indonesia-pernah-lima-kali-gagal-ke-semifinal</t>
+          <t>https://finance.detik.com/infrastruktur/d-8603725/apa-kabar-proyek-trans-papua-50-km-begini-progresnya</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pembangunan-trans-papua-1785826507044_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3479,33 +3479,33 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Welbeck Kemarin Hobi Jebol Chelsea, Kini Jagoan Baru The Blues</t>
+          <t>Kapan Prabowo Luncurkan Insentif Kendaraan Listrik?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:00:15 +0700</t>
+          <t>Tue, 04 Aug 2026 13:35:04 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chelsea resmi mendatangkan Danny Welbeck. Sang striker veteran lumayan hobi jebol gawang The Blues dulu, tapi kini diharapkan jadi jagoan.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa bilang dalam beberapa pekan ke depan insentif kendaraan listrik akan diluncurkan Presiden Prabowo Subianto.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8603780/welbeck-kemarin-hobi-jebol-chelsea-kini-jagoan-baru-the-blues</t>
+          <t>https://finance.detik.com/industri/d-8603674/kapan-prabowo-luncurkan-insentif-kendaraan-listrik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/danny-welbeckchelseabursa-transfer-chelsea-1785602779561.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/06/tekan-biaya-transportasi-motor-listrik-jadi-andalan-baru-masyarakat-1775465692322_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3517,33 +3517,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ini Sebab PBSI Belum Rilis Daftar Pemain di Asian Games</t>
+          <t>Proyek PLTS 100 GW Segera Dimulai, Bali Jadi Lokasi Pertama</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:50:00 +0700</t>
+          <t>Tue, 04 Aug 2026 13:26:52 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nama-nama pebulutangkis Indonesia yang akan diturunkan di Asian Games 2026 belum final. PBSI masih akan melihat hasil dari Kejuaraan Dunia pada 17-23 Agustus.</t>
+          <t>Menteri ESDM Bahlil Lahadalia umumkan pembangunan PLTS 100 GW bertahap, dimulai di Bali. Proyek ini ditargetkan rampung dengan perencanaan matang.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8603931/ini-sebab-pbsi-belum-rilis-daftar-pemain-di-asian-games</t>
+          <t>https://finance.detik.com/energi/d-8603661/proyek-plts-100-gw-segera-dimulai-bali-jadi-lokasi-pertama</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/26/logo-pbsi.webp?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/22/menteri-esdm-bahlil-lahadalia-eva-sdetikcom-1782133701407_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3555,33 +3555,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>John Herdman ke Suporter: Kita Menang Bersama, Kalah Juga Bersama</t>
+          <t>Ketemu World Bank-IMF, Purbaya: I'm the Most Unlucky Minister in the World</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:40:25 +0700</t>
+          <t>Tue, 04 Aug 2026 13:10:09 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dihajar Timnas Vietnam saat menjalani laga kandang di Piala AFF 2026. John Herdman berjanji Skuad Garuda akan bangkit.</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa curhat dirinya menjadi menteri paling kurang beruntung di dunia.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603741/john-herdman-ke-suporter-kita-menang-bersama-kalah-juga-bersama</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603641/ketemu-world-bank-imf-purbaya-im-the-most-unlucky-minister-in-the-world</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/31/herdman-janji-bangkit-usai-kekalahan-targetkan-indonesia-ke-piala-dunia-2030-1774891836257_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186786140_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3593,33 +3593,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Awas MU, Bayern Munich Minati Benjamin Sesko</t>
+          <t>Peternakan dan Pertanian Terpadu di Sleman Perkuat Sistem Pangan Berkelanjutan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:20:10 +0700</t>
+          <t>Tue, 04 Aug 2026 13:00:10 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bayern Munich menaruh minat pada striker Man United, Benjamin Sesko. Tapi Bayern enggak mau buru-buru merekrutnya dulu, mungkin beberapa tahun mendatang nanti.</t>
+          <t>Konsep integrated farming di Sleman menghubungkan peternakan, pertanian, dan pengolahan limbah. Sistem ini mendukung produksi lebih efisien dan berkelanjutan.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603737/awas-mu-bayern-munich-minati-benjamin-sesko</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8603467/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/02/benjamin-sesko-1772389311489.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/peternakan-dan-pertanian-terpadu-di-sleman-perkuat-sistem-pangan-berkelanjutan-1785816225367_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3631,33 +3631,33 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Viet Anh Berdarah-Darah untuk Tuntaskan Dendam ke Indonesia</t>
+          <t>Cara Scan QRIS Cross Border di Luar Negeri</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:00:45 +0700</t>
+          <t>Tue, 04 Aug 2026 12:57:38 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vietnam sukses membabat Indonesia 3-0 dalam laga Grup A Piala AFF 2026. Bek Bui Hoang Viet Anh sangat puas Golden Star Warriors berhasil balas dendam.</t>
+          <t>DANA mendukung transaksi QRIS Cross Border di luar negeri, memudahkan pengguna berbelanja di Thailand, Malaysia, Jepang, dan negara lainnya tanpa uang tunai.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603740/viet-anh-berdarah-darah-untuk-tuntaskan-dendam-ke-indonesia</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603628/cara-scan-qris-cross-border-di-luar-negeri</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ilustrasi-qris-1785823037090_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3669,33 +3669,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Asian Games 2026: Bulutangkis Beregu Putra Jadi Asa Indonesia Raih Emas</t>
+          <t>IHSG Tertahan di Level 6.200</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:51:15 +0700</t>
+          <t>Tue, 04 Aug 2026 12:41:11 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chef de Mission Indonesia Todotua Pasaribu berharap bulutangkis bisa mendapatkan medali emas di Asian Games 2026. Secara khusus nomor ganda putra.</t>
+          <t>HSG menguat 0,57% ke level 6.270,15 hingga penutupan perdagangan siang ini.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8603821/asian-games-2026-bulutangkis-beregu-putra-jadi-asa-indonesia-raih-emas</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603595/ihsg-tertahan-di-level-6-200</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/06/ilustrasi-bulutangkis.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/18/ihsg-anjlok-ke-zona-merah-bursa-saham-melemah-tajam-1779098741182_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3707,33 +3707,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bermain Buruk, Indonesia Dipecundangi Vietnam!</t>
+          <t>Magang Nasional Banjir Peminat, Pendaftar Tembus 732 Ribu!</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:44:50 +0700</t>
+          <t>Tue, 04 Aug 2026 12:36:26 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Apakah Indonesia bisa menjaga asa untuk tampil di semifinal Piala AFF 2026?</t>
+          <t>Peminat Magang Nasional mencapai 732 ribu, namun hanya 50 ribu yang diterima.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/sepakbola-indonesia/d-8603690/bermain-buruk-indonesia-dipecundangi-vietnam</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603589/magang-nasional-banjir-peminat-pendaftar-tembus-732-ribu</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detiksore-4-agustus-2026-1785825691822_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/program-magang-kerja-phr-batch-9-hadir-untuk-memberikan-pengalaman-profesional-pendampingan-dari-para-ahli-dan-kesempatan-berk-1781240776723_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3745,33 +3745,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Marselino Ferdinan Tak Bisa Main di Piala AFF 2026!</t>
+          <t>Gelombang PHK Makin Besar di Singapura, 4.500 Orang Jadi Korban</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:40:10 +0700</t>
+          <t>Tue, 04 Aug 2026 12:14:37 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kabar buruk menghampiri Timnas Indonesia di tengah gelaran Piala AFF 2026. Marselino Ferdinan tak bisa memperkuat Skuad Garuda!</t>
+          <t>Gelombang PHK di Singapura meningkat pada kuartal II-2026, mencapai 4.500 pekerja. Meski demikian, total lapangan kerja justru bertambah 10.700.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603636/marselino-ferdinan-tak-bisa-main-di-piala-aff-2026</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603555/gelombang-phk-makin-besar-di-singapura-4-500-orang-jadi-korban</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/12/marselino-ferdinan_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/10/27/ilustrasi-kena-phk_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3783,33 +3783,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Usai Permalukan Indonesia, Vietnam Dapat Bonus Rp1,37 Miliar</t>
+          <t>LPEI Kucurkan US$ 8,5 Juta Danai Ekspor Gerbong Barang ke Selandia Baru</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:20:10 +0700</t>
+          <t>Tue, 04 Aug 2026 12:11:18 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Timnas Vietnam mempermalukan Timnas Indonesia di Piala AFF 2026. Golden Star Warriors mendapat bonus 2 miliar dong atau setara Rp1,37 miliar.</t>
+          <t>LPEI dukung PT INKA ekspor 340 unit Wagon ke Selandia Baru dengan fasilitas USD 8,5 juta. Sinergi ini perkuat industri strategis dan perekonomian nasional.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603633/usai-permalukan-indonesia-vietnam-dapat-bonus-rp1-37-miliar</t>
+          <t>https://finance.detik.com/moneter/d-8603549/lpei-kucurkan-us-8-5-juta-danai-ekspor-gerbong-barang-ke-selandia-baru</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/eximbank-danai-ekspor-pt-inka-ke-selandia-baru-1785820259573_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3821,33 +3821,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Presiden FIFA Batal Naik Gaji 500 Persen</t>
+          <t>Alarm Berbunyi di Rusia, Bank-bank Mulai Krisis Uang Tunai!</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:00:15 +0700</t>
+          <t>Tue, 04 Aug 2026 12:03:30 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Presiden FIFA Gianni Infantino diketahui bakal naik gaji 525 persen andai wacana jual saham Piala Dunia sukses. Wacana itu batal, nggak gaji naik deh!</t>
+          <t>Bank-bank Rusia menghadapi tekanan likuiditas rubel, membatasi pembelian obligasi pemerintah. Defisit anggaran meningkat.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603662/presiden-fifa-batal-naik-gaji-500-persen</t>
+          <t>https://finance.detik.com/moneter/d-8603535/alarm-berbunyi-di-rusia-bank-bank-mulai-krisis-uang-tunai</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/16/gianni-infantino.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/03/01/ini-yang-bikin-warga-rusia-panik-serbu-atm-bank-buat-tarik-uang_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3859,33 +3859,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sebuah Perenungan Rizky Ridho</t>
+          <t>BSI dan Danantara Perkuat Ekosistem UMKM agar Pelaku Usaha Naik Kelas</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:40 +0700</t>
+          <t>Tue, 04 Aug 2026 11:51:53 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rizky Ridho mengakui kesalahannya dalam kekalahan Indonesia dari Vietnam. Dia akan mencoba merenungkannya untuk berbenah di laga selanjutnya.</t>
+          <t>PT Bank Syariah Indonesia (BSI) dan Danantara memperkuat UMKM melalui 35 Sentra dan 4 UMKM Center, mendukung pembiayaan, digitalisasi, dan sertifikasi halal.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603568/sebuah-perenungan-rizky-ridho</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603515/bsi-dan-danantara-perkuat-ekosistem-umkm-agar-pelaku-usaha-naik-kelas</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/direktur-utama-bsi-anggoro-eko-cahyo-1785820807840_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3897,33 +3897,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bagas Maulana ke Ganda Campuran, Tandem sama Indah Cahya</t>
+          <t>Tak Mau Kehilangan Guru Berkualitas, Singapura Naikkan Gaji hingga 9%</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:35:30 +0700</t>
+          <t>Tue, 04 Aug 2026 11:48:03 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PBSI kembali jajal kombinasi baru di sektor ganda campuran. Kali ini, Bagas Maulana dipasangkan dengan Indah Cahya Sari Jamil!</t>
+          <t>Pemerintah Singapura akan menaikkan gaji guru dan tenaga pendidik 2-9% mulai 1 Oktober 2026, untuk menarik dan mempertahankan tenaga pendidik berkualitas.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/raket/d-8603660/bagas-maulana-ke-ganda-campuran-tandem-sama-indah-cahya</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603511/tak-mau-kehilangan-guru-berkualitas-singapura-naikkan-gaji-hingga-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/22/fajarfikri-kalahkan-bagasleo-di-indonesia-masters-2026-1769070561744.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/21/pendidikan-nilai-1750494841214_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3935,33 +3935,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jika Arsenal Dapatkan Vinicius...</t>
+          <t>Trump Bantu Jepang Selamatkan Yen, Apa Untungnya buat AS?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:20:25 +0700</t>
+          <t>Tue, 04 Aug 2026 11:43:30 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Situasi Vinicius Jr di Madrid masih tanda tanya, rumor Arsenal mau merekrutnya juga terus mencuat. Wilshere bakal girang betul andai The Gunners mendapatkannya.</t>
+          <t>Presiden AS Donald Trump mengatakan, intervensi ini dilakukan atas permintaan pemerintah Jepang.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603570/jika-arsenal-dapatkan-vinicius</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603507/trump-bantu-jepang-selamatkan-yen-apa-untungnya-buat-as</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/02/vinicius-jr.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3973,33 +3973,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Indonesia Vs Vietnam: Sayap-sayap Lemah Garuda</t>
+          <t>Peresmian Pabrik Baterai EV di Karawang Tinggal Tunggu Jadwal Prabowo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 11:11:33 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibenamkan Timnas Vietnam di Piala AFF 2026. Sayap-sayap Garuda terlihat lemah di hadapan Golden Star Warriors.</t>
+          <t>Menteri ESDM Bahlil mengumumkan pabrik baterai listrik di Karawang siap diresmikan, tinggal menunggu jadwal Presiden. Investasi mencapai US$5,9 miliar.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603566/indonesia-vs-vietnam-sayap-sayap-lemah-garuda</t>
+          <t>https://finance.detik.com/energi/d-8603463/peresmian-pabrik-baterai-ev-di-karawang-tinggal-tunggu-jadwal-prabowo</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/menteri-esdm-bahlil-lahadalia-1784186781817_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4011,33 +4011,33 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Posisi di FIFA Terancam, Infantino Minta Dukungan Trump?</t>
+          <t>RI-Thailand Sepakat Genjot Perdagangan Tembus Rp 360 Triliun</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:40:25 +0700</t>
+          <t>Tue, 04 Aug 2026 11:02:03 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Posisi Gianni Infantino di FIFA terancam usai geger wacana jual saham Piala Dunia. Pria asal Swiss itu kabarnya meminta dukungan Presiden AS Donald Trump.</t>
+          <t>Indonesia dan Thailand sepakat menggenjot perdagangan dengan target Rp 360 triliun pada 2030.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603451/posisi-di-fifa-terancam-infantino-minta-dukungan-trump</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603447/ri-thailand-sepakat-genjot-perdagangan-tembus-rp-360-triliun</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/presiden-as-donald-trump-1783299814038_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/presiden-prabowo-subianto-menggelar-jamuan-santap-malam-resmi-untuk-pm-kerajaan-thailand-anutin-charnvirakul-foto-rusman-biro--1785806274579_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4049,33 +4049,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Balik Latihan di Madrid, Vinicius Segera Perpanjang Kontrak</t>
+          <t>Mengenang Burhanuddin 'Bur' Maras, Tokoh Migas dan Pendiri Lekom Maras</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:20:30 +0700</t>
+          <t>Tue, 04 Aug 2026 11:00:37 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vinicius Jr dilaporkan segera memperpanjang kontraknya setelah sudah kembali berlatih dengan Real Madrid. Ia memutuskan bertahan di El Real.</t>
+          <t>Burhanuddin 'Bur' Maras, pendiri PT Lekom Maras, wafat di usia 90 tahun. Ia dikenal sebagai tokoh penting di industri perminyakan dan politik Indonesia.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/liga-spanyol/d-8603450/balik-latihan-di-madrid-vinicius-segera-perpanjang-kontrak</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603445/mengenang-burhanuddin-bur-maras-tokoh-migas-dan-pendiri-lekom-maras</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/21/vinicius-jr-1768973038339_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/burhanuddin-bur-maras-1785815972293.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4087,33 +4087,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8 Data Fakta usai Indonesia Dihantam Vietnam: Bulan Madu Herdman Selesai</t>
+          <t>Krisis Iran Memanas, Warga Teheran Tetap Jalani Aktivitas di Tengah Ketegangan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:00:20 +0700</t>
+          <t>Tue, 04 Aug 2026 11:00:34 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Timnas Indonesia menelan kekalahan telak dari Timnas Vietnam di Piala AFF 2026. Bulan madu John Herdman bersama Skuad Garuda selesai.</t>
+          <t>Krisis Iran menjadi sorotan dunia. Di tengah ketegangan politik dan hubungan internasional, warga Teheran tetap menjalani aktivitas sehari-hari.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603448/8-data-fakta-usai-indonesia-dihantam-vietnam-bulan-madu-herdman-selesai</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8602911/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735_43.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/krisis-iran-memanas-warga-teheran-tetap-jalani-aktivitas-di-tengah-ketegangan-1785761340975_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4125,33 +4125,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Flick: Dear Barca, Mana Striker Barunya Nih?</t>
+          <t>Buruh Batalkan Rencana Demo di DPR Senin Depan, Takut Ada Penyusup</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:40:10 +0700</t>
+          <t>Tue, 04 Aug 2026 10:48:57 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Belum ada juga pemain baru datang untuk menggantikan Robert Lewandowski. Pelatih Barcelona Hansi Flick mencoba sabar menunggu.</t>
+          <t>KBPBI menunda aksi unjuk rasa di depan DPR untuk mendesak RUU Ketenagakerjaan. Keputusan diambil untuk menghindari potensi penyusup dan menjaga ketertiban.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603267/flick-dear-barca-mana-striker-barunya-nih</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603423/buruh-batalkan-rencana-demo-di-dpr-senin-depan-takut-ada-penyusup</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hansi-flick-1785806312405_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/22/presiden-konfederasi-serikat-pekerja-seluruh-indonesia-kspsi-andi-gani-1758528973493_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4163,33 +4163,33 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bikin Pantun untuk Fermin Aldeguer &amp;amp; Alex Marquez, Dapatkan Saldo E-Wallet</t>
+          <t>Setelah Naik Beruntun, Harga Emas Antam Akhirnya Turun</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:22:46 +0700</t>
+          <t>Tue, 04 Aug 2026 09:51:02 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ikuti kuis kreatif dari detikcom dan Bold Riders! Buat pantun lucu untuk Fermin Aldeguer atau Alex Marquez dan menangkan saldo e-wallet Rp 250 ribu!</t>
+          <t>Harga emas Antam hari ini turun Rp 7.000 per gram menjadi Rp 2.603.000. Rincian harga emas dari 0,5 gram hingga 1.000 gram juga disajikan.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/moto-gp/d-8603482/bikin-pantun-untuk-fermin-aldeguer-alex-marquez-dapatkan-saldo-e-wallet</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603360/setelah-naik-beruntun-harga-emas-antam-akhirnya-turun</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/la-bold-1785817343343.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/13/emas-batangan-1763011692898_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4201,33 +4201,33 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Direktur RB Leipzig: Kata Siapa Diomande Sudah 'Here We Go'?</t>
+          <t>Mitratel Cetak Laba Rp 1,11 T</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:20:45 +0700</t>
+          <t>Tue, 04 Aug 2026 09:48:19 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Yan Diomande sempat diklaim tinggal selangkah lagi gabung Real Madrid. Kabar itu dibantah keras petinggi RB Leipzig.</t>
+          <t>PT Dayamitra Telekomunikasi Tbk (MTEL) alias Mitratel membukukan kinerja positif hingga akhir Juni 2026.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603249/direktur-rb-leipzig-kata-siapa-diomande-sudah-here-we-go</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603358/mitratel-cetak-laba-rp-1-11-t</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/yann-diomande-1785778891457_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/17/potret-tower-mitratel-yang-manfaatkan-panel-surya-5_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4239,33 +4239,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jadwal Semifinal Piala Presiden: Persib Vs Persija, Persebaya Vs Arema</t>
+          <t>Dolar AS Tembus Rp 18.000 Pagi Ini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:00:41 +0700</t>
+          <t>Tue, 04 Aug 2026 09:33:38 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jadwal semifinal Piala Presiden 2026 mempertemukan Persib vs Persija dan Persebaya vs Arema. Simak jadwal semifinal hingga final.</t>
+          <t>Dolar AS bergerak menguat 0,06% ke level Rp 18.000 di awal pembukaan perdagangan.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603340/jadwal-semifinal-piala-presiden-persib-vs-persija-persebaya-vs-arema</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603345/dolar-as-tembus-rp-18-000-pagi-ini</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/12/980f4b19-e319-452f-bd84-74e7316325ce_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338333_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4277,33 +4277,33 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Liverpool Disarankan Pulangkan Alexander-Arnold</t>
+          <t>IHSG Dibuka Menguat ke 6.255</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:40:35 +0700</t>
+          <t>Tue, 04 Aug 2026 09:29:37 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Liverpool disarankan memulangkan Trent Alexander-Arnold yang kesulitan di Real Madrid. Umpan silang akurat dari TAA dinilai sangat dibutuhkan Alexander Isak.</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) pada perdagangan hari ini dibuka menguat.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603306/liverpool-disarankan-pulangkan-alexander-arnold</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603339/ihsg-dibuka-menguat-ke-6-255</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/13/trent-alexander-arnold-1773385024632_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/30/ihsg-rebound-usai-dua-hari-anjlok-seiring-pengunduran-diri-dirut-bei-1769748663323_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4315,33 +4315,33 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>John Herdman Rasakan Kekalahan Kedua Latih Indonesia</t>
+          <t>Empat Sistem Karantina Diperkuat, Ekspor Ikan Hias Indonesia Makin Mendunia</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:20:30 +0700</t>
+          <t>Tue, 04 Aug 2026 09:00:23 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Timnas Indonesia jadi bulan-bulanan Vietnam di Piala AFF 2026. Ini menjadi kekalahan kedua Garuda di bawah asuhan John Herdman.</t>
+          <t>Barantin memperkuat empat sistem karantina untuk meningkatkan daya saing dan kepercayaan pasar global terhadap ikan hias Indonesia.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603299/john-herdman-rasakan-kekalahan-kedua-latih-indonesia</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8602609/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/john-herdman-1785718686520_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/empat-sistem-karantina-diperkuat-ekspor-ikan-hias-indonesia-makin-mendunia-1785750239859_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4353,33 +4353,33 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bernardo Silva Tak Masalah Mainkan Banyak Peran di Madrid</t>
+          <t>Bos BGN Buka Suara soal Putusan MK Anggaran MBG dan Pendidikan Dipisah</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:00:20 +0700</t>
+          <t>Tue, 04 Aug 2026 08:50:38 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bernardo Silva siap dimainkan di berbagai posisi bersama Real Madrid. Ia punya kemampuan untuk memainkan sejumlah peran di lapangan.</t>
+          <t>Kami ini adalah lembaga operasional. Tentu saja kami akan melaksanakan apapun kebijakan dari pemerintah, kata Sudaryono.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603262/bernardo-silva-tak-masalah-mainkan-banyak-peran-di-madrid</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603305/bos-bgn-buka-suara-soal-putusan-mk-anggaran-mbg-dan-pendidikan-dipisah</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2288876689-1785802177577_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053334_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4391,33 +4391,33 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Indonesia Dikalahkan Vietnam, John Herdman Minta Garuda Tetap Fokus</t>
+          <t>TLKM Catat Kinerja Semester I-2026, BUVA dan TAPG Umumkan Aksi Korporasi</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:40:30 +0700</t>
+          <t>Tue, 04 Aug 2026 08:45:59 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Timnas Indonesia kalah 0-3 dari Vietnam pada matchday ketiga Piala AFF 2026. Pelatih Garuda John Herdman meminta timnya untuk tetap fokus.</t>
+          <t>TLKM membukukan pendapatan Rp75,9 triliun dan laba Rp10,6 triliun pada semester I-2026. BUVA siapkan rights issue, sementara TAPG tetapkan dividen interim.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603309/indonesia-dikalahkan-vietnam-john-herdman-minta-garuda-tetap-fokus</t>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8603300/tlkm-catat-kinerja-semester-i-2026-buva-dan-tapg-umumkan-aksi-korporasi</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bursa-dan-valas-1785806578-1785806579142.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4429,33 +4429,33 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ferran Mau Saja Bertahan di Barca Asalkan...</t>
+          <t>Trump Tak Suka Exxon &amp;amp; Chevron Untung Gede Gara-gara Harga Minyak Tinggi</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:20:05 +0700</t>
+          <t>Tue, 04 Aug 2026 08:17:17 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ferran Torres tidak masalah jika akhirnya bertahan di Barcelona. Tapi, ada satu syarat yang harus dipenuhi Los Cules, apa itu?</t>
+          <t>Mereka meraup terlalu banyak uang dari kelangkaan ini. Saya tidak menyukainya, ujar Trump.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603308/ferran-mau-saja-bertahan-di-barca-asalkan</t>
+          <t>https://finance.detik.com/energi/d-8603261/trump-tak-suka-exxon-chevron-untung-gede-gara-gara-harga-minyak-tinggi</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ferran-torres-1785808347370_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4467,33 +4467,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Persiapan Vietnam Biasa Saja, tapi Bisa Bantai Indonesia</t>
+          <t>Tips Aman Pakai QRIS agar Terhindar dari Penipuan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:00:10 +0700</t>
+          <t>Tue, 04 Aug 2026 08:05:09 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Timnas Vietnam mengganyang Indonesia di Piala AFF 2026. Pelatih Kim Sang-sik mengaku tak mempersiapkan timnya secara khusus sebelum pertandingan.</t>
+          <t>QRIS adalah metode pembayaran digital praktis. Pelajari tips aman bertransaksi, cara menggunakan QRIS, dan cara mengenali penipuan untuk keamanan Anda.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603248/persiapan-vietnam-biasa-saja-tapi-bisa-bantai-indonesia</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8602406/tips-aman-pakai-qris-agar-terhindar-dari-penipuan</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/timnas-vietnam-1785766971799_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/tips-aman-pakai-qris-agar-terhindar-dari-penipuan-1785745583872.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4505,33 +4505,33 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tinggalkan Madrid, Gonzalo Garcia Gabung Fulham</t>
+          <t>Pernak-pernik HUT Ke-81 RI Mulai Diburu di Pasar Asemka</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:30:20 +0700</t>
+          <t>Tue, 04 Aug 2026 08:00:44 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gonzalo Garcia resmi meninggalkan Real Madrid. Penyerang muda Spanyol itu melanjutkan kariernya bersama Fulham.</t>
+          <t>Permintaan pernak-pernik kemerdekaan mulai meningkat menjelang HUT Ke-81 RI. Pedagang Pasar Asemka mencatat penjualan naik sekitar 20 persen sejak akhir Juli.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603244/tinggalkan-madrid-gonzalo-garcia-gabung-fulham</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8601820/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gonzalo-garcia-1785804604431_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pernak-pernik-hut-ke-81-ri-mulai-diburu-di-pasar-asemka-1785728519984_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4543,33 +4543,33 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kualifikasi GTR Ultra Tutup 7 Agustus, Jangan Sampai Gagal Ikut Trail Run Ini</t>
+          <t>KSP &amp;amp; Bahlil  Buka Suara soal Ekspor 'Harta Karun' RI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:15:47 +0700</t>
+          <t>Tue, 04 Aug 2026 07:25:00 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kabar penting buat pelari trail, pendaftaran kualifikasi GTR Ultra 2026 resmi akan ditutup 7 Agustus 2026 pukul 23.30 WIB.</t>
+          <t>Kantor Staf Presiden (KSP) buka suara terkait soal harta karun Indonesia yakni logam tanah jarang.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sportstyle/d-8603071/kualifikasi-gtr-ultra-tutup-7-agustus-jangan-sampai-gagal-ikut-trail-run-ini</t>
+          <t>https://finance.detik.com/energi/d-8603108/ksp-bahlil-buka-suara-soal-ekspor-harta-karun-ri</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/gtr-ultra-2026-1773216163821_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/09/logam-tanah-jarang-jadi-harta-karun-yang-diincar-dunia-3_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4581,33 +4581,33 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bantai Indonesia, Vietnam Lanjutkan Rekor Tak Terkalahkan Sejak 2024</t>
+          <t>Musim Cuan 17 Agustus Dimulai, Pedagang Bendera Mulai Gelar Lapak</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 06:56:08 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vietnam melanjutkan catatan tak terkalahkan usai menumbangkan Indonesia. Golden Star Warriors tak terkalahkan dalam 21 laga terakhir.</t>
+          <t>Pedagang bendera di Jakarta mulai ramai menjelang HUT ke-81 RI, namun penjualan menurun.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603202/bantai-indonesia-vietnam-lanjutkan-rekor-tak-terkalahkan-sejak-2024</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603046/musim-cuan-17-agustus-dimulai-pedagang-bendera-mulai-gelar-lapak</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pedagang-bendera-1785742448675_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4619,33 +4619,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nguyen Hai Long Bobol Indonesia, Pamer Patch Emas Vietnam</t>
+          <t>Pameran Wastra Sultra Dorong Ekonomi Kreatif Perajin Lokal</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:30:40 +0700</t>
+          <t>Tue, 04 Aug 2026 06:30:56 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pemain Vietnam Nguyen Hai Long membobol gawang Timnas Indonesia. Dia merayakan golnya dengan memamerkan patch emas tanda juara bertahan Piala AFF.</t>
+          <t>Pameran kain tenun dan baju adat Sultra di Museum Sultra menjadi upaya melestarikan wastra sekaligus mengenalkan kekayaan budaya daerah.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603197/nguyen-hai-long-bobol-indonesia-pamer-patch-emas-vietnam</t>
+          <t>https://finance.detik.com/foto-bisnis/d-8602729/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pameran-wastra-sultra-dorong-ekonomi-kreatif-perajin-lokal-1785754770623_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4657,33 +4657,33 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Henderson Pilih Chelsea karena Xabi Alonso</t>
+          <t>Impor RI Naik Tajam, Ini Biang Keroknya</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 05:55:02 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Nama besar Xabi Alonso di sepakbola tentu jadi magnet untuk banyak pesepakbola, tak terkecuali Jordan Henderson. Alonso jadi alasannya gabung Chelsea.</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai impor Indonesia meningkat tajam pada Juni 2026 mencapai US$ 25,9 miliar atau naik 34,27%.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603196/henderson-pilih-chelsea-karena-xabi-alonso</t>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603040/impor-ri-naik-tajam-ini-biang-keroknya</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jordan-henderson-1785800731761_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/09/tanjung-priok-tetap-sibuk-di-tengah-tekanan-dolar-harapan-ekspor-menguat-1780979463918_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4700,28 +4700,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Statistik Indonesia Vs Vietnam: Efektivitas Jadi Pembeda</t>
+          <t>PSSI Cuan Rp 722 Miliar, Tetap Terbuka Bantuan dari Pemerintah</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:30:45 +0700</t>
+          <t>Tue, 04 Aug 2026 23:30:30 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Statistik saat Timnas Indonesia kalah 0-3 dari Vietnam. Tim Garuda tumpul di depan dan rapuh di belakang hingga kalah telak di kandang.</t>
+          <t>PSSI sukses mengumpulkan pendapatan fantastis Rp722 miliar. Angka tersebut sudah cukup buat PSSI, tetapi tetap terbuka jika ada tawaran bantuan pemerintah.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603163/statistik-indonesia-vs-vietnam-efektivitas-jadi-pembeda</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604319/pssi-cuan-rp-722-miliar-tetap-terbuka-bantuan-dari-pemerintah</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513806_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/menpora-erick-thohir-1783676745865.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4738,28 +4738,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pochettino Teken Kontrak Baru, Latih Timnas AS sampai 2030</t>
+          <t>Indonesia Punya 2 Srikandi di Asia Cross Country Rally 2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 23:25:00 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Karier Mauricio Pochettino sebagai pelatih Timnas Amerika Serikat masih panjang. Pria asal Argentina itu baru saja meneken kontrak baru.</t>
+          <t>Asia Cross Country Rally 2026 rupanya menarik minat para pereli wanita Indonesia. Mereka adalah Lody Natasha dan Satsy Laksamana.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8603160/pochettino-teken-kontrak-baru-latih-timnas-as-sampai-2030</t>
+          <t>https://sport.detik.com/sport-lain/d-8604616/indonesia-punya-2-srikandi-di-asia-cross-country-rally-2026</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/mauricio-pochettino-1785784945554_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/lody-natasha-dan-satsy-laksamana-1785860860805_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4776,28 +4776,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Indonesia Susah Banget Tembus Pertahanan Vietnam</t>
+          <t>Final Piala Presiden 2026: Persib Bandung Vs Persebaya Surabaya</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 23:00:00 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Timnas Indonesia mati kutu saat menjamu Vietnam dalam lanjutan Piala AFF 2026. Garuda kesulitan menembus pertahanan lawan dan jadi bulan-bulanan. Duh!</t>
+          <t>Final Piala Presiden 2026 akhirnya mendapatkan kontestannya. Persib Bandung vs Persebaya Surabaya akan tersaji di partai puncak.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603148/indonesia-susah-banget-tembus-pertahanan-vietnam</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604606/final-piala-presiden-2026-persib-bandung-vs-persebaya-surabaya</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492015_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4814,28 +4814,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Indonesia Digebuk Vietnam, Nadeo: Kami Main Kurang Bagus</t>
+          <t>Piala AFF: Indonesia Dijagokan Taklukkan Singapura, Lolos ke Semifinal</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 22:40:30 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Timnas Indonesia digebuk Vietnam di hadapan pendukung sendiri. Kiper Nadeo Argawinata mewakili rekan setimnya meminta maaf atas hasil buruk tersebut.</t>
+          <t>Timnas Indonesia akan dijamu Timnas Singapura dalam laga penentuan tiket ke semifinal Piala AFF 2026. Garuda dijagokan mengalahkan The Lions.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603151/indonesia-digebuk-vietnam-nadeo-kami-main-kurang-bagus</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604294/piala-aff-indonesia-dijagokan-taklukkan-singapura-lolos-ke-semifinal</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nadeo-argawinata-1785776694751_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_43.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4852,28 +4852,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>'Arsenal Sudah Pasti Mau Pertahankan Gelar, Tekanan Ada di Rival'</t>
+          <t>Cara Memen Agar Mobilnya Siap Taklukkan Medan Berat AXCR 2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:00:30 +0700</t>
+          <t>Tue, 04 Aug 2026 22:25:00 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Christos Tzolis menyatakan bahwa Arsenal siap untuk mempertahankan gelar. Pemain baru Meriam London itu menyebut tekanan ada di rival.</t>
+          <t>Memen Harianto akan membawa nama Indonesia di Asia Cross Country Rally (AXCR) 2026. Dia melakukan persiapan secara maksimal, terutama untuk mobilnya.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603149/arsenal-sudah-pasti-mau-pertahankan-gelar-tekanan-ada-di-rival</t>
+          <t>https://sport.detik.com/sport-lain/d-8604594/cara-memen-agar-mobilnya-siap-taklukkan-medan-berat-axcr-2026</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/arsenal-1785694598503_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/memen-harianto-1785860948781_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4890,28 +4890,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jelang Tampil di AXCR 2026, Memen Harianto Dapat 'Tenaga' Baru</t>
+          <t>Persebaya Vs Arema: Bajul Ijo Menang 1-0, Lolos ke Final Piala Presiden</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:45:20 +0700</t>
+          <t>Tue, 04 Aug 2026 22:17:39 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Memen Harianto terus mempersiapkan diri jelang Asia Cross Country Rally (AXCR) 2026. Memen mendapat suntikan tenaga baru, apa itu?</t>
+          <t>Persebaya Surabaya meraih kemenangan 1-0 atas Arema FC di semifinal Piala Presiden 2026. Persebaya lolos ke final untuk menghadapi Persib Bandung.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sport-lain/d-8603162/jelang-tampil-di-axcr-2026-memen-harianto-dapat-tenaga-baru</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604584/persebaya-vs-arema-bajul-ijo-menang-1-0-lolos-ke-final-piala-presiden</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/indonesia-cross-country-rally-team-1785786307522_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Erick Thohir Maju Jadi Ketum PSSI Lagi Tahun Depan?</t>
+          <t>Hasil Piala AFF 2026: Thailand Atasi Filipina 1-0</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:00:05 +0700</t>
+          <t>Tue, 04 Aug 2026 21:58:26 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Erick Thohir tidak menutup peluang mencalonkan diri kembali menjadi Ketua Umum PSSI. Tapi sebelum itu, ia akan berkonsultasi dengan pemerintah dan FIFA dulu.</t>
+          <t>Thailand melanjutkan start positifnya di Piala AFF 2026. Tim War Elephants menang tipis 1-0 atas Filipina dan menguasai pucuk klasemen Grup B.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603147/erick-thohir-maju-jadi-ketum-pssi-lagi-tahun-depan</t>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604566/hasil-piala-aff-2026-thailand-atasi-filipina-1-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pssi-1785758655620_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/14/logo-piala-aff-2026-1768381280444_169.png?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4958,8 +4958,2478 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Vicario dan Suzuki Diincar Juventus, Buffon Bilang Begini!</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:45:05 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Juventus dikabarkan menjadikan Guglielmo Vicario dan Zion Suzuki sebagai kandidat kiper anyar. Bagaimana menurut Gianluigi Buffon?</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8604289/vicario-dan-suzuki-diincar-juventus-buffon-bilang-begini</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/04/gianluigi-buffon_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pelajaran dari Singapura Sukses Antar Vietnam Cukur Indonesia</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:30:15 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Vietnam banyak belajar dari hasil imbang melawan Singapura. Pemilihan strategi yang tepat sukses antar Vietnam mencukur Timnas Indonesia 3-0.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604285/pelajaran-dari-singapura-sukses-antar-vietnam-cukur-indonesia</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PBSI Cari Pasangan untuk Adnan Maulana</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:20:37 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PP PBSI masih mencari pasangan untuk Adnan Maulana. Itu setelah rekan tandemnya yang lama, Indah Cahya Sari Jamil, dipasangkan dengan pemain lain.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8604509/pbsi-cari-pasangan-untuk-adnan-maulana</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/02/adnan-maulanaindah-cahya-sari-jamil-1780382604246_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Matthijs de Ligt Belum Bisa Gabung ke MU</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:15:40 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Manchester United masih belum bisa diperkuat bek tengahnya, Matthijs de Ligt. Dirinya masih belum pulih setelah operasi cedera punggung.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603854/matthijs-de-ligt-belum-bisa-gabung-ke-mu</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/07/matthijs-de-ligt-1775546584882.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Jelang Lawan Singapura, Timnas Indonesia Butuh Pemulihan Moral</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia sangat terpukul usai kalah 0-3 dari Vietnam. Skuad Garuda kini harus memulihkan moral jelang melawan Singapura.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604284/jelang-lawan-singapura-timnas-indonesia-butuh-pemulihan-moral</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Jorge Martin Tak Sabar Lanjutkan Duel Sengit Perebutan Gelar MotoGP 2026!</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:50:40 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Jorge Martin antusias menatap paruh kedua MotoGP 2026. Ia yakin persaingan gelar juara dunia akan semakin sengit karena lima pebalap hanya terpaut 24 poin.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8604324/jorge-martin-tak-sabar-lanjutkan-duel-sengit-perebutan-gelar-motogp-2026</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/moto-motogp-ned-1782675298213_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Mulai Tahun Depan Piala Presiden untuk Timnas Indonesia, Tidak Lagi Klub</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:45:15 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ketum PSSI Erick Thohir mengungkapkan Piala Presiden mulai tahun depan tidak lagi menjadi turnamen pramusim klub, melainkan jadi agenda Timnas Indonesia.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604194/mulai-tahun-depan-piala-presiden-untuk-timnas-indonesia-tidak-lagi-klub</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Kovacic: Anderson Bikin Lini Tengah Man City Lebih Bertenaga</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:30:50 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Mateo Kovacic antusias dengan Elliott Anderson, meski itu juga berarti persaingan lini tengah Manchester City kian ketat. Ia yakin tim makin kuat.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604197/kovacic-anderson-bikin-lini-tengah-man-city-lebih-bertenaga</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/29/elliott-anderson-1764354213557_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Usai Indonesia Dihajar Vietnam, Hubner Saling Sindir dengan Do Hoang Hen</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia dihajar Timnas Vietnam dalam laga lanjutan Piala AFF 2026. Justin Hubner saling sindir dengan pemain Golden Star Warriors, Do Hoang Hen.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604196/usai-indonesia-dihajar-vietnam-hubner-saling-sindir-dengan-do-hoang-hen</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513456_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Buffon Percaya sama Mancini, Semoga Italia Lolos ke Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:00:40 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sepakbola Italia bergejolak belakangan ini dalam penunjukan pelatih baru. Buffon mau drama itu berakhir, percayakan ke juru taktik baru Roberto Mancini.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8604208/buffon-percaya-sama-mancini-semoga-italia-lolos-ke-piala-dunia</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/03/gianluigi-buffon-1748885612603.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Marco Bezzecchi Belum 100%, tapi Siap Comeback di MotoGP Inggris 2026!</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:50:50 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Marco Bezzecchi siap kembali balapan di MotoGP Inggris 2026 meski mengaku belum pulih 100 persen usai menjalani operasi tulang selangka dan lutut.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8604281/marco-bezzecchi-belum-100-tapi-siap-comeback-di-motogp-inggris-2026</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/15/motor-motogp-germany-1784050516185_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Vietnam 'Oper' Tekanan ke Indonesia</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Vietnam datang dengan tekanan dan kini melemparnya ke Indonesia. Mampukah skuad Garuda merespons tekanan itu dan keluar dari posisi terjepit.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604184/vietnam-oper-tekanan-ke-indonesia</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Liverpool Enggan Jual Gakpo, tapi Kalau Tottenham Kasih Harga Bagus...</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:20:45 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur meminati Cody Gakpo dari Liverpool. The Reds mau mempertahankan sang winger, tapi bakal goyah kalau dikasih harga bagus.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8604186/liverpool-enggan-jual-gakpo-tapi-kalau-tottenham-kasih-harga-bagus</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/05/cody-gakpo-1754352181260.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Detak Jantung Marc Marquez Bisa Ungkap Kans Juara MotoGP 2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:10:20 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Detak jantung Marc Marquez saat MotoGP Inggris diyakini bisa menjadi indikator keberhasilan pemulihan fisiknya terkait kans mengejar gelar dunia MotoGP 2026.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8604170/detak-jantung-marc-marquez-bisa-ungkap-kans-juara-motogp-2026</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/12/marc-marquez-1783860046236_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>John Herdman: Indonesia Asyik di Depan, Jadi Lupa Pertahanan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Pelatih Timnas Indonesia John Herdman menyebut timnya terlalu asyik main di depan saat jumpa Vietnam. Hasilnya timnya malah kecolongan di lini pertahanan.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604183/john-herdman-indonesia-asyik-di-depan-jadi-lupa-pertahanan</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/27/gaya-nyentrik-john-herdman-kawal-timnas-garuda-1774628369095.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Singapura Vs Indonesia: Ulangan Situasi di Manila Sedekade Lalu</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:40:45 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Indonesia menjalani laga hidup dan mati melawan Singapura di Piala AFF 2026. Laga ini menjadi ulangan persaingan Garuda melawan The Lions sedekade lalu.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603914/singapura-vs-indonesia-ulangan-situasi-di-manila-sedekade-lalu</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/11/26/54e9d3f7-5e6d-46d8-b5d2-e2d0149535a8_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Malut United Resmi Ganti Nama Jadi Java United, Pindah Markas ke Semarang</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Malut United resmi berganti nama menjadi Java United dan memindahkan markas dari Ternate ke Semarang.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604279/malut-united-resmi-ganti-nama-jadi-java-united-pindah-markas-ke-semarang</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/java-united-1785770401869_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Chelsea Mulai Bersih-bersih</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:20:15 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Chelsea punya 40 pemain di dalam skuadnya. Bursa transfer musim panas 2026 masih buka sampai 1 September, Si Biru kini saatnya bersih-bersih.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603920/chelsea-mulai-bersih-bersih</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/09/chelsea-1778261458229.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RI Bawa Pulang 15 Medali dari Kejuaraan Asia MMA, Kini Fokus Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:10:25 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Tim MMA Indonesia meraih 15 medali, termasuk lima emas, di GAMMA Asian Championships 2026.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sport-lain/d-8604192/ri-bawa-pulang-15-medali-dari-kejuaraan-asia-mma-kini-fokus-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gamma-asian-championships-2026-1785838947680_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Erick Thohir: Saya Tetap Percaya pada John Herdman</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia kalah 0-3 dari Vietnam, kans ke semifinal Piala AFF 2026 terancam. Ketum PSSI Erick Thohir membela pelatih John Herdman.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603911/erick-thohir-saya-tetap-percaya-pada-john-herdman</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/13/selamat-datang-john-herdman-pelatih-baru-timnas-indonesia-1768277980430.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Dirumorkan Kembali ke Italia, Kovacic: Man City Masih Mengandalkanku</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:45:40 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Mateo Kovacic dirumorkan kembali ke Italia, dengan kabar Juventus dan Inter Milan meminati. Tapi gelandang senior itu bilang masih diandalkan Manchester City.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603894/dirumorkan-kembali-ke-italia-kovacic-man-city-masih-mengandalkanku</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/20/wolverhampton-wanderers-manchester-city_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Persib Vs Persija: Menang 2-1, Maung Bandung ke Final Piala Presiden 2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:31:55 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Persib Bandung mengalahkan Persija Jakarta di semifinal Piala Presiden 2026. Pasukan Igor Tolic pun melaju ke final.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8604212/persib-vs-persija-menang-2-1-maung-bandung-ke-final-piala-presiden-2026</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Bagas Maulana Dinilai Cocok ke Ganda Campuran, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Pelatih ganda putra Antonius Budi Ariantho menjelaskan alasan Bagas Maulana dipindahkan ke sektor ganda campuran.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8604165/bagas-maulana-dinilai-cocok-ke-ganda-campuran-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/02/12/bagas-maulana-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Vietnam Tahu Caranya Keluar dari Tekanan</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Vietnam datang ke Indonesia dengan tekanan besar usai ditahan Singapura. The Golden Star Warriors merespons dengan cemerlang.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603861/vietnam-tahu-caranya-keluar-dari-tekanan</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Dear Liverpool, Ini Isak yang Baru</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:00:25 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Alexander Isak mengaku sudah pulih 100 persen. Sang striker siap berikan yang terbaik buat Liverpool di musim baru!</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603859/dear-liverpool-ini-isak-yang-baru</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/alexander-isak-1778251850354.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia Masih Berani Main High Pressing, John?</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:40:40 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia sangat buruk dalam transisi bertahan dengan permainan high pressing. Pelatih John Herdman apakah akan mengubah cara bermain Garuda?</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603770/timnas-indonesia-masih-berani-main-high-pressing-john</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Piala AFF: Indonesia Pernah Lima Kali Gagal ke Semifinal</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:20:15 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia sedang di ujung tanduk di Piala AFF 2026. Sepanjang sejarah pesta sepakbola ASEAN, Skuad Garuda pernah lima kali gagal ke semifinal.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603776/piala-aff-indonesia-pernah-lima-kali-gagal-ke-semifinal</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Welbeck Kemarin Hobi Jebol Chelsea, Kini Jagoan Baru The Blues</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Chelsea resmi mendatangkan Danny Welbeck. Sang striker veteran lumayan hobi jebol gawang The Blues dulu, tapi kini diharapkan jadi jagoan.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8603780/welbeck-kemarin-hobi-jebol-chelsea-kini-jagoan-baru-the-blues</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/danny-welbeckchelseabursa-transfer-chelsea-1785602779561.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ini Sebab PBSI Belum Rilis Daftar Pemain di Asian Games</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Nama-nama pebulutangkis Indonesia yang akan diturunkan di Asian Games 2026 belum final. PBSI masih akan melihat hasil dari Kejuaraan Dunia pada 17-23 Agustus.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8603931/ini-sebab-pbsi-belum-rilis-daftar-pemain-di-asian-games</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/26/logo-pbsi.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>John Herdman ke Suporter: Kita Menang Bersama, Kalah Juga Bersama</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:40:25 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia dihajar Timnas Vietnam saat menjalani laga kandang di Piala AFF 2026. John Herdman berjanji Skuad Garuda akan bangkit.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603741/john-herdman-ke-suporter-kita-menang-bersama-kalah-juga-bersama</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/31/herdman-janji-bangkit-usai-kekalahan-targetkan-indonesia-ke-piala-dunia-2030-1774891836257_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Awas MU, Bayern Munich Minati Benjamin Sesko</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Bayern Munich menaruh minat pada striker Man United, Benjamin Sesko. Tapi Bayern enggak mau buru-buru merekrutnya dulu, mungkin beberapa tahun mendatang nanti.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603737/awas-mu-bayern-munich-minati-benjamin-sesko</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/02/benjamin-sesko-1772389311489.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Viet Anh Berdarah-Darah untuk Tuntaskan Dendam ke Indonesia</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:00:45 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Vietnam sukses membabat Indonesia 3-0 dalam laga Grup A Piala AFF 2026. Bek Bui Hoang Viet Anh sangat puas Golden Star Warriors berhasil balas dendam.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603740/viet-anh-berdarah-darah-untuk-tuntaskan-dendam-ke-indonesia</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513664_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Asian Games 2026: Bulutangkis Beregu Putra Jadi Asa Indonesia Raih Emas</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:51:15 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Chef de Mission Indonesia Todotua Pasaribu berharap bulutangkis bisa mendapatkan medali emas di Asian Games 2026. Secara khusus nomor ganda putra.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8603821/asian-games-2026-bulutangkis-beregu-putra-jadi-asa-indonesia-raih-emas</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/06/ilustrasi-bulutangkis.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Bermain Buruk, Indonesia Dipecundangi Vietnam!</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:44:50 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Apakah Indonesia bisa menjaga asa untuk tampil di semifinal Piala AFF 2026?</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/sepakbola-indonesia/d-8603690/bermain-buruk-indonesia-dipecundangi-vietnam</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/detiksore-4-agustus-2026-1785825691822_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Marselino Ferdinan Tak Bisa Main di Piala AFF 2026!</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:40:10 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Kabar buruk menghampiri Timnas Indonesia di tengah gelaran Piala AFF 2026. Marselino Ferdinan tak bisa memperkuat Skuad Garuda!</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603636/marselino-ferdinan-tak-bisa-main-di-piala-aff-2026</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/12/marselino-ferdinan_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Usai Permalukan Indonesia, Vietnam Dapat Bonus Rp1,37 Miliar</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Timnas Vietnam mempermalukan Timnas Indonesia di Piala AFF 2026. Golden Star Warriors mendapat bonus 2 miliar dong atau setara Rp1,37 miliar.</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603633/usai-permalukan-indonesia-vietnam-dapat-bonus-rp1-37-miliar</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Presiden FIFA Batal Naik Gaji 500 Persen</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Presiden FIFA Gianni Infantino diketahui bakal naik gaji 525 persen andai wacana jual saham Piala Dunia sukses. Wacana itu batal, nggak gaji naik deh!</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603662/presiden-fifa-batal-naik-gaji-500-persen</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/16/gianni-infantino.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sebuah Perenungan Rizky Ridho</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:40:40 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Rizky Ridho mengakui kesalahannya dalam kekalahan Indonesia dari Vietnam. Dia akan mencoba merenungkannya untuk berbenah di laga selanjutnya.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603568/sebuah-perenungan-rizky-ridho</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Bagas Maulana ke Ganda Campuran, Tandem sama Indah Cahya</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:35:30 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>PBSI kembali jajal kombinasi baru di sektor ganda campuran. Kali ini, Bagas Maulana dipasangkan dengan Indah Cahya Sari Jamil!</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8603660/bagas-maulana-ke-ganda-campuran-tandem-sama-indah-cahya</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/22/fajarfikri-kalahkan-bagasleo-di-indonesia-masters-2026-1769070561744.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Jika Arsenal Dapatkan Vinicius...</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:20:25 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Situasi Vinicius Jr di Madrid masih tanda tanya, rumor Arsenal mau merekrutnya juga terus mencuat. Wilshere bakal girang betul andai The Gunners mendapatkannya.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603570/jika-arsenal-dapatkan-vinicius</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/02/vinicius-jr.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Indonesia Vs Vietnam: Sayap-sayap Lemah Garuda</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia dibenamkan Timnas Vietnam di Piala AFF 2026. Sayap-sayap Garuda terlihat lemah di hadapan Golden Star Warriors.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603566/indonesia-vs-vietnam-sayap-sayap-lemah-garuda</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Posisi di FIFA Terancam, Infantino Minta Dukungan Trump?</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:40:25 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Posisi Gianni Infantino di FIFA terancam usai geger wacana jual saham Piala Dunia. Pria asal Swiss itu kabarnya meminta dukungan Presiden AS Donald Trump.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603451/posisi-di-fifa-terancam-infantino-minta-dukungan-trump</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/presiden-as-donald-trump-1783299814038_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Balik Latihan di Madrid, Vinicius Segera Perpanjang Kontrak</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:20:30 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Vinicius Jr dilaporkan segera memperpanjang kontraknya setelah sudah kembali berlatih dengan Real Madrid. Ia memutuskan bertahan di El Real.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603450/balik-latihan-di-madrid-vinicius-segera-perpanjang-kontrak</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/21/vinicius-jr-1768973038339_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>8 Data Fakta usai Indonesia Dihantam Vietnam: Bulan Madu Herdman Selesai</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:00:20 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia menelan kekalahan telak dari Timnas Vietnam di Piala AFF 2026. Bulan madu John Herdman bersama Skuad Garuda selesai.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603448/8-data-fakta-usai-indonesia-dihantam-vietnam-bulan-madu-herdman-selesai</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513735_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Flick: Dear Barca, Mana Striker Barunya Nih?</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:40:10 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Belum ada juga pemain baru datang untuk menggantikan Robert Lewandowski. Pelatih Barcelona Hansi Flick mencoba sabar menunggu.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603267/flick-dear-barca-mana-striker-barunya-nih</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/hansi-flick-1785806312405_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Bikin Pantun untuk Fermin Aldeguer &amp;amp; Alex Marquez, Dapatkan Saldo E-Wallet</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:22:46 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Ikuti kuis kreatif dari detikcom dan Bold Riders! Buat pantun lucu untuk Fermin Aldeguer atau Alex Marquez dan menangkan saldo e-wallet Rp 250 ribu!</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8603482/bikin-pantun-untuk-fermin-aldeguer-alex-marquez-dapatkan-saldo-e-wallet</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/la-bold-1785817343343.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Direktur RB Leipzig: Kata Siapa Diomande Sudah 'Here We Go'?</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:20:45 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Yan Diomande sempat diklaim tinggal selangkah lagi gabung Real Madrid. Kabar itu dibantah keras petinggi RB Leipzig.</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-jerman/d-8603249/direktur-rb-leipzig-kata-siapa-diomande-sudah-here-we-go</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/yann-diomande-1785778891457_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Jadwal Semifinal Piala Presiden: Persib Vs Persija, Persebaya Vs Arema</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:00:41 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Jadwal semifinal Piala Presiden 2026 mempertemukan Persib vs Persija dan Persebaya vs Arema. Simak jadwal semifinal hingga final.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603340/jadwal-semifinal-piala-presiden-persib-vs-persija-persebaya-vs-arema</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/12/980f4b19-e319-452f-bd84-74e7316325ce_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Liverpool Disarankan Pulangkan Alexander-Arnold</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:40:35 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Liverpool disarankan memulangkan Trent Alexander-Arnold yang kesulitan di Real Madrid. Umpan silang akurat dari TAA dinilai sangat dibutuhkan Alexander Isak.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603306/liverpool-disarankan-pulangkan-alexander-arnold</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/13/trent-alexander-arnold-1773385024632_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>John Herdman Rasakan Kekalahan Kedua Latih Indonesia</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:20:30 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia jadi bulan-bulanan Vietnam di Piala AFF 2026. Ini menjadi kekalahan kedua Garuda di bawah asuhan John Herdman.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603299/john-herdman-rasakan-kekalahan-kedua-latih-indonesia</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/john-herdman-1785718686520_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Bernardo Silva Tak Masalah Mainkan Banyak Peran di Madrid</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:00:20 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Bernardo Silva siap dimainkan di berbagai posisi bersama Real Madrid. Ia punya kemampuan untuk memainkan sejumlah peran di lapangan.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603262/bernardo-silva-tak-masalah-mainkan-banyak-peran-di-madrid</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/2288876689-1785802177577_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Indonesia Dikalahkan Vietnam, John Herdman Minta Garuda Tetap Fokus</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia kalah 0-3 dari Vietnam pada matchday ketiga Piala AFF 2026. Pelatih Garuda John Herdman meminta timnya untuk tetap fokus.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603309/indonesia-dikalahkan-vietnam-john-herdman-minta-garuda-tetap-fokus</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ferran Mau Saja Bertahan di Barca Asalkan...</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:20:05 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Ferran Torres tidak masalah jika akhirnya bertahan di Barcelona. Tapi, ada satu syarat yang harus dipenuhi Los Cules, apa itu?</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8603308/ferran-mau-saja-bertahan-di-barca-asalkan</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/ferran-torres-1785808347370_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Persiapan Vietnam Biasa Saja, tapi Bisa Bantai Indonesia</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Timnas Vietnam mengganyang Indonesia di Piala AFF 2026. Pelatih Kim Sang-sik mengaku tak mempersiapkan timnya secara khusus sebelum pertandingan.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603248/persiapan-vietnam-biasa-saja-tapi-bisa-bantai-indonesia</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/timnas-vietnam-1785766971799_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Tinggalkan Madrid, Gonzalo Garcia Gabung Fulham</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Gonzalo Garcia resmi meninggalkan Real Madrid. Penyerang muda Spanyol itu melanjutkan kariernya bersama Fulham.</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603244/tinggalkan-madrid-gonzalo-garcia-gabung-fulham</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gonzalo-garcia-1785804604431_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Kualifikasi GTR Ultra Tutup 7 Agustus, Jangan Sampai Gagal Ikut Trail Run Ini</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:15:47 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Kabar penting buat pelari trail, pendaftaran kualifikasi GTR Ultra 2026 resmi akan ditutup 7 Agustus 2026 pukul 23.30 WIB.</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sportstyle/d-8603071/kualifikasi-gtr-ultra-tutup-7-agustus-jangan-sampai-gagal-ikut-trail-run-ini</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/gtr-ultra-2026-1773216163821_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Bantai Indonesia, Vietnam Lanjutkan Rekor Tak Terkalahkan Sejak 2024</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Vietnam melanjutkan catatan tak terkalahkan usai menumbangkan Indonesia. Golden Star Warriors tak terkalahkan dalam 21 laga terakhir.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603202/bantai-indonesia-vietnam-lanjutkan-rekor-tak-terkalahkan-sejak-2024</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Nguyen Hai Long Bobol Indonesia, Pamer Patch Emas Vietnam</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:30:40 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Pemain Vietnam Nguyen Hai Long membobol gawang Timnas Indonesia. Dia merayakan golnya dengan memamerkan patch emas tanda juara bertahan Piala AFF.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603197/nguyen-hai-long-bobol-indonesia-pamer-patch-emas-vietnam</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Henderson Pilih Chelsea karena Xabi Alonso</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Nama besar Xabi Alonso di sepakbola tentu jadi magnet untuk banyak pesepakbola, tak terkecuali Jordan Henderson. Alonso jadi alasannya gabung Chelsea.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603196/henderson-pilih-chelsea-karena-xabi-alonso</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/jordan-henderson-1785800731761_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Statistik Indonesia Vs Vietnam: Efektivitas Jadi Pembeda</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Statistik saat Timnas Indonesia kalah 0-3 dari Vietnam. Tim Garuda tumpul di depan dan rapuh di belakang hingga kalah telak di kandang.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603163/statistik-indonesia-vs-vietnam-efektivitas-jadi-pembeda</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513806_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pochettino Teken Kontrak Baru, Latih Timnas AS sampai 2030</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Karier Mauricio Pochettino sebagai pelatih Timnas Amerika Serikat masih panjang. Pria asal Argentina itu baru saja meneken kontrak baru.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8603160/pochettino-teken-kontrak-baru-latih-timnas-as-sampai-2030</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/mauricio-pochettino-1785784945554_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Indonesia Susah Banget Tembus Pertahanan Vietnam</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia mati kutu saat menjamu Vietnam dalam lanjutan Piala AFF 2026. Garuda kesulitan menembus pertahanan lawan dan jadi bulan-bulanan. Duh!</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603148/indonesia-susah-banget-tembus-pertahanan-vietnam</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513519_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Indonesia Digebuk Vietnam, Nadeo: Kami Main Kurang Bagus</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia digebuk Vietnam di hadapan pendukung sendiri. Kiper Nadeo Argawinata mewakili rekan setimnya meminta maaf atas hasil buruk tersebut.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8603151/indonesia-digebuk-vietnam-nadeo-kami-main-kurang-bagus</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nadeo-argawinata-1785776694751_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>'Arsenal Sudah Pasti Mau Pertahankan Gelar, Tekanan Ada di Rival'</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Christos Tzolis menyatakan bahwa Arsenal siap untuk mempertahankan gelar. Pemain baru Meriam London itu menyebut tekanan ada di rival.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8603149/arsenal-sudah-pasti-mau-pertahankan-gelar-tekanan-ada-di-rival</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/arsenal-1785694598503_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Jelang Tampil di AXCR 2026, Memen Harianto Dapat 'Tenaga' Baru</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:45:20 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Memen Harianto terus mempersiapkan diri jelang Asia Cross Country Rally (AXCR) 2026. Memen mendapat suntikan tenaga baru, apa itu?</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sport-lain/d-8603162/jelang-tampil-di-axcr-2026-memen-harianto-dapat-tenaga-baru</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/indonesia-cross-country-rally-team-1785786307522_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H119"/>
+  <autoFilter ref="A1:H184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-04.xlsx
+++ b/data/berita_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,17 +419,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +474,11 @@
           <t>Media</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sentimen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +517,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +556,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +595,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +634,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,6 +673,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -701,6 +712,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -739,6 +751,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -777,6 +790,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -815,6 +829,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -853,6 +868,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -891,6 +907,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -929,6 +946,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -967,6 +985,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1005,6 +1024,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1043,6 +1063,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1081,6 +1102,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1119,6 +1141,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1157,6 +1180,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1195,6 +1219,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1233,6 +1258,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1271,6 +1297,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1309,6 +1336,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1347,6 +1375,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1385,6 +1414,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1423,6 +1453,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1461,6 +1492,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1499,6 +1531,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1537,6 +1570,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1575,6 +1609,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1613,6 +1648,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1651,6 +1687,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1689,6 +1726,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1727,6 +1765,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1765,6 +1804,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1803,6 +1843,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1841,6 +1882,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1879,6 +1921,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1917,6 +1960,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1955,6 +1999,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1993,6 +2038,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2031,6 +2077,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2069,6 +2116,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2107,6 +2155,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2145,6 +2194,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2183,6 +2233,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2221,6 +2272,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2259,6 +2311,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2297,6 +2350,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2335,6 +2389,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2373,6 +2428,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2411,6 +2467,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2449,6 +2506,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2487,6 +2545,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2525,6 +2584,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2563,6 +2623,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2601,6 +2662,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2639,6 +2701,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2677,6 +2740,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2715,6 +2779,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2753,6 +2818,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2791,6 +2857,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2829,6 +2896,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2867,6 +2935,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2905,6 +2974,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2943,6 +3013,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2981,6 +3052,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3019,6 +3091,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3057,6 +3130,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3095,6 +3169,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3133,6 +3208,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3171,6 +3247,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3209,6 +3286,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3247,6 +3325,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3285,6 +3364,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3323,6 +3403,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3361,6 +3442,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3399,6 +3481,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3437,6 +3520,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3475,6 +3559,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3513,6 +3598,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3551,6 +3637,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3589,6 +3676,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3627,6 +3715,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3665,6 +3754,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3703,6 +3793,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3741,6 +3832,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3779,6 +3871,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3817,6 +3910,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3855,6 +3949,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3893,6 +3988,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3931,6 +4027,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3969,6 +4066,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4007,6 +4105,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4045,6 +4144,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4083,6 +4183,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4121,6 +4222,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4159,6 +4261,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4197,6 +4300,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4235,6 +4339,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4273,6 +4378,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4311,6 +4417,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4349,6 +4456,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4387,6 +4495,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4425,6 +4534,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4463,6 +4573,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4501,6 +4612,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4539,6 +4651,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4577,6 +4690,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4615,6 +4729,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4653,6 +4768,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4691,6 +4807,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4729,6 +4846,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4767,6 +4885,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4805,6 +4924,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4843,6 +4963,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4881,6 +5002,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4919,6 +5041,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4957,6 +5080,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4995,6 +5119,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5033,6 +5158,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5071,6 +5197,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5109,6 +5236,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5147,6 +5275,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5185,6 +5314,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5223,6 +5353,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5261,6 +5392,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5299,6 +5431,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5337,6 +5470,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5375,6 +5509,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5413,6 +5548,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5451,6 +5587,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5489,6 +5626,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5527,6 +5665,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5565,6 +5704,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5603,6 +5743,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5641,6 +5782,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5679,6 +5821,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5717,6 +5860,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5755,6 +5899,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5793,6 +5938,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5831,6 +5977,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5869,6 +6016,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5907,6 +6055,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5945,6 +6094,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5983,6 +6133,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6021,6 +6172,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6059,6 +6211,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6097,6 +6250,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6135,6 +6289,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6173,6 +6328,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6211,6 +6367,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6249,6 +6406,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6287,6 +6445,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6325,6 +6484,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6363,6 +6523,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6401,6 +6562,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6439,6 +6601,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6477,6 +6640,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6515,6 +6679,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6553,6 +6718,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6591,6 +6757,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6629,6 +6796,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6667,6 +6835,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6705,6 +6874,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6743,6 +6913,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6781,6 +6952,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6819,6 +6991,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6857,6 +7030,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6895,6 +7069,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6933,6 +7108,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6971,6 +7147,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7009,6 +7186,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7047,6 +7225,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7085,6 +7264,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7123,6 +7303,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7161,6 +7342,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7199,6 +7381,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7237,6 +7420,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7275,6 +7459,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7313,6 +7498,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7351,6 +7537,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7389,6 +7576,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7427,9 +7615,104 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Balik Latihan di Madrid, Vinicius Segera Perpanjang Kontrak</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:20:30 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Vinicius Jr dilaporkan segera memperpanjang kontraknya setelah sudah kembali berlatih dengan Real Madrid. Ia memutuskan bertahan di El Real.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/liga-spanyol/d-8603450/balik-latihan-di-madrid-vinicius-segera-perpanjang-kontrak</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/21/vinicius-jr-1768973038339_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Pochettino Teken Kontrak Baru, Latih Timnas AS sampai 2030</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Karier Mauricio Pochettino sebagai pelatih Timnas Amerika Serikat masih panjang. Pria asal Argentina itu baru saja meneken kontrak baru.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/juara-bola-dunia-2026/bola-dunia/d-8603160/pochettino-teken-kontrak-baru-latih-timnas-as-sampai-2030</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/mauricio-pochettino-1785784945554_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H184"/>
+  <autoFilter ref="A1:I186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-04.xlsx
+++ b/data/berita_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -430,7 +430,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7812,8 +7812,1136 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Trump Kena Batunya, China Makin Kuat Sudah Tak Butuh Amerika</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>China mengeluarkan revisi peraturan pembuatan chip untuk melindungi desain lokal di tengah pembatasan AS. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804133025-37-756435/trump-kena-batunya-china-makin-kuat-sudah-tak-butuh-amerika</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/15/presiden-china-xi-jinping-memperlihatkan-suasana-kompleks-bersejarah-zhongnanhai-kepada-presiden-amerika-serikat-donald-trump--1778835074284_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Cara Bos ChatGPT Mengasuh Anak Bikin Merinding Seperti di Dunia Lain</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pendiri OpenAI, Sam Altman, mengusulkan penggunaan AI dalam mengasuh anak.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804114025-37-756356/cara-bos-chatgpt-mengasuh-anak-bikin-merinding-seperti-di-dunia-lain</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/16/sam-altman-ceo-openai-menghadiri-konferensi-media-dan-teknologi-tahunan-allen-and-co-sun-valley-di-sun-valley-resort-di-sun-va-1784174569958_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Salah Ketik Nama Satu Karakter, Salah Masuk Penjara 18 Bulan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Brandon Klayme, warga Kanada, dipenjara 18 bulan karena kesalahan penulisan nama pengguna.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804124440-37-756391/salah-ketik-nama-satu-karakter-salah-masuk-penjara-18-bulan</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/29/ilustrasi-penjara-pexels-1766985566454_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Satu Bulan Tak Hujan Setetes Pun, Peristiwa Langka 1,5 Abad</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Rekor mengkhawatirkan tercatat di Inggris: Stasiun cuaca Kew Gardens mencatat bulan Juli 2026 tanpa curah hujan.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804130458-37-756406/satu-bulan-tak-hujan-setetes-pun-peristiwa-langka-15-abad</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/23/seorang-wanita-menggunakan-payung-untuk-melindungi-diri-dari-matahari-saat-berjalan-di-dekat-gedung-parlemen-di-tengah-cuaca-p-1782221722073_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sumber Kehidupan Timur Tengah Musnah, Rasulullah Sudah Peringatkan</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Dua sungai legendaris, Eufrat dan Tigris, terancam kering total pada 2040 akibat perubahan iklim. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804143451-37-756460/sumber-kehidupan-timur-tengah-musnah-rasulullah-sudah-peringatkan</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/17/suasana-sungai-tigris-di-baghdad-irak-negara-yang-sangat-terdampak-oleh-perubahan-iklim-telah-dilanda-kekeringan-dan-curah-huj-1765973136752_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Peringatan Buat Amerika, China Sudah Tak Bisa Dikalahkan</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Teknologi AI open-source China makin mendominasi, menantang AS. Banyak perusahaan beralih ke model China yang lebih murah dan mumpuni.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804142947-37-756456/peringatan-buat-amerika-china-sudah-tak-bisa-dikalahkan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/08/02/usa-chinataiwan_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Chromebook Hilang Sempat Ramai di RI, Muncul Googlebook Merk China</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Lenovo memperkenalkan Googlebook, laptop baru dengan desain mirip Chromebook dan kekuatan AI Gemini.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804105737-37-756339/chromebook-hilang-sempat-ramai-di-ri-muncul-googlebook-merk-china</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/04/googlebook-1785816802667_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sinergi Danantara, TelkomGroup Genjot Pasar External InfraNexia 37,6%</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:16:17 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Elga Nurmutia</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>InfraNexia mencatat pertumbuhan positif dengan pendapatan Rp 7,7 triliun di semester I-2026, didukung oleh kepercayaan industri dan transformasi yang efisien.</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804171123-37-756541/sinergi-danantara-telkomgroup-genjot-pasar-external-infranexia-376</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/04/dok-pt-telkom-infrastruktur-indonesia-infranexia-1785838563437_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Marak Karyawan Kerja Cuma Cari Gaji Tinggi, Ternyata Ini Dampaknya</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Perusahaan berlomba-lomba merekrut talenta AI dengan gaji tinggi. Pengusaha ungkap dampaknya. Simak!</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804125149-37-756404/marak-karyawan-kerja-cuma-cari-gaji-tinggi-ternyata-ini-dampaknya</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/11/21/infografis-survei-kenaikan-gaji-tahun-2021-karyawan-ri-naik-gaji-paling-tinggi-di-dunia_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Ulah Amerika Bikin Geger, Satu Dunia Terancam Lumpuh Total</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Insiden peretasan AI di OpenAI dan Anthropic memicu kekhawatiran global. Begini respons pemerintahan Trump.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804112549-37-756350/ulah-amerika-bikin-geger-satu-dunia-terancam-lumpuh-total</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/30/usa-trump-1785371156663_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Grup WhatsApp Rahasia Orang Terkaya Terungkap, Isinya Bikin Kaget</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Grup WhatsApp rahasia isinya orang-orang kaya baru. Begini isinya.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804121447-37-756372/grup-whatsapp-rahasia-orang-terkaya-terungkap-isinya-bikin-kaget</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/03/whatsapp-reutersdado-ruvicillustrationfile-photo-1770118007754_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Uang Rp 18.000 Triliun Hilang Dirampok Maling M-Banking, Waspada!</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Visa mengungkap kerugian global akibat penipuan mencapai Rp18.000 triliun per tahun. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804114416-37-756360/uang-rp-18000-triliun-hilang-dirampok-maling-m-banking-waspada</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/10/17/ilustrasi-penipuan-online_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>iPhone Air 2 Segera Rilis Maret 2027, Spesifikasinya Tak Main-Main</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Apple bersiap meluncurkan iPhone Air generasi kedua pada kuartal I-2027, dengan peningkatan kamera, chipset A20 Pro, dan modem 5G C2.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804134051-37-756442/iphone-air-2-segera-rilis-maret-2027-spesifikasinya-tak-main-main</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/10/iphone-air-tergantung-selama-acara-apple-di-steve-jobs-theater-di-kampusnya-di-cupertino-california-as-9-september-2025-1757463861093_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Waspada Akun WhatsApp Mendadak Diblokir, Pengguna Diminta Lakukan Ini</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pengguna WhatsApp di berbagai negara, termasuk Indonesia, mengalami pemblokiran akun mendadak. Simak peringatan pakar!</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804124323-37-756390/waspada-akun-whatsapp-mendadak-diblokir-pengguna-diminta-lakukan-ini</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/07/18/whatsapp-blur-tangkapan-layar-1752822162616_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Perusahaan Bangkrut Gara-Gara Starlink, Begini Kronologinya</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Dominasi Starlink membuat perusahaan asal AS akhirnya bangkrut. Ratusan karyawan dirumahkan. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804111140-37-756346/perusahaan-bangkrut-gara-gara-starlink-begini-kronologinya</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/06/03/starlink-starlinkcom-2_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Usher GIIAS Direkam Diam-Diam, Bisa Dilacak Pakai Aplikasi Ini</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Aplikasi Antizuck Smart Glasses Scanner untuk iPhone mendeteksi kacamata pintar tanpa izin.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804105316-37-756337/usher-giias-direkam-diam-diam-bisa-dilacak-pakai-aplikasi-ini</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/18/meta-platforms-virtual-reality-1758169373850_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Rekam Warga Diam-Diam Pakai Kacamata Pintar, Pelaku Ditangkap Polisi</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Insiden perekaman tanpa izin menggunakan kacamata pintar bukan cuma terjadi di Indonesia. Pelaku langsung ditangkap polisi.</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804110450-37-756344/rekam-warga-diam-diam-pakai-kacamata-pintar-pelaku-ditangkap-polisi</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/18/meta-platforms-virtual-reality-1758169553502_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Menkomdigi Meutya Bantah Batasi Liputan Demo, Ingatkan Soal Hoaks</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Menteri Komunikasi Meutya Hafid menegaskan media bebas meliput selama mematuhi kaidah jurnalistik.</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804104849-37-756334/menkomdigi-meutya-bantah-batasi-liputan-demo-ingatkan-soal-hoaks</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/menteri-komunikasi-dan-digital-meutya-hafid-di-kantor-komdigi-senin-382026-1785753783932_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 Besok Meluncur ke Orbit Terbang dari China</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 akan diluncurkan pada 5 Agustus 2026 untuk mendukung pertumbuhan ekonomi kelautan dan pengelolaan lingkungan di Lampung.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804090032-37-756284/satelit-lampung-1-besok-meluncur-ke-orbit-terbang-dari-china</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/04/pada-tanggal-5-agustus-starvision-akan-meluncurkan-ose-hyperspectral-twin-satellites-dari-laut-lepas-pantai-shandong-tiongkok--1785809821007_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Ramai Akun WhatsApp Tiba-Tiba Kena Review Tak Bisa Chat, Ini Kata Meta</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>WhatsApp mengalami gangguan, banyak akun terkunci dan dalam status "sedang ditinjau".</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804082259-37-756278/ramai-akun-whatsapp-tiba-tiba-kena-review-tak-bisa-chat-ini-kata-meta</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/11/19/ilustrasi-whatsapp-reutersdado-ruvic_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Mendagri Siapkan Akta Kelahiran Digital, Dokumen Dikirim via Email</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:35:37 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri siapkan akta kelahiran digital yang dikirim via email kepada orang tua. Sistem ini memudahkan pengurusan administrasi kelahiran.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804075937-37-756262/mendagri-siapkan-akta-kelahiran-digital-dokumen-dikirim-via-email</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/menteri-dalam-negeri-mendagri-muhammad-tito-karnavian-1784725668894_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Kabar Baru yang Bakal Bikin Harga HP Makin Mahal</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:13:36 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Harga smartphone diprediksi naik akibat rencana Qualcomm menaikkan harga chip hingga dua digit.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260804081138-37-756273/kabar-baru-yang-bakal-bikin-harga-hp-makin-mahal</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/02/02/penjualan-gawai-5_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Microsoft Warning Pemilik Laptop Windows yang Suka Pakai WiFi Hotel</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Pengguna Windows diimbau waspada saat menggunakan WiFi hotel. Simak langkah aman yang perlu diambil.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803140848-37-756092/microsoft-warning-pemilik-laptop-windows-yang-suka-pakai-wifi-hotel</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/07/02/27b256b7-0a03-41c0-9675-2a7e49892f36_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ketemu Kulit Utuh 125 Juta Tahun, Dinosaurus Ini Ternyata Mirip Landak</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Penemuan fosil dinosaurus Haolong dongi berusia 125 juta tahun di China mengejutkan dunia.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803111405-37-755994/ketemu-kulit-utuh-125-juta-tahun-dinosaurus-ini-ternyata-mirip-landak</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/18/dinosaurus-haolong-naga-berduri-1771410589157_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I157"/>
+  <autoFilter ref="A1:I181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-04.xlsx
+++ b/data/berita_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8940,8 +8940,1042 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Gisel Akui Penuh Tantangan Jadi Orang Tua Tunggal: Tapi Aku Berusaha Terus</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 22:02:30 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Gisel bercerita soal menjadi orang tua tunggal. Ia mengakui hal itu menantang.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604060/gisel-akui-penuh-tantangan-jadi-orang-tua-tunggal-tapi-aku-berusaha-terus</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gisel-1785835834891_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Davina Karamoy Giat Olahraga Karena Suka Makan</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:01:34 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Artis Davina Karamoy mengungkapkan hal di balik giat olahraga. Ia ternyata suka makan.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603951/davina-karamoy-giat-olahraga-karena-suka-makan</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/davina-karamoy-1785833365238_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Adzam Senang Punya 2 Ayah, Nathalie Holscher: Iya Juga Sih Ya</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:09:00 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Putra Nathalie Holscher, Adzam, nempel banget nih dengan Aripat. Ia juga senang karena, punya dua ayah.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603895/adzam-senang-punya-2-ayah-nathalie-holscher-iya-juga-sih-ya</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nathalie-holscher-1785831809878_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Asila Maisa Kasih Paham Hater: Saya Berpenghasilan, Beli Barang Branded Sendiri</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:09:18 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Asila Maisa, putri Ramzi, menanggapi hater yang menyoroti barang branded miliknya. Ia menegaskan penghasilannya sendiri sebagai penyanyi dan influencer.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8604027/asila-maisa-kasih-paham-hater-saya-berpenghasilan-beli-barang-branded-sendiri</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/asila-maisa-1784532141138_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Billy Syahputra soal Jaga Keharmonisan dengan Vika Kolesnaya</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:05:02 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Billy Syahputra berbagi cerita tentang hubungan harmonisnya dengan Vika Kolesnaya, mengakui perselisihan dan pentingnya saling percaya dalam rumah tangga.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603675/billy-syahputra-soal-jaga-keharmonisan-dengan-vika-kolesnaya</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/09/billy-syahputra-1770619097300_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Aura Kasih Gak Peduli Dianggap Jorok Karena Bisnis Ternak Ayam</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:07:15 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Aura Kasih ternyata punya bisnis ternak ayam. Usahanya itu bahkan sudah jalan 4 tahun.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603841/aura-kasih-gak-peduli-dianggap-jorok-karena-bisnis-ternak-ayam</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/aura-kasih-1785830708163_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Gilang Dirga Koleksi Komik Langka hingga Sepatu Ukuran Besar</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:08:29 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Gilang Dirga, presenter dan komedian, mengungkapkan kecintaannya pada komik dan sepatu. Ia mengoleksi komik legendaris dan sepatu berukuran 45.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603771/gilang-dirga-koleksi-komik-langka-hingga-sepatu-ukuran-besar</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/15/gilang-dirga-1755247487861_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Nadine Kaiser, Putri Susi Pudjiastuti Berduka</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:36:25 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Ada kabar duka dari Nadine Kaiser, putri Susi Pudjiastuti. Ayahnya meninggal dunia.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603924/nadine-kaiser-putri-susi-pudjiastuti-berduka</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/nadine-kaiser-1785832454505_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Denny Sumargo Ajarkan Kesederhanaan di Perayaan Ulang Tahun Kedua Anak</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:11:58 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Denny Sumargo merayakan ulang tahun kedua putrinya, Biel, dengan sederhana. Ia mengajak Biel ke panti asuhan untuk menanamkan nilai-nilai kehidupan positif.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603659/denny-sumargo-ajarkan-kesederhanaan-di-perayaan-ulang-tahun-kedua-anak</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/16/5-potret-gabriella-anak-denny-sumargo-olivia-1773640376402_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Roland Judita Bikin Heboh Sukatani, Diserbu Ibu-ibu Saat Manggung</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:27:37 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Roland Judita memukau penonton di acara tahunan Sukatani, membawakan 8 lagu hits. Ia unik, lebih suka nyawer penonton daripada disawer.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8603755/roland-judita-bikin-heboh-sukatani-diserbu-ibu-ibu-saat-manggung</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/roland-judita-1785828036839_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Bahagia Tengku Firmansyah Masjid Pertama Edmonton Berdiri, Nikita Willy Datang</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:07:35 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Tengku Firmansyah membagiakn momen soft launching masjid pertama di Edmonton. Momen itu juga dihadiri Nikita Willy dan suami.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603679/bahagia-tengku-firmansyah-masjid-pertama-edmonton-berdiri-nikita-willy-datang</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/tengku-firmansyah-1785822802047_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Gilang Dirga Kantongi Sertifikasi Blue Economy, Jadi Bekal Proyek Kuliah</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:06:44 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Gilang Dirga meraih sertifikasi Certified Blue Economist untuk memahami ekonomi biru. Ini alasan Gilang Dirga.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603324/gilang-dirga-kantongi-sertifikasi-blue-economy-jadi-bekal-proyek-kuliah</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/26/gilang-dirga-1756186241877_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Aura Kasih Punya Pacar Blasteran, Sudah Dekat dengan Anak</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:34:41 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aura Kasih mengungkap kehidupan asmaranya, kini memiliki kekasih baru. Ia menyebut hubungan tersebut sudah diketahui putrinya dan terjalin baik.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602940/aura-kasih-punya-pacar-blasteran-sudah-dekat-dengan-anak</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/23/aura-kasih-1784765419252_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Syahrini Rayakan Ultah di Bali, Tulis Ungkapan Menyentuh</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:10:58 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Syahrini merayakan ulang tahun ke-46 di Bali. Gak cuma itu, putrinya juga merayakan ulang tahun kedua.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601904/syahrini-rayakan-ultah-di-bali-tulis-ungkapan-menyentuh</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/syahirni-1785730899366_43.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Aura Kasih 4 Tahun Jadi Pebisnis Ternak Ayam: Nggak Ngejar Duit Gede</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:33:30 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Aura Kasih kini fokus pada bisnis peternakan ayam dan pertanian setelah jarang tampil di hiburan. Ia menekuni usaha ini untuk ketahanan pangan mandiri.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602902/aura-kasih-4-tahun-jadi-pebisnis-ternak-ayam-nggak-ngejar-duit-gede</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/23/aura-kasih-1766497327694_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Perasaan Aaliyah-Zahwa Massaid Nyanyi Bareng Reza Artamevia</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:02:17 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Pemandangan menarik tersaji dalam keluarga Reza Artamevia. Ia bernyanyi bareng kedua anaknya, Aaliyah dan Zahwa Massaid.</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601811/perasaan-aaliyah-zahwa-massaid-nyanyi-bareng-reza-artamevia</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/reza-artamevia-1785728402396_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Respons Denny Sumargo Dituding Memihak di Masalah Ruben Onsu-Sarwendah</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:05:27 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Denny Sumargo menghadapi kritik netizen terkait netralitasnya dalam wawancara Sarwendah dan Ruben Onsu.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603241/respons-denny-sumargo-dituding-memihak-di-masalah-ruben-onsu-sarwendah</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/30/denny-sumargo-1782801402795_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Catherine Wilson soal Belum Punya Pasangan Lagi</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:09:44 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Selebritas Catherine Wilson atau yang akrab disapa Keket, bicara soal belum punya pasangan lagi.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601193/catherine-wilson-soal-belum-punya-pasangan-lagi</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/07/catherine-wilson_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Rina Nose Tak Asal Oplas, Pertimbangkan Fungsi hingga Ideal Orang Asia</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:08:10 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Rina Nose menjadi salah satu selebritas yang melakukan operasi hidung. Rina mengaku nggak asal, tapi juga mempertimbangkan banyak hal sebelum operasi.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603215/rina-nose-tak-asal-oplas-pertimbangkan-fungsi-hingga-ideal-orang-asia</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/rina-nose-1778220542305_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Pihak Ruben Onsu Minta Isu Selingkuh Tak Diungkit Lagi</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:04:18 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Ruben Onsu, Minola Sebayang, menegaskan tuduhan perselingkuhan kliennya tidak terbukti dan meminta fokus pada proses hukum serta hak asuh anak.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602894/pihak-ruben-onsu-minta-isu-selingkuh-tak-diungkit-lagi</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/03/ruben-onsu-1783015395436_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Diding Boneng Meninggal Dunia, Raffi Ahmad Berduka</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:08:48 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Raffi Ahmad ikut berduka dengan kabar meninggalnya Diding Boneng. Hal ini terlihat dalam Instagram miliknya.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602100/diding-boneng-meninggal-dunia-raffi-ahmad-berduka</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/diding-boneng-1785737813815_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Joanna Alexandra Buka Lembaran Baru dengan Christover Usai 5 Tahun Sendiri</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:10:24 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Joanna Alexandra mengakhiri masa sendirinya usai lima tahun Raditya Oloan meninggal. Ia menjalin asmara dengan Immanuel Christover, sampai di titik pernikahan.</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8603128/joanna-alexandra-buka-lembaran-baru-dengan-christover-usai-5-tahun-sendiri</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/joanna-aklexandra-1785743358499_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I181"/>
+  <autoFilter ref="A1:I203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-04.xlsx
+++ b/data/berita_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$237</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:I237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9974,8 +9974,1606 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>FOTO: Kuba Gelap Gulita Akibat Blokade AS</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 22:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>REUTERS</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Jaringan listrik nasional kolaps di Havana, Kuba, imbas blokade energi Amerika Serikat.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804083058-136-1388299/foto-kuba-gelap-gulita-akibat-blokade-as</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/negara-kuba-gelap-gulita-akibat-blokade-as-1785805225218_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>BoP: Israel Tarik Pasukan di Gaza jika Hamas Selesai Serahkan Senjata</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:05:06 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>BoP sebut penarikan militer Israel dari Gaza baru akan dimulai jika Hamas selesaikan pelucutan senjata.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804170410-120-1388547/bop-israel-tarik-pasukan-di-gaza-jika-hamas-selesai-serahkan-senjata</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/10/11/israel-mulai-tarik-mundur-pasukan-dari-gaza-1760164942685_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Pusat Data AI Jadi Target Empuk Iran, Bisa Bikin AS 'Babak Belur'</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:41:06 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Iran mulai menjadikan Pusat Data Akal Imitasi (AI) AS di negara-negara Timur Tengah sebagai sasaran empuk dalam rencana serangan mereka.</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804203408-120-1388657/pusat-data-ai-jadi-target-empuk-iran-bisa-bikin-as-babak-belur</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/28/balas-gempuran-as-iran-luncurkan-serangan-ke-bahrain-1782643855052_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Wilayah di Negara Tetangga RI Bakal Merdeka, Ini Namanya</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:45:25 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Wilayah otonom Bougainville menetapkan akan akhiri pemerintahan otonom, bakal umumkan kemerdekaan pada 2030.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804185206-113-1388604/wilayah-di-negara-tetangga-ri-bakal-merdeka-ini-namanya</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/png-politics-bougainville-referendum-1785844555639_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Dikabarkan Bakal Mundur, Presiden Iran Pezeshkian Buka Suara</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:20:02 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Presiden Iran Masoud Pezeshkian buka suara setelah dikabarkan bakal mundur di tengah perang dengan Amerika Serikat dan Israel.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804184825-120-1388601/dikabarkan-bakal-mundur-presiden-iran-pezeshkian-buka-suara</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/18/presiden-iran-masoud-pezeshkian-memegang-dokumen-yang-menunjukkan-nota-kesepahaman-yang-ditandatanganinya-untuk-mengakhiri-per-1781763114445_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Trump Bangga Beri Iran Kesempatan Terakhir daripada Bom Teheran</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:45:26 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump mengaku bangga bisa memberi Iran kesempatan negosiasi daripada terus membom Teheran.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804153740-134-1388517/trump-bangga-beri-iran-kesempatan-terakhir-daripada-bom-teheran</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/18/kelakar-trump-usai-inggris-tersingkir-harry-kane-jadi-sorotan-1784345022835_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Media Israel Cemooh Trump soal Ancaman ke Iran, Dianggap Gertak Sambal</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:08:23 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Media Israel mengejek pernyataan Presiden Amerika Serikat Donald Trump terkait ancamannya ke Israel yang dianggap gertak sambal.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804174843-120-1388562/media-israel-cemooh-trump-soal-ancaman-ke-iran-dianggap-gertak-sambal</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/06/presiden-amerika-donald-trump-1780743428817_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Survei: Mayoritas Warga Israel Tak Percaya Netanyahu Menang Pemilu</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:28:11 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Jajak pendapat terbaru untuk memotret pandangan warga Israel terhadap kepemimpinan PM Netanyahu memberi isyarat kekalahan dalam Pemilu Oktober.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804170725-120-1388549/survei-mayoritas-warga-israel-tak-percaya-netanyahu-menang-pemilu</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/03/24/israel-gelar-pemilu-4-kali-dalam-dua-tahun-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Hampir Seribu Tentara Israel Diklaim Tewas Sejak Agresi ke Gaza</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:55:24 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Total hampir seribu tentara Israel diklaim tewas sejak agresi Zionis ke Jalur Gaza, termasuk perang melawan Iran, dan milisi di Lebanon serta Yaman.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804164731-120-1388543/hampir-seribu-tentara-israel-diklaim-tewas-sejak-agresi-ke-gaza</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/12/09/tentara-israel-1765247279132_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Warga Israel Ramai-ramai Kabur dari Negaranya, Tembus Hingga 268.000</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:22:22 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Warga Israel berbondong-bondong kabur dari negara mereka selama konflik di Timur Tengah berlangsung.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804152245-120-1388509/warga-israel-ramai-ramai-kabur-dari-negaranya-tembus-hingga-268000</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/10/10/bandara-ben-gurion-di-israel-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Iran Batal Serang Ukraina usai Kyiv Minta Maaf</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:49:32 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Iran membatalkan serangan yang menargetkan tiga situs di Ukraina, setelah Kyiv menyampaikan permintaan maaf buntut serangan ke kapal dagang milik Teheran.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804153519-120-1388515/iran-batal-serang-ukraina-usai-kyiv-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/24/penasihat-militer-senior-iran-mohsen-rezaei-1774324927767_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Kasus Diare Meledak di AS, 11 Ribu Warga Positif Terpapar</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:16:38 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Dua orang meninggal dan 11 ribu lainnya di Amerika Serikat positif terpapar wabah yang memicu diare akut.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804144713-134-1388492/kasus-diare-meledak-di-as-11-ribu-warga-positif-terpapar</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/05/19/ilustrasi-anak-di-toilet_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AS Bersiap Tutup Konsulat di Medan Demi Hemat Anggaran</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:41:27 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Kemlu Amerika Serikat bakal tutup lima misi diplomatik asing di luar negeri, salah satunya konsulat di Medan, Sumatra Utara.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804131433-134-1388433/as-bersiap-tutup-konsulat-di-medan-demi-hemat-anggaran</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/05/17/ilustrasi-bendera-amerika-1747462907616_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Polisi Malaysia Kenali Petugas yang Loloskan Pilot Bawa Narkoba ke RI</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:31 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Kepolisian Malaysia telah mengidentifikasi petugas bandara KLIA yang meloloskan pilot pembawa narkotika 26 kilogram ke Indonesia, Mohd Saufi bin Othman.</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804134018-106-1388451/polisi-malaysia-kenali-petugas-yang-loloskan-pilot-bawa-narkoba-ke-ri</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/31/pilot-maskapai-asing-ditangkap-di-bandara-soetta-usai-kedapatan-bawa-sabu-dan-ekstasi-25-kg-1785461146712_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Negara Ini Resmi Ganti Nama Baru</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Negara terkecil ketiga di dunia resmi mengganti nama sesuai dengan bahasa nasional mereka.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804115456-113-1388380/negara-ini-resmi-ganti-nama-baru</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/11/19/dbd9db88-30d2-4a66-9aee-1194a86bd2e2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Apa itu Ceuta di Spanyol yang Jadi Tujuan Ribuan Migran Maroko?</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Mengenal wilayah Ceuta Spanyol yang diserbu puluhan ribu migran ilegal dari Maroko.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260803200227-134-1388178/apa-itu-ceuta-di-spanyol-yang-jadi-tujuan-ribuan-migran-maroko</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/02/spanyol-pasang-penghalang-apung-usai-diserbu-imigran-maroko-1785668295763_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Trump Ultimatum Iran Buat Nego: Kesempatan Terakhir Sebelum Dipenggal</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Presiden AS Donald Trump mengultimatum Iran soal kesempatan terakhir untuk berunding sebelum menghadapi konsekuensi yang lebih besar lagi dari sekadar perang.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804095931-139-1388326/trump-ultimatum-iran-buat-nego-kesempatan-terakhir-sebelum-dipenggal</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/thumbnail-video-1785812552160_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Malaysia Bingung Pilot Bisa Lolos Selundupkan 26 Kg Narkoba ke RI</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Malaysia masih menyelidiki pilot Malaysia Airlines Mohd Saufi yang lolos serangkaian pemeriksaan bandara dan menyelundupkan 26 kilogram narkoba ke Indonesia.</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804114042-106-1388368/malaysia-bingung-pilot-bisa-lolos-selundupkan-26-kg-narkoba-ke-ri</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/02/17/be21f5ca-953a-4f51-93c2-f3a7ce29da94_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Netanyahu Makin Gila, Samakan Warga Gaza dengan Korut Tak Bisa Keluar</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>PM Israel Benjamin Netanyahu menyamakan warga di Jalur Gaza Palestina dengan Korea Utara karena penduduknya tak bisa meninggalkan wilayah tersebut.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804101713-120-1388334/netanyahu-samakan-warga-gaza-dengan-korut-tak-bisa-keluar-palestina</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/28/benjamin-netanyahu-1759026599434_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>AS Ngotot Iran Masuk List, Negara Mana Saja yang Punya Senjata Nuklir?</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Negara pemilik senjata nuklir menjadi sorotan dalam beberapa waktu terakhir di tengah konflik yang terus membara antara Iran dan Amerika Serikat.</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804090547-113-1388312/as-ngotot-iran-masuk-list-negara-mana-saja-yang-punya-senjata-nuklir</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/06/23/fasilitas-nuklir-iran-dari-citra-satelit-usai-diserang-as-1750655690951_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Iran Mulai Diserang dari Dalam, Milisi Kurdi Serbu Pangkalan IRGC</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Sayap bersenjata kelompok Kurdi mengklaim bertanggung jawab atas serangan terhadap pasukan Iran di Marivan, Provinsi Kurdistan, Rojhelat, Minggu (2/8).</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804092418-120-1388324/iran-mulai-diserang-dari-dalam-milisi-kurdi-serbu-pangkalan-irgc</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/29/jet-tempur-f-5-iran-1777452483869_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Apa Saja Hasil Pertemuan Prabowo dan PM Thailand Anutin Charnvirakul?</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pertemuan Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul di Jakarta, Senin (3/8), membahas dan menghasilkan sejumlah kesepakatan</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804093619-106-1388321/apa-saja-hasil-pertemuan-prabowo-dan-pm-thailand-anutin-charnvirakul</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/pm-thailand-sowan-ke-ri-usai-15-tahun-absen-1785759396308_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Trump Ultimatum Iran: Ini Kesempatan Terakhir Sebelum Dipenggal</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Presiden AS Donald Trump mengultimatum Iran soal kesempatan terakhir untuk berunding sebelum menghadapi konsekuensi yang lebih besar lagi dari sekadar perang.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804084241-134-1388309/trump-soal-iran-bebal-negosiasi-kesempatan-terakhir-sebelum-dipenggal</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/06/presiden-amerika-donald-trump-1780736862156_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Momen Prabowo Terima Baret Merah dan Medali Militer Dari PM Thailand</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Sekretariat Presiden</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Presiden RI Prabowo Subianto menerima tanda kehormatan militer Medali Special Warfare Command, Royal Thai Army dari Kerajaan Thailand.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804080109-110-1388291/momen-prabowo-terima-baret-merah-medali-militer-dari-pm-thailand</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/thumbnail-video-1785805537984_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>BBM Makin Langka, Kuba Gelap Gulita Imbas Pemadaman Listrik Nasional</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Kuba mengalami pemadaman listrik nasional imbas kekurangan bahan bakar akut. Ini pemadaman nasional kali keenam sepanjang 2026.</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804075452-134-1388288/bbm-makin-langka-kuba-gelap-gulita-imbas-pemadaman-listrik-nasional</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/09/kuba-gelap-total-10-juta-warga-tercekik-blokade-as-1783597551121_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>China Gelar Latihan Militer di LCS, Makin Dekat ke Perairan RI</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>China disebut latihan angkatan laut dan udara di pulau sengketa, di sekitar Scarborough Shoal, Laut China Selatan, pada Sabtu (1/8).</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260803202729-113-1388186/china-gelar-latihan-militer-di-lcs-makin-dekat-ke-perairan-ri</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/06/kapal-penjaga-pantai-tiongkok-semprotkan-meriam-air-ke-kapal-filipina-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Trump soal Iran Bantah Nego dengan AS Lagi: Sangat Bermuka Dua!</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Presiden Donald Trump melontarkan kecaman keras setelah Iran membantah tengah bernegosiasi lagi dengan Amerika Serikat.</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804064026-120-1388265/trump-soal-iran-bantah-nego-dengan-as-lagi-sangat-bermuka-dua</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/09/donald-trump-1783564607045_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Tolak Deal Hamas-AS, Israel Bombardir Gaza Lagi Meski Sedang Gencatan</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:00:32 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Israel kembali menggempur habis-habisan Jalur Gaza, Palestina, pada pekan lalu meski masih dalam masa gencatan senjata.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804065547-120-1388268/tolak-deal-hamas-as-israel-bombardir-gaza-lagi-meski-sedang-gencatan</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/momen-serangan-udara-israel-hantam-masjid-di-gaza-1785308539451_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Makna 'Baret Merah' dan Medali Militer Thailand yang Diterima Prabowo</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto jadi kepala negara asing yang dianugerahi tanda kehormatan militer Medali Special Warfare Command, Royal Thai Army Kerajaan Thailand.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804055641-106-1388236/makna-baret-merah-medali-militer-thailand-yang-diterima-prabowo</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/pm-thailand-beri-prabowo-penghargaan-1785799148877_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Malaysia Selidiki Pilot Selundup Ekstasi ke RI sampai Militer AS Buntu</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:05 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Kasus pilot Malaysia penyelundup narkoba ke RI hingga Perang AS vs Iran yang masih berlangsung masih menjadi perhatian berita internasional pada Senin (3/8).</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260804054509-113-1388233/malaysia-selidiki-pilot-selundup-ekstasi-ke-ri-sampai-militer-as-buntu</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/14/ilustrasi-bendera-malaysia_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Gudang Senjata Militer Irak Terbakar Gara-gara Suhu Panas Ekstrem</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Gudang senjata di pangkalan militer utama Irak terbakar gara-gara suhu panas ekstrem.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260803192316-120-1388158/gudang-senjata-militer-irak-terbakar-gara-gara-suhu-panas-ekstrem</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/30/ilustrasi-ledakan-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>FOTO: Kebakaran Spokane Terburuk Sepanjang Sejarah, 65 Ribu Mengungsi</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:30:36 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Kobaran api ganas melahap kawasan Spokane, Washington, 600 bangunan hancur dan ribuan keluarga terpaksa mengungsi.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260803172231-136-1388105/foto-kebakaran-spokane-terburuk-sepanjang-sejarah-65-ribu-mengungsi</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/kebakaran-spokane-terburuk-sepanjang-sejarah-65-ribu-mengungsi-1785752406656_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>FOTO: Penembakan di Pusat Perbelanjaan Idaho AS</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:00:08 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Aksi penembakan mengguncang kawasan pusat perbelanjaan di Kota Twin Falls, Idaho AS, menewaskan tiga orang termasuk pelaku serta melukai dua orang.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260803122018-136-1387958/foto-penembakan-di-pusat-perbelanjaan-idaho-as</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/penembakan-di-restoran-di-idaho-as-1785721411083_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>FOTO: Bom Bunuh Diri Meledak di Pakistan, 14 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:00:35 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Unjuk rasa anti-milisi dan perdamaian di Provinsi Khyber Pakhtunkhwa, Pakistan, berubah menjadi tragedi setelah bom bunuh diri meledak di lokasi demonstrasi.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260803114109-115-1387936/foto-bom-bunuh-diri-meledak-di-pakistan-14-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/bom-bunuh-diri-meledak-di-pakistan-14-orang-tewas-1785732017784_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I203"/>
+  <autoFilter ref="A1:I237"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>